--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{599F8649-C465-7A4D-87AA-7F6692DE965C}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD67BE2A-5F38-B848-BFBA-2198F6680C4E}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="660" windowWidth="24680" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2183,9 +2183,6 @@
     <t>Anno di Contratto corrente</t>
   </si>
   <si>
-    <t>consules</t>
-  </si>
-  <si>
     <t>Mendy P.</t>
   </si>
   <si>
@@ -2262,6 +2259,9 @@
   </si>
   <si>
     <t>E;M</t>
+  </si>
+  <si>
+    <t>Wehrmacht FC</t>
   </si>
 </sst>
 </file>
@@ -2331,10 +2331,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2845,7 +2841,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H4" s="2">
         <v>9</v>
@@ -2859,7 +2855,7 @@
         <v>15.75</v>
       </c>
       <c r="K4" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
@@ -2879,7 +2875,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -2910,7 +2906,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -2978,7 +2974,7 @@
         <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -3012,7 +3008,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H9" s="2">
         <v>20</v>
@@ -3077,7 +3073,7 @@
         <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -3111,7 +3107,7 @@
         <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H12" s="2">
         <v>13</v>
@@ -3306,7 +3302,7 @@
         <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H18">
         <v>2</v>
@@ -3377,7 +3373,7 @@
         <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H20" s="2">
         <v>4</v>
@@ -3547,7 +3543,7 @@
         <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -3578,7 +3574,7 @@
         <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H26">
         <v>11</v>
@@ -3739,7 +3735,7 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H31">
         <v>13</v>
@@ -3838,7 +3834,7 @@
         <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H34">
         <v>3</v>
@@ -3971,7 +3967,7 @@
         <v>29</v>
       </c>
       <c r="G38" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H38" s="2">
         <v>13</v>
@@ -4263,7 +4259,7 @@
         <v>1.75</v>
       </c>
       <c r="K46" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -4317,7 +4313,7 @@
         <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H48" s="2">
         <v>12</v>
@@ -4331,7 +4327,7 @@
         <v>21</v>
       </c>
       <c r="K48" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -4447,7 +4443,7 @@
         <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H52" s="2">
         <v>4</v>
@@ -4484,7 +4480,7 @@
         <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H53" s="2">
         <v>13</v>
@@ -4589,7 +4585,7 @@
         <v>33</v>
       </c>
       <c r="G56" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H56" s="2">
         <v>8</v>
@@ -4623,7 +4619,7 @@
         <v>32</v>
       </c>
       <c r="G57" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H57">
         <v>3</v>
@@ -4671,7 +4667,7 @@
         <v>15.75</v>
       </c>
       <c r="K58" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -4691,7 +4687,7 @@
         <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H59">
         <v>7</v>
@@ -4725,7 +4721,7 @@
         <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H60" s="2">
         <v>12</v>
@@ -4793,7 +4789,7 @@
         <v>32</v>
       </c>
       <c r="G62" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H62" s="2">
         <v>16</v>
@@ -4807,7 +4803,7 @@
         <v>28</v>
       </c>
       <c r="K62" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -4864,7 +4860,7 @@
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H64">
         <v>6</v>
@@ -4895,7 +4891,7 @@
         <v>33</v>
       </c>
       <c r="G65" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -4991,7 +4987,7 @@
         <v>28</v>
       </c>
       <c r="G68" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H68" s="2">
         <v>17</v>
@@ -5025,7 +5021,7 @@
         <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H69">
         <v>10</v>
@@ -5056,7 +5052,7 @@
         <v>28</v>
       </c>
       <c r="G70" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H70">
         <v>2</v>
@@ -5141,7 +5137,7 @@
         <v>28</v>
       </c>
       <c r="K72" t="s">
-        <v>13</v>
+        <v>742</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -5192,7 +5188,7 @@
         <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -5226,7 +5222,7 @@
         <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H75" s="2">
         <v>12</v>
@@ -5277,7 +5273,7 @@
         <v>28</v>
       </c>
       <c r="K76" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
@@ -5297,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="G77" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -5541,7 +5537,7 @@
         <v>28</v>
       </c>
       <c r="G84" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H84" s="2">
         <v>19</v>
@@ -5615,7 +5611,7 @@
         <v>33</v>
       </c>
       <c r="G86" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H86" s="2">
         <v>8</v>
@@ -5652,7 +5648,7 @@
         <v>31</v>
       </c>
       <c r="G87" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H87" s="2">
         <v>24</v>
@@ -5717,7 +5713,7 @@
         <v>32</v>
       </c>
       <c r="G89" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H89">
         <v>3</v>
@@ -5810,7 +5806,7 @@
         <v>32</v>
       </c>
       <c r="G92" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -5889,7 +5885,7 @@
         <v>26.25</v>
       </c>
       <c r="K94" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
@@ -6005,7 +6001,7 @@
         <v>30</v>
       </c>
       <c r="G98" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H98" s="2">
         <v>23</v>
@@ -6019,7 +6015,7 @@
         <v>40.25</v>
       </c>
       <c r="K98" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -6073,7 +6069,7 @@
         <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H100" s="2">
         <v>24</v>
@@ -6311,7 +6307,7 @@
         <v>36</v>
       </c>
       <c r="G107" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H107">
         <v>3</v>
@@ -6342,7 +6338,7 @@
         <v>37</v>
       </c>
       <c r="G108" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H108">
         <v>9</v>
@@ -6376,7 +6372,7 @@
         <v>36</v>
       </c>
       <c r="G109" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H109" s="2">
         <v>14</v>
@@ -6481,7 +6477,7 @@
         <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H112" s="2">
         <v>10</v>
@@ -6555,7 +6551,7 @@
         <v>32</v>
       </c>
       <c r="G114" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H114" s="2">
         <v>7</v>
@@ -6589,7 +6585,7 @@
         <v>32</v>
       </c>
       <c r="G115" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -6620,7 +6616,7 @@
         <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -6756,7 +6752,7 @@
         <v>26</v>
       </c>
       <c r="G120" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H120">
         <v>5</v>
@@ -6787,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="G121" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H121">
         <v>3</v>
@@ -6889,7 +6885,7 @@
         <v>26</v>
       </c>
       <c r="G124" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H124" s="2">
         <v>13</v>
@@ -6926,7 +6922,7 @@
         <v>26</v>
       </c>
       <c r="G125" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H125" s="2">
         <v>19</v>
@@ -7102,7 +7098,7 @@
         <v>32</v>
       </c>
       <c r="G130" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H130">
         <v>10</v>
@@ -7136,7 +7132,7 @@
         <v>28</v>
       </c>
       <c r="G131" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H131" s="2">
         <v>11</v>
@@ -7170,7 +7166,7 @@
         <v>26</v>
       </c>
       <c r="G132" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H132">
         <v>8</v>
@@ -7300,7 +7296,7 @@
         <v>28</v>
       </c>
       <c r="G136" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -7331,7 +7327,7 @@
         <v>26</v>
       </c>
       <c r="G137" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H137">
         <v>4</v>
@@ -7467,7 +7463,7 @@
         <v>29</v>
       </c>
       <c r="G141" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H141">
         <v>9</v>
@@ -7498,7 +7494,7 @@
         <v>27</v>
       </c>
       <c r="G142" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H142">
         <v>11</v>
@@ -7563,7 +7559,7 @@
         <v>29</v>
       </c>
       <c r="G144" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H144" s="2">
         <v>10</v>
@@ -7577,7 +7573,7 @@
         <v>17.5</v>
       </c>
       <c r="K144" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
@@ -7614,7 +7610,7 @@
         <v>15.75</v>
       </c>
       <c r="K145" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
@@ -7637,7 +7633,7 @@
         <v>30</v>
       </c>
       <c r="G146" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H146" s="2">
         <v>16</v>
@@ -7733,7 +7729,7 @@
         <v>33</v>
       </c>
       <c r="G149" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H149">
         <v>3</v>
@@ -7767,7 +7763,7 @@
         <v>31</v>
       </c>
       <c r="G150" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H150" s="2">
         <v>11</v>
@@ -7875,7 +7871,7 @@
         <v>25</v>
       </c>
       <c r="G153" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H153">
         <v>8</v>
@@ -8016,7 +8012,7 @@
         <v>26.25</v>
       </c>
       <c r="K157" t="s">
-        <v>13</v>
+        <v>742</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
@@ -8036,7 +8032,7 @@
         <v>25</v>
       </c>
       <c r="G158" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H158">
         <v>5</v>
@@ -8070,7 +8066,7 @@
         <v>26</v>
       </c>
       <c r="G159" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H159" s="2">
         <v>6</v>
@@ -8084,7 +8080,7 @@
         <v>10.5</v>
       </c>
       <c r="K159" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
@@ -8104,7 +8100,7 @@
         <v>29</v>
       </c>
       <c r="G160" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H160">
         <v>4</v>
@@ -8172,7 +8168,7 @@
         <v>29</v>
       </c>
       <c r="G162" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H162">
         <v>12</v>
@@ -8257,7 +8253,7 @@
         <v>3.5</v>
       </c>
       <c r="K164" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
@@ -8280,7 +8276,7 @@
         <v>32</v>
       </c>
       <c r="G165" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H165" s="2">
         <v>15</v>
@@ -8368,7 +8364,7 @@
         <v>12.25</v>
       </c>
       <c r="K167" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
@@ -8425,7 +8421,7 @@
         <v>24</v>
       </c>
       <c r="G169" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H169">
         <v>2</v>
@@ -8459,7 +8455,7 @@
         <v>26</v>
       </c>
       <c r="G170" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H170" s="2">
         <v>6</v>
@@ -8567,7 +8563,7 @@
         <v>26</v>
       </c>
       <c r="G173" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H173">
         <v>7</v>
@@ -8601,7 +8597,7 @@
         <v>28</v>
       </c>
       <c r="G174" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H174" s="2">
         <v>13</v>
@@ -8615,7 +8611,7 @@
         <v>22.75</v>
       </c>
       <c r="K174" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
@@ -8669,7 +8665,7 @@
         <v>25</v>
       </c>
       <c r="G176" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H176" s="2">
         <v>10</v>
@@ -8720,7 +8716,7 @@
         <v>35</v>
       </c>
       <c r="K177" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
@@ -8774,7 +8770,7 @@
         <v>28</v>
       </c>
       <c r="G179" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H179" s="2">
         <v>14</v>
@@ -8808,7 +8804,7 @@
         <v>25</v>
       </c>
       <c r="G180" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H180">
         <v>7</v>
@@ -8910,7 +8906,7 @@
         <v>26</v>
       </c>
       <c r="G183" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H183" s="2">
         <v>10</v>
@@ -8944,7 +8940,7 @@
         <v>33</v>
       </c>
       <c r="G184" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H184">
         <v>9</v>
@@ -9046,7 +9042,7 @@
         <v>25</v>
       </c>
       <c r="G187" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H187" s="2">
         <v>10</v>
@@ -9134,7 +9130,7 @@
         <v>12.25</v>
       </c>
       <c r="K189" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
@@ -9157,7 +9153,7 @@
         <v>29</v>
       </c>
       <c r="G190" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H190" s="2">
         <v>25</v>
@@ -9290,7 +9286,7 @@
         <v>25</v>
       </c>
       <c r="G194" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H194">
         <v>8</v>
@@ -9395,7 +9391,7 @@
         <v>31</v>
       </c>
       <c r="G197" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H197">
         <v>1</v>
@@ -9429,7 +9425,7 @@
         <v>26</v>
       </c>
       <c r="G198" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H198" s="2">
         <v>15</v>
@@ -9466,7 +9462,7 @@
         <v>24</v>
       </c>
       <c r="G199" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H199" s="2">
         <v>11</v>
@@ -9624,7 +9620,7 @@
         <v>25</v>
       </c>
       <c r="G204" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H204">
         <v>4</v>
@@ -9655,7 +9651,7 @@
         <v>25</v>
       </c>
       <c r="G205" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H205">
         <v>10</v>
@@ -9717,7 +9713,7 @@
         <v>34</v>
       </c>
       <c r="G207" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H207">
         <v>16</v>
@@ -9751,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="G208" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H208" s="2">
         <v>18</v>
@@ -9788,7 +9784,7 @@
         <v>25</v>
       </c>
       <c r="G209" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H209" s="2">
         <v>14</v>
@@ -9856,7 +9852,7 @@
         <v>30</v>
       </c>
       <c r="G211" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H211" s="2">
         <v>10</v>
@@ -9995,7 +9991,7 @@
         <v>25</v>
       </c>
       <c r="G215" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H215">
         <v>13</v>
@@ -10094,7 +10090,7 @@
         <v>24</v>
       </c>
       <c r="G218" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H218">
         <v>7</v>
@@ -10156,7 +10152,7 @@
         <v>25</v>
       </c>
       <c r="G220" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H220">
         <v>2</v>
@@ -10187,7 +10183,7 @@
         <v>29</v>
       </c>
       <c r="G221" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H221">
         <v>3</v>
@@ -10221,7 +10217,7 @@
         <v>27</v>
       </c>
       <c r="G222" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H222" s="2">
         <v>2</v>
@@ -10255,7 +10251,7 @@
         <v>33</v>
       </c>
       <c r="G223" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H223">
         <v>5</v>
@@ -10286,7 +10282,7 @@
         <v>30</v>
       </c>
       <c r="G224" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H224">
         <v>5</v>
@@ -10317,7 +10313,7 @@
         <v>23</v>
       </c>
       <c r="G225" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H225">
         <v>5</v>
@@ -10379,7 +10375,7 @@
         <v>26</v>
       </c>
       <c r="G227" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H227">
         <v>8</v>
@@ -10413,7 +10409,7 @@
         <v>24</v>
       </c>
       <c r="G228" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H228" s="2">
         <v>8</v>
@@ -10478,7 +10474,7 @@
         <v>25</v>
       </c>
       <c r="G230" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H230">
         <v>6</v>
@@ -10571,7 +10567,7 @@
         <v>27</v>
       </c>
       <c r="G233" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H233">
         <v>1</v>
@@ -10695,7 +10691,7 @@
         <v>27</v>
       </c>
       <c r="G237" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H237">
         <v>11</v>
@@ -10726,7 +10722,7 @@
         <v>26</v>
       </c>
       <c r="G238" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H238">
         <v>2</v>
@@ -10760,7 +10756,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H239" s="2">
         <v>14</v>
@@ -10797,7 +10793,7 @@
         <v>24</v>
       </c>
       <c r="G240" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H240" s="2">
         <v>10</v>
@@ -10831,7 +10827,7 @@
         <v>33</v>
       </c>
       <c r="G241" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H241">
         <v>9</v>
@@ -10893,7 +10889,7 @@
         <v>24</v>
       </c>
       <c r="G243" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H243">
         <v>11</v>
@@ -10955,7 +10951,7 @@
         <v>27</v>
       </c>
       <c r="G245" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H245">
         <v>5</v>
@@ -11017,7 +11013,7 @@
         <v>30</v>
       </c>
       <c r="G247" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H247">
         <v>4</v>
@@ -11110,7 +11106,7 @@
         <v>23</v>
       </c>
       <c r="G250" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H250">
         <v>11</v>
@@ -11141,7 +11137,7 @@
         <v>29</v>
       </c>
       <c r="G251" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H251">
         <v>13</v>
@@ -11274,7 +11270,7 @@
         <v>27</v>
       </c>
       <c r="G255" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H255" s="2">
         <v>11</v>
@@ -11339,7 +11335,7 @@
         <v>23</v>
       </c>
       <c r="G257" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H257">
         <v>1</v>
@@ -11444,7 +11440,7 @@
         <v>25</v>
       </c>
       <c r="G260" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H260">
         <v>6</v>
@@ -11475,7 +11471,7 @@
         <v>26</v>
       </c>
       <c r="G261" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H261">
         <v>6</v>
@@ -11506,7 +11502,7 @@
         <v>25</v>
       </c>
       <c r="G262" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H262">
         <v>2</v>
@@ -11577,7 +11573,7 @@
         <v>31</v>
       </c>
       <c r="G264" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H264" s="2">
         <v>6</v>
@@ -11591,7 +11587,7 @@
         <v>10.5</v>
       </c>
       <c r="K264" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.2">
@@ -11614,7 +11610,7 @@
         <v>24</v>
       </c>
       <c r="G265" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H265" s="2">
         <v>20</v>
@@ -11648,7 +11644,7 @@
         <v>27</v>
       </c>
       <c r="G266" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H266">
         <v>1</v>
@@ -11682,7 +11678,7 @@
         <v>24</v>
       </c>
       <c r="G267" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H267" s="2">
         <v>14</v>
@@ -11747,7 +11743,7 @@
         <v>24</v>
       </c>
       <c r="G269" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H269">
         <v>6</v>
@@ -11818,7 +11814,7 @@
         <v>24</v>
       </c>
       <c r="G271" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H271" s="2">
         <v>13</v>
@@ -11889,7 +11885,7 @@
         <v>23</v>
       </c>
       <c r="G273" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H273">
         <v>1</v>
@@ -11923,7 +11919,7 @@
         <v>25</v>
       </c>
       <c r="G274" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H274" s="2">
         <v>6</v>
@@ -12090,7 +12086,7 @@
         <v>25</v>
       </c>
       <c r="G279" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H279" s="2">
         <v>10</v>
@@ -12124,7 +12120,7 @@
         <v>27</v>
       </c>
       <c r="G280" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H280">
         <v>4</v>
@@ -12192,7 +12188,7 @@
         <v>27</v>
       </c>
       <c r="G282" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H282">
         <v>4</v>
@@ -12223,7 +12219,7 @@
         <v>23</v>
       </c>
       <c r="G283" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H283">
         <v>7</v>
@@ -12285,7 +12281,7 @@
         <v>23</v>
       </c>
       <c r="G285" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H285">
         <v>2</v>
@@ -12333,7 +12329,7 @@
         <v>35</v>
       </c>
       <c r="K286" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
@@ -12353,7 +12349,7 @@
         <v>22</v>
       </c>
       <c r="G287" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H287">
         <v>13</v>
@@ -12387,7 +12383,7 @@
         <v>23</v>
       </c>
       <c r="G288" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H288" s="2">
         <v>6</v>
@@ -12554,7 +12550,7 @@
         <v>24</v>
       </c>
       <c r="G293" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H293" s="2">
         <v>9</v>
@@ -12591,7 +12587,7 @@
         <v>26</v>
       </c>
       <c r="G294" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H294" s="2">
         <v>13</v>
@@ -12628,7 +12624,7 @@
         <v>28</v>
       </c>
       <c r="G295" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H295" s="2">
         <v>13</v>
@@ -12662,7 +12658,7 @@
         <v>22</v>
       </c>
       <c r="G296" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H296">
         <v>7</v>
@@ -12693,7 +12689,7 @@
         <v>22</v>
       </c>
       <c r="G297" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H297">
         <v>7</v>
@@ -12755,7 +12751,7 @@
         <v>22</v>
       </c>
       <c r="G299" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H299">
         <v>9</v>
@@ -12786,7 +12782,7 @@
         <v>19</v>
       </c>
       <c r="G300" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H300">
         <v>1</v>
@@ -12928,7 +12924,7 @@
         <v>28</v>
       </c>
       <c r="G304" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H304">
         <v>5</v>
@@ -12976,7 +12972,7 @@
         <v>29.75</v>
       </c>
       <c r="K305" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.2">
@@ -12999,7 +12995,7 @@
         <v>26</v>
       </c>
       <c r="G306" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H306" s="2">
         <v>15</v>
@@ -13098,7 +13094,7 @@
         <v>23</v>
       </c>
       <c r="G309" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H309" s="2">
         <v>4</v>
@@ -13132,7 +13128,7 @@
         <v>28</v>
       </c>
       <c r="G310" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H310">
         <v>2</v>
@@ -13163,7 +13159,7 @@
         <v>26</v>
       </c>
       <c r="G311" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H311">
         <v>5</v>
@@ -13228,7 +13224,7 @@
         <v>27</v>
       </c>
       <c r="G313" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H313" s="2">
         <v>11</v>
@@ -13242,7 +13238,7 @@
         <v>19.25</v>
       </c>
       <c r="K313" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.2">
@@ -13262,7 +13258,7 @@
         <v>36</v>
       </c>
       <c r="G314" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H314">
         <v>3</v>
@@ -13293,7 +13289,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H315">
         <v>2</v>
@@ -13364,7 +13360,7 @@
         <v>26</v>
       </c>
       <c r="G317" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H317" s="2">
         <v>10</v>
@@ -13438,7 +13434,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H319" s="2">
         <v>13</v>
@@ -13472,7 +13468,7 @@
         <v>25</v>
       </c>
       <c r="G320" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H320">
         <v>1</v>
@@ -13565,7 +13561,7 @@
         <v>22</v>
       </c>
       <c r="G323" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H323">
         <v>5</v>
@@ -13596,7 +13592,7 @@
         <v>26</v>
       </c>
       <c r="G324" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H324">
         <v>5</v>
@@ -13644,7 +13640,7 @@
         <v>28</v>
       </c>
       <c r="K325" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.2">
@@ -13667,7 +13663,7 @@
         <v>26</v>
       </c>
       <c r="G326" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H326" s="2">
         <v>6</v>
@@ -13701,7 +13697,7 @@
         <v>24</v>
       </c>
       <c r="G327" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H327">
         <v>15</v>
@@ -13732,7 +13728,7 @@
         <v>21</v>
       </c>
       <c r="G328" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H328">
         <v>7</v>
@@ -13766,7 +13762,7 @@
         <v>22</v>
       </c>
       <c r="G329" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H329" s="2">
         <v>3</v>
@@ -13780,7 +13776,7 @@
         <v>5.25</v>
       </c>
       <c r="K329" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.2">
@@ -13800,7 +13796,7 @@
         <v>23</v>
       </c>
       <c r="G330" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H330">
         <v>5</v>
@@ -13831,7 +13827,7 @@
         <v>22</v>
       </c>
       <c r="G331" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H331">
         <v>7</v>
@@ -13862,7 +13858,7 @@
         <v>23</v>
       </c>
       <c r="G332" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H332">
         <v>8</v>
@@ -13893,7 +13889,7 @@
         <v>22</v>
       </c>
       <c r="G333" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H333">
         <v>6</v>
@@ -13924,7 +13920,7 @@
         <v>24</v>
       </c>
       <c r="G334" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H334">
         <v>6</v>
@@ -14063,7 +14059,7 @@
         <v>30</v>
       </c>
       <c r="G338" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H338" s="2">
         <v>7</v>
@@ -14134,7 +14130,7 @@
         <v>27</v>
       </c>
       <c r="G340" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H340">
         <v>9</v>
@@ -14227,7 +14223,7 @@
         <v>28</v>
       </c>
       <c r="G343" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H343">
         <v>9</v>
@@ -14258,7 +14254,7 @@
         <v>20</v>
       </c>
       <c r="G344" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H344">
         <v>4</v>
@@ -14289,7 +14285,7 @@
         <v>22</v>
       </c>
       <c r="G345" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H345">
         <v>3</v>
@@ -14337,7 +14333,7 @@
         <v>1.75</v>
       </c>
       <c r="K346" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.2">
@@ -14388,7 +14384,7 @@
         <v>22</v>
       </c>
       <c r="G348" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H348">
         <v>3</v>
@@ -14422,7 +14418,7 @@
         <v>22</v>
       </c>
       <c r="G349" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H349" s="2">
         <v>16</v>
@@ -14586,7 +14582,7 @@
         <v>21</v>
       </c>
       <c r="G354" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H354">
         <v>2</v>
@@ -14634,7 +14630,7 @@
         <v>24.5</v>
       </c>
       <c r="K355" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.2">
@@ -14654,7 +14650,7 @@
         <v>21</v>
       </c>
       <c r="G356" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H356">
         <v>3</v>
@@ -14753,7 +14749,7 @@
         <v>22</v>
       </c>
       <c r="G359" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H359">
         <v>6</v>
@@ -14784,7 +14780,7 @@
         <v>26</v>
       </c>
       <c r="G360" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H360">
         <v>3</v>
@@ -14846,7 +14842,7 @@
         <v>26</v>
       </c>
       <c r="G362" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H362">
         <v>3</v>
@@ -14877,7 +14873,7 @@
         <v>26</v>
       </c>
       <c r="G363" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H363">
         <v>3</v>
@@ -14987,7 +14983,7 @@
         <v>26.25</v>
       </c>
       <c r="K366" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.2">
@@ -15007,7 +15003,7 @@
         <v>23</v>
       </c>
       <c r="G367" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H367">
         <v>4</v>
@@ -15038,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="G368" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H368">
         <v>2</v>
@@ -15069,7 +15065,7 @@
         <v>26</v>
       </c>
       <c r="G369" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H369">
         <v>1</v>
@@ -15100,7 +15096,7 @@
         <v>24</v>
       </c>
       <c r="G370" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H370">
         <v>3</v>
@@ -15255,7 +15251,7 @@
         <v>31</v>
       </c>
       <c r="G375" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H375">
         <v>3</v>
@@ -15317,7 +15313,7 @@
         <v>27</v>
       </c>
       <c r="G377" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H377">
         <v>4</v>
@@ -15348,7 +15344,7 @@
         <v>20</v>
       </c>
       <c r="G378" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H378">
         <v>6</v>
@@ -15379,7 +15375,7 @@
         <v>27</v>
       </c>
       <c r="G379" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H379">
         <v>10</v>
@@ -15413,7 +15409,7 @@
         <v>24</v>
       </c>
       <c r="G380" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H380" s="2">
         <v>8</v>
@@ -15478,7 +15474,7 @@
         <v>21</v>
       </c>
       <c r="G382" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H382">
         <v>9</v>
@@ -15540,7 +15536,7 @@
         <v>25</v>
       </c>
       <c r="G384" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H384">
         <v>1</v>
@@ -15588,7 +15584,7 @@
         <v>17.5</v>
       </c>
       <c r="K385" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.2">
@@ -15611,7 +15607,7 @@
         <v>26</v>
       </c>
       <c r="G386" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H386" s="2">
         <v>9</v>
@@ -15645,7 +15641,7 @@
         <v>29</v>
       </c>
       <c r="G387" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H387">
         <v>8</v>
@@ -15679,7 +15675,7 @@
         <v>24</v>
       </c>
       <c r="G388" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H388" s="2">
         <v>16</v>
@@ -15775,7 +15771,7 @@
         <v>24</v>
       </c>
       <c r="G391" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H391">
         <v>3</v>
@@ -15868,7 +15864,7 @@
         <v>22</v>
       </c>
       <c r="G394" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H394">
         <v>7</v>
@@ -15899,7 +15895,7 @@
         <v>25</v>
       </c>
       <c r="G395" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H395">
         <v>7</v>
@@ -15930,7 +15926,7 @@
         <v>23</v>
       </c>
       <c r="G396" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H396">
         <v>1</v>
@@ -16128,7 +16124,7 @@
         <v>27</v>
       </c>
       <c r="G402" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H402">
         <v>3</v>
@@ -16221,7 +16217,7 @@
         <v>24</v>
       </c>
       <c r="G405" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H405">
         <v>8</v>
@@ -16317,7 +16313,7 @@
         <v>23</v>
       </c>
       <c r="G408" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H408" s="2">
         <v>11</v>
@@ -16351,7 +16347,7 @@
         <v>23</v>
       </c>
       <c r="G409" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H409">
         <v>4</v>
@@ -16422,7 +16418,7 @@
         <v>20</v>
       </c>
       <c r="G411" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H411" s="2">
         <v>10</v>
@@ -16487,7 +16483,7 @@
         <v>19</v>
       </c>
       <c r="G413" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H413">
         <v>2</v>
@@ -16580,7 +16576,7 @@
         <v>23</v>
       </c>
       <c r="G416" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H416">
         <v>3</v>
@@ -16611,7 +16607,7 @@
         <v>20</v>
       </c>
       <c r="G417" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H417">
         <v>5</v>
@@ -16673,7 +16669,7 @@
         <v>21</v>
       </c>
       <c r="G419" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H419">
         <v>2</v>
@@ -16704,7 +16700,7 @@
         <v>25</v>
       </c>
       <c r="G420" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H420">
         <v>1</v>
@@ -16735,7 +16731,7 @@
         <v>24</v>
       </c>
       <c r="G421" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H421">
         <v>7</v>
@@ -16766,7 +16762,7 @@
         <v>29</v>
       </c>
       <c r="G422" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H422">
         <v>8</v>
@@ -16967,7 +16963,7 @@
         <v>24</v>
       </c>
       <c r="G428" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H428" s="2">
         <v>4</v>
@@ -17001,7 +16997,7 @@
         <v>21</v>
       </c>
       <c r="G429" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H429">
         <v>5</v>
@@ -17032,7 +17028,7 @@
         <v>19</v>
       </c>
       <c r="G430" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H430">
         <v>1</v>
@@ -17094,7 +17090,7 @@
         <v>24</v>
       </c>
       <c r="G432" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H432">
         <v>6</v>
@@ -17230,7 +17226,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H436">
         <v>1</v>
@@ -17323,7 +17319,7 @@
         <v>22</v>
       </c>
       <c r="G439" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H439">
         <v>1</v>
@@ -17354,7 +17350,7 @@
         <v>27</v>
       </c>
       <c r="G440" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H440">
         <v>7</v>
@@ -17676,7 +17672,7 @@
         <v>23</v>
       </c>
       <c r="G450" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H450">
         <v>1</v>
@@ -17834,7 +17830,7 @@
         <v>26</v>
       </c>
       <c r="G455" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H455" s="2">
         <v>9</v>
@@ -17868,7 +17864,7 @@
         <v>26</v>
       </c>
       <c r="G456" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H456">
         <v>4</v>
@@ -17916,7 +17912,7 @@
         <v>26.25</v>
       </c>
       <c r="K457" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.2">
@@ -18066,7 +18062,7 @@
         <v>24</v>
       </c>
       <c r="G462" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H462">
         <v>2</v>
@@ -18097,7 +18093,7 @@
         <v>19</v>
       </c>
       <c r="G463" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H463">
         <v>1</v>
@@ -18128,7 +18124,7 @@
         <v>18</v>
       </c>
       <c r="G464" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H464">
         <v>1</v>
@@ -18159,7 +18155,7 @@
         <v>30</v>
       </c>
       <c r="G465" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H465">
         <v>9</v>
@@ -18193,7 +18189,7 @@
         <v>25</v>
       </c>
       <c r="G466" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H466" s="2">
         <v>14</v>
@@ -18230,7 +18226,7 @@
         <v>23</v>
       </c>
       <c r="G467" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H467" s="2">
         <v>18</v>
@@ -18264,7 +18260,7 @@
         <v>24</v>
       </c>
       <c r="G468" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H468">
         <v>2</v>
@@ -18298,7 +18294,7 @@
         <v>27</v>
       </c>
       <c r="G469" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H469" s="2">
         <v>11</v>
@@ -18312,7 +18308,7 @@
         <v>19.25</v>
       </c>
       <c r="K469" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.2">
@@ -18332,7 +18328,7 @@
         <v>22</v>
       </c>
       <c r="G470" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H470">
         <v>4</v>
@@ -18363,7 +18359,7 @@
         <v>21</v>
       </c>
       <c r="G471" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H471">
         <v>1</v>
@@ -18394,7 +18390,7 @@
         <v>23</v>
       </c>
       <c r="G472" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H472">
         <v>2</v>
@@ -18490,7 +18486,7 @@
         <v>21</v>
       </c>
       <c r="G475" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H475" s="2">
         <v>7</v>
@@ -18555,7 +18551,7 @@
         <v>23</v>
       </c>
       <c r="G477" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H477">
         <v>2</v>
@@ -18617,7 +18613,7 @@
         <v>21</v>
       </c>
       <c r="G479" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H479">
         <v>1</v>
@@ -18682,7 +18678,7 @@
         <v>28</v>
       </c>
       <c r="G481" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H481" s="2">
         <v>10</v>
@@ -18696,7 +18692,7 @@
         <v>17.5</v>
       </c>
       <c r="K481" t="s">
-        <v>716</v>
+        <v>13</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.2">
@@ -18818,7 +18814,7 @@
         <v>22</v>
       </c>
       <c r="G485" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H485" s="2">
         <v>15</v>
@@ -18832,7 +18828,7 @@
         <v>26.25</v>
       </c>
       <c r="K485" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.2">
@@ -18852,7 +18848,7 @@
         <v>21</v>
       </c>
       <c r="G486" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H486">
         <v>10</v>
@@ -18900,7 +18896,7 @@
         <v>17.5</v>
       </c>
       <c r="K487" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.2">
@@ -18985,7 +18981,7 @@
         <v>21</v>
       </c>
       <c r="G490" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H490" s="2">
         <v>26</v>
@@ -19053,7 +19049,7 @@
         <v>23</v>
       </c>
       <c r="G492" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H492" s="2">
         <v>18</v>
@@ -19087,7 +19083,7 @@
         <v>26</v>
       </c>
       <c r="G493" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H493">
         <v>1</v>
@@ -19149,7 +19145,7 @@
         <v>24</v>
       </c>
       <c r="G495" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H495">
         <v>2</v>
@@ -19248,7 +19244,7 @@
         <v>22</v>
       </c>
       <c r="G498" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H498">
         <v>3</v>
@@ -19279,7 +19275,7 @@
         <v>23</v>
       </c>
       <c r="G499" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H499">
         <v>5</v>
@@ -19313,7 +19309,7 @@
         <v>23</v>
       </c>
       <c r="G500" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H500" s="2">
         <v>11</v>
@@ -19395,7 +19391,7 @@
         <v>35</v>
       </c>
       <c r="K502" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.2">
@@ -19418,7 +19414,7 @@
         <v>17</v>
       </c>
       <c r="G503" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H503" s="2">
         <v>4</v>
@@ -19452,7 +19448,7 @@
         <v>24</v>
       </c>
       <c r="G504" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H504">
         <v>5</v>
@@ -19514,7 +19510,7 @@
         <v>19</v>
       </c>
       <c r="G506" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H506">
         <v>2</v>
@@ -19562,7 +19558,7 @@
         <v>24.5</v>
       </c>
       <c r="K507" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.2">
@@ -19613,7 +19609,7 @@
         <v>22</v>
       </c>
       <c r="G509" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H509">
         <v>2</v>
@@ -19684,7 +19680,7 @@
         <v>20</v>
       </c>
       <c r="G511" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H511" s="2">
         <v>12</v>
@@ -19814,7 +19810,7 @@
         <v>23</v>
       </c>
       <c r="G515" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H515" s="2">
         <v>3</v>
@@ -19848,7 +19844,7 @@
         <v>27</v>
       </c>
       <c r="G516" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H516">
         <v>1</v>
@@ -19882,7 +19878,7 @@
         <v>22</v>
       </c>
       <c r="G517" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H517" s="2">
         <v>14</v>
@@ -19896,7 +19892,7 @@
         <v>24.5</v>
       </c>
       <c r="K517" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.2">
@@ -19947,7 +19943,7 @@
         <v>23</v>
       </c>
       <c r="G519" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H519">
         <v>5</v>
@@ -20009,7 +20005,7 @@
         <v>22</v>
       </c>
       <c r="G521" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H521">
         <v>4</v>
@@ -20040,7 +20036,7 @@
         <v>25</v>
       </c>
       <c r="G522" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H522">
         <v>7</v>
@@ -20108,7 +20104,7 @@
         <v>29</v>
       </c>
       <c r="G524" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H524">
         <v>2</v>
@@ -20207,7 +20203,7 @@
         <v>25</v>
       </c>
       <c r="G527" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H527">
         <v>6</v>
@@ -20374,7 +20370,7 @@
         <v>20</v>
       </c>
       <c r="G532" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H532">
         <v>1</v>
@@ -20467,7 +20463,7 @@
         <v>18</v>
       </c>
       <c r="G535" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H535">
         <v>2</v>
@@ -20702,7 +20698,7 @@
         <v>20</v>
       </c>
       <c r="G542" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H542">
         <v>5</v>
@@ -20773,7 +20769,7 @@
         <v>20</v>
       </c>
       <c r="G544" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H544" s="2">
         <v>6</v>
@@ -20807,7 +20803,7 @@
         <v>25</v>
       </c>
       <c r="G545" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H545">
         <v>5</v>
@@ -20841,7 +20837,7 @@
         <v>20</v>
       </c>
       <c r="G546" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H546" s="2">
         <v>15</v>
@@ -20906,7 +20902,7 @@
         <v>22</v>
       </c>
       <c r="G548" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H548">
         <v>5</v>
@@ -20937,7 +20933,7 @@
         <v>26</v>
       </c>
       <c r="G549" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H549">
         <v>2</v>
@@ -20971,7 +20967,7 @@
         <v>29</v>
       </c>
       <c r="G550" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H550" s="2">
         <v>11</v>
@@ -21036,7 +21032,7 @@
         <v>32</v>
       </c>
       <c r="G552" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H552">
         <v>1</v>
@@ -21067,7 +21063,7 @@
         <v>22</v>
       </c>
       <c r="G553" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H553">
         <v>1</v>
@@ -21098,7 +21094,7 @@
         <v>21</v>
       </c>
       <c r="G554" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H554">
         <v>6</v>
@@ -21191,7 +21187,7 @@
         <v>29</v>
       </c>
       <c r="G557" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H557">
         <v>2</v>
@@ -21222,7 +21218,7 @@
         <v>23</v>
       </c>
       <c r="G558" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H558">
         <v>1</v>
@@ -21256,7 +21252,7 @@
         <v>22</v>
       </c>
       <c r="G559" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H559" s="2">
         <v>9</v>
@@ -21290,7 +21286,7 @@
         <v>24</v>
       </c>
       <c r="G560" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H560">
         <v>4</v>
@@ -21321,7 +21317,7 @@
         <v>27</v>
       </c>
       <c r="G561" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H561">
         <v>5</v>
@@ -21352,7 +21348,7 @@
         <v>24</v>
       </c>
       <c r="G562" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H562">
         <v>3</v>
@@ -21383,7 +21379,7 @@
         <v>27</v>
       </c>
       <c r="G563" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H563">
         <v>2</v>
@@ -21445,7 +21441,7 @@
         <v>25</v>
       </c>
       <c r="G565" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H565">
         <v>1</v>
@@ -21600,7 +21596,7 @@
         <v>22</v>
       </c>
       <c r="G570" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H570">
         <v>1</v>
@@ -21786,7 +21782,7 @@
         <v>20</v>
       </c>
       <c r="G576" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H576">
         <v>1</v>
@@ -21817,7 +21813,7 @@
         <v>19</v>
       </c>
       <c r="G577" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H577">
         <v>1</v>
@@ -21989,7 +21985,7 @@
         <v>10.5</v>
       </c>
       <c r="K582" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.2">
@@ -22108,7 +22104,7 @@
         <v>26</v>
       </c>
       <c r="G586" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H586">
         <v>1</v>
@@ -22368,7 +22364,7 @@
         <v>19</v>
       </c>
       <c r="G594" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H594">
         <v>6</v>
@@ -22430,7 +22426,7 @@
         <v>21</v>
       </c>
       <c r="G596" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H596">
         <v>11</v>
@@ -22464,7 +22460,7 @@
         <v>26</v>
       </c>
       <c r="G597" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H597" s="2">
         <v>4</v>
@@ -22566,7 +22562,7 @@
         <v>23</v>
       </c>
       <c r="G600" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H600">
         <v>10</v>
@@ -22597,7 +22593,7 @@
         <v>19</v>
       </c>
       <c r="G601" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H601">
         <v>2</v>
@@ -22631,7 +22627,7 @@
         <v>22</v>
       </c>
       <c r="G602" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H602" s="2">
         <v>8</v>
@@ -22746,7 +22742,7 @@
         <v>7239</v>
       </c>
       <c r="B606" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D606" t="s">
         <v>9</v>
@@ -22851,7 +22847,7 @@
         <v>20</v>
       </c>
       <c r="G609" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H609">
         <v>2</v>
@@ -23012,7 +23008,7 @@
         <v>19</v>
       </c>
       <c r="G614" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H614">
         <v>4</v>
@@ -23167,7 +23163,7 @@
         <v>20</v>
       </c>
       <c r="G619" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H619">
         <v>4</v>
@@ -23452,7 +23448,7 @@
         <v>20</v>
       </c>
       <c r="G628" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H628">
         <v>2</v>
@@ -23517,7 +23513,7 @@
         <v>23</v>
       </c>
       <c r="G630" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H630" s="2">
         <v>14</v>
@@ -23613,7 +23609,7 @@
         <v>25</v>
       </c>
       <c r="G633" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H633">
         <v>9</v>
@@ -23644,7 +23640,7 @@
         <v>22</v>
       </c>
       <c r="G634" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H634">
         <v>1</v>
@@ -23675,7 +23671,7 @@
         <v>21</v>
       </c>
       <c r="G635" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H635">
         <v>5</v>
@@ -23737,7 +23733,7 @@
         <v>20</v>
       </c>
       <c r="G637" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H637">
         <v>2</v>
@@ -23768,7 +23764,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H638">
         <v>10</v>
@@ -23799,7 +23795,7 @@
         <v>25</v>
       </c>
       <c r="G639" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H639">
         <v>6</v>
@@ -23985,7 +23981,7 @@
         <v>20</v>
       </c>
       <c r="G645" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H645">
         <v>5</v>
@@ -24078,7 +24074,7 @@
         <v>18</v>
       </c>
       <c r="G648" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H648">
         <v>1</v>
@@ -24109,7 +24105,7 @@
         <v>19</v>
       </c>
       <c r="G649" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H649">
         <v>1</v>
@@ -24205,7 +24201,7 @@
         <v>23</v>
       </c>
       <c r="G652" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H652" s="2">
         <v>12</v>
@@ -24338,7 +24334,7 @@
         <v>18</v>
       </c>
       <c r="G656" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H656">
         <v>1</v>
@@ -24388,7 +24384,7 @@
         <v>7368</v>
       </c>
       <c r="B658" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -24419,7 +24415,7 @@
         <v>7374</v>
       </c>
       <c r="B659" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D659" t="s">
         <v>9</v>
@@ -24450,7 +24446,7 @@
         <v>7377</v>
       </c>
       <c r="B660" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D660" t="s">
         <v>9</v>
@@ -24462,7 +24458,7 @@
         <v>19</v>
       </c>
       <c r="G660" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H660">
         <v>2</v>
@@ -24481,7 +24477,7 @@
         <v>7381</v>
       </c>
       <c r="B661" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D661" t="s">
         <v>9</v>
@@ -24512,7 +24508,7 @@
         <v>7382</v>
       </c>
       <c r="B662" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D662" t="s">
         <v>9</v>
@@ -24543,7 +24539,7 @@
         <v>7383</v>
       </c>
       <c r="B663" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D663" t="s">
         <v>9</v>
@@ -24574,7 +24570,7 @@
         <v>7388</v>
       </c>
       <c r="B664" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D664" t="s">
         <v>9</v>

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92033CD2-E867-F548-BF6E-54A17FA6D562}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE368F77-8ABE-EB45-A928-ACACC25E12FB}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="660" windowWidth="24680" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6393,7 +6393,7 @@
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F100">
         <v>21</v>
@@ -23900,7 +23900,7 @@
         <v>10</v>
       </c>
       <c r="I642" s="2">
-        <f t="shared" ref="I642:I705" si="20">H642/5</f>
+        <f t="shared" ref="I642:I664" si="20">H642/5</f>
         <v>2</v>
       </c>
       <c r="J642" s="2">

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE368F77-8ABE-EB45-A928-ACACC25E12FB}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E419F5-11FE-504D-BA2F-5BCA70FB8BDC}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="660" windowWidth="24680" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D692AF2E-C56B-6244-B2F8-25693B91DA3D}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DDB59B2-2DB9-B140-95BB-EF34855B50A9}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista calciatori" sheetId="1" r:id="rId1"/>
@@ -3211,15 +3211,15 @@
         <v>723</v>
       </c>
       <c r="H5" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
@@ -3347,15 +3347,15 @@
         <v>11</v>
       </c>
       <c r="H9" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>31.5</v>
       </c>
       <c r="K9" t="s">
         <v>30</v>
@@ -3486,15 +3486,15 @@
         <v>729</v>
       </c>
       <c r="H13" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="2">
         <f t="shared" si="1"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K13" t="s">
         <v>30</v>
@@ -3554,15 +3554,15 @@
         <v>723</v>
       </c>
       <c r="H15" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2">
         <f t="shared" si="0"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" s="2">
         <f t="shared" si="1"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K15" t="s">
         <v>30</v>
@@ -3656,15 +3656,15 @@
         <v>730</v>
       </c>
       <c r="H18" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="2">
         <f t="shared" si="1"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K18" t="s">
         <v>30</v>
@@ -3761,15 +3761,15 @@
         <v>727</v>
       </c>
       <c r="H21" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" s="2">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J21" s="2">
         <f t="shared" si="1"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K21" t="s">
         <v>30</v>
@@ -3795,15 +3795,15 @@
         <v>11</v>
       </c>
       <c r="H22" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="2">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J22" s="2">
         <f t="shared" si="1"/>
-        <v>31.5</v>
+        <v>29.75</v>
       </c>
       <c r="K22" t="s">
         <v>30</v>
@@ -3863,15 +3863,15 @@
         <v>58</v>
       </c>
       <c r="H24" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I24" s="2">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J24" s="2">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>31.5</v>
       </c>
       <c r="K24" t="s">
         <v>30</v>
@@ -4005,15 +4005,15 @@
         <v>723</v>
       </c>
       <c r="H28" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="2">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" s="2">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -4073,15 +4073,15 @@
         <v>731</v>
       </c>
       <c r="H30" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I30" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="J30" s="2">
         <f t="shared" si="1"/>
-        <v>43.75</v>
+        <v>40.25</v>
       </c>
       <c r="K30" t="s">
         <v>28</v>
@@ -4107,15 +4107,15 @@
         <v>723</v>
       </c>
       <c r="H31" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="2">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J31" s="2">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="K31" t="s">
         <v>28</v>
@@ -4141,15 +4141,15 @@
         <v>731</v>
       </c>
       <c r="H32" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I32" s="2">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J32" s="2">
         <f t="shared" si="1"/>
-        <v>31.5</v>
+        <v>29.75</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -4280,15 +4280,15 @@
         <v>10</v>
       </c>
       <c r="H36" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2">
         <f t="shared" si="0"/>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J36" s="2">
         <f t="shared" si="1"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
@@ -4348,15 +4348,15 @@
         <v>731</v>
       </c>
       <c r="H38" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J38" s="2">
         <f t="shared" si="1"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -4416,15 +4416,15 @@
         <v>82</v>
       </c>
       <c r="H40" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40" s="2">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K40" t="s">
         <v>28</v>
@@ -4450,15 +4450,15 @@
         <v>723</v>
       </c>
       <c r="H41" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J41" s="2">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
@@ -4518,15 +4518,15 @@
         <v>58</v>
       </c>
       <c r="H43" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I43" s="2">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J43" s="2">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
@@ -4552,15 +4552,15 @@
         <v>10</v>
       </c>
       <c r="H44" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I44" s="2">
         <f t="shared" si="0"/>
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J44" s="2">
         <f t="shared" si="1"/>
-        <v>29.75</v>
+        <v>31.5</v>
       </c>
       <c r="K44" t="s">
         <v>28</v>
@@ -4623,15 +4623,15 @@
         <v>723</v>
       </c>
       <c r="H46" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="K46" t="s">
         <v>28</v>
@@ -4827,15 +4827,15 @@
         <v>11</v>
       </c>
       <c r="H52" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I52" s="2">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K52" t="s">
         <v>28</v>
@@ -4963,15 +4963,15 @@
         <v>10</v>
       </c>
       <c r="H56" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J56" s="2">
         <f t="shared" si="1"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="K56" t="s">
         <v>64</v>
@@ -5031,15 +5031,15 @@
         <v>727</v>
       </c>
       <c r="H58" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I58" s="2">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J58" s="2">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="K58" t="s">
         <v>64</v>
@@ -5167,15 +5167,15 @@
         <v>727</v>
       </c>
       <c r="H62" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="2">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J62" s="2">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="K62" t="s">
         <v>64</v>
@@ -5340,15 +5340,15 @@
         <v>727</v>
       </c>
       <c r="H67" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I67" s="2">
         <f t="shared" si="2"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J67" s="2">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K67" t="s">
         <v>64</v>
@@ -5445,15 +5445,15 @@
         <v>735</v>
       </c>
       <c r="H70" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I70" s="2">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="K70" t="s">
         <v>64</v>
@@ -5550,15 +5550,15 @@
         <v>11</v>
       </c>
       <c r="H73" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I73" s="2">
         <f t="shared" si="2"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J73" s="2">
         <f t="shared" si="3"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K73" t="s">
         <v>64</v>
@@ -5584,15 +5584,15 @@
         <v>723</v>
       </c>
       <c r="H74" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I74" s="2">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J74" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K74" t="s">
         <v>64</v>
@@ -5618,15 +5618,15 @@
         <v>82</v>
       </c>
       <c r="H75" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I75" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J75" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K75" t="s">
         <v>64</v>
@@ -5652,15 +5652,15 @@
         <v>723</v>
       </c>
       <c r="H76" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I76" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J76" s="2">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K76" t="s">
         <v>64</v>
@@ -5720,15 +5720,15 @@
         <v>730</v>
       </c>
       <c r="H78" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I78" s="2">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J78" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K78" t="s">
         <v>64</v>
@@ -5754,15 +5754,15 @@
         <v>10</v>
       </c>
       <c r="H79" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I79" s="2">
         <f t="shared" si="2"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2">
         <f t="shared" si="3"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K79" t="s">
         <v>64</v>
@@ -5788,15 +5788,15 @@
         <v>724</v>
       </c>
       <c r="H80" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I80" s="2">
         <f t="shared" si="2"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J80" s="2">
         <f t="shared" si="3"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="K80" t="s">
         <v>64</v>
@@ -5822,15 +5822,15 @@
         <v>14</v>
       </c>
       <c r="H81" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I81" s="2">
         <f t="shared" si="2"/>
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J81" s="2">
         <f t="shared" si="3"/>
-        <v>29.75</v>
+        <v>28</v>
       </c>
       <c r="K81" t="s">
         <v>64</v>
@@ -5856,15 +5856,15 @@
         <v>11</v>
       </c>
       <c r="H82" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I82" s="2">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J82" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K82" t="s">
         <v>64</v>
@@ -6233,15 +6233,15 @@
         <v>723</v>
       </c>
       <c r="H93" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I93" s="2">
         <f t="shared" si="2"/>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J93" s="2">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="K93" t="s">
         <v>18</v>
@@ -6480,15 +6480,15 @@
         <v>11</v>
       </c>
       <c r="H100" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I100" s="2">
         <f t="shared" si="2"/>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J100" s="2">
         <f t="shared" si="3"/>
-        <v>24.5</v>
+        <v>22.75</v>
       </c>
       <c r="K100" t="s">
         <v>18</v>
@@ -6582,15 +6582,15 @@
         <v>731</v>
       </c>
       <c r="H103" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I103" s="2">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J103" s="2">
         <f t="shared" si="3"/>
-        <v>52.5</v>
+        <v>49</v>
       </c>
       <c r="K103" t="s">
         <v>18</v>
@@ -6616,15 +6616,15 @@
         <v>723</v>
       </c>
       <c r="H104" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I104" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J104" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K104" t="s">
         <v>18</v>
@@ -6684,15 +6684,15 @@
         <v>727</v>
       </c>
       <c r="H106" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I106" s="2">
         <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="J106" s="2">
         <f t="shared" si="3"/>
-        <v>19.25</v>
+        <v>21</v>
       </c>
       <c r="K106" t="s">
         <v>18</v>
@@ -6820,15 +6820,15 @@
         <v>735</v>
       </c>
       <c r="H110" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I110" s="2">
         <f t="shared" si="2"/>
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J110" s="2">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>52.5</v>
       </c>
       <c r="K110" t="s">
         <v>15</v>
@@ -6888,15 +6888,15 @@
         <v>727</v>
       </c>
       <c r="H112" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I112" s="2">
         <f t="shared" si="2"/>
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J112" s="2">
         <f t="shared" si="3"/>
-        <v>45.5</v>
+        <v>43.75</v>
       </c>
       <c r="K112" t="s">
         <v>15</v>
@@ -6922,15 +6922,15 @@
         <v>11</v>
       </c>
       <c r="H113" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I113" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J113" s="2">
         <f t="shared" si="3"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K113" t="s">
         <v>15</v>
@@ -7024,15 +7024,15 @@
         <v>10</v>
       </c>
       <c r="H116" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I116" s="2">
         <f t="shared" si="2"/>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J116" s="2">
         <f t="shared" si="3"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K116" t="s">
         <v>15</v>
@@ -7194,15 +7194,15 @@
         <v>724</v>
       </c>
       <c r="H121" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I121" s="2">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J121" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K121" t="s">
         <v>15</v>
@@ -7262,15 +7262,15 @@
         <v>726</v>
       </c>
       <c r="H123" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I123" s="2">
         <f t="shared" si="2"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J123" s="2">
         <f t="shared" si="3"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="K123" t="s">
         <v>15</v>
@@ -7296,15 +7296,15 @@
         <v>10</v>
       </c>
       <c r="H124" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I124" s="2">
         <f t="shared" si="2"/>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="J124" s="2">
         <f t="shared" si="3"/>
-        <v>40.25</v>
+        <v>42</v>
       </c>
       <c r="K124" t="s">
         <v>15</v>
@@ -7435,15 +7435,15 @@
         <v>727</v>
       </c>
       <c r="H128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I128" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J128" s="2">
         <f t="shared" si="3"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K128" t="s">
         <v>15</v>
@@ -7540,15 +7540,15 @@
         <v>729</v>
       </c>
       <c r="H131" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I131" s="2">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J131" s="2">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="K131" t="s">
         <v>15</v>
@@ -7682,15 +7682,15 @@
         <v>82</v>
       </c>
       <c r="H135" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I135" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J135" s="2">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
       <c r="K135" t="s">
         <v>25</v>
@@ -7892,15 +7892,15 @@
         <v>723</v>
       </c>
       <c r="H141" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I141" s="2">
         <f t="shared" si="4"/>
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J141" s="2">
         <f t="shared" si="5"/>
-        <v>47.25</v>
+        <v>49</v>
       </c>
       <c r="K141" t="s">
         <v>25</v>
@@ -7926,15 +7926,15 @@
         <v>58</v>
       </c>
       <c r="H142" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I142" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J142" s="2">
         <f t="shared" si="5"/>
-        <v>26.25</v>
+        <v>24.5</v>
       </c>
       <c r="K142" t="s">
         <v>25</v>
@@ -8031,15 +8031,15 @@
         <v>733</v>
       </c>
       <c r="H145" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I145" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J145" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K145" t="s">
         <v>25</v>
@@ -8099,15 +8099,15 @@
         <v>729</v>
       </c>
       <c r="H147" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I147" s="2">
         <f t="shared" si="4"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J147" s="2">
         <f t="shared" si="5"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K147" t="s">
         <v>25</v>
@@ -8133,15 +8133,15 @@
         <v>731</v>
       </c>
       <c r="H148" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I148" s="2">
         <f t="shared" si="4"/>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J148" s="2">
         <f t="shared" si="5"/>
-        <v>22.75</v>
+        <v>21</v>
       </c>
       <c r="K148" t="s">
         <v>25</v>
@@ -8306,15 +8306,15 @@
         <v>727</v>
       </c>
       <c r="H153" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I153" s="2">
         <f t="shared" si="4"/>
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J153" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K153" t="s">
         <v>25</v>
@@ -8442,15 +8442,15 @@
         <v>727</v>
       </c>
       <c r="H157" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I157" s="2">
         <f t="shared" si="4"/>
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J157" s="2">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="K157" t="s">
         <v>25</v>
@@ -8618,15 +8618,15 @@
         <v>10</v>
       </c>
       <c r="H162" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I162" s="2">
         <f t="shared" si="4"/>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J162" s="2">
         <f t="shared" si="5"/>
-        <v>31.5</v>
+        <v>33.25</v>
       </c>
       <c r="K162" t="s">
         <v>12</v>
@@ -8794,15 +8794,15 @@
         <v>58</v>
       </c>
       <c r="H167" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I167" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J167" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K167" t="s">
         <v>12</v>
@@ -8828,15 +8828,15 @@
         <v>723</v>
       </c>
       <c r="H168" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I168" s="2">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J168" s="2">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
       <c r="K168" t="s">
         <v>12</v>
@@ -8896,15 +8896,15 @@
         <v>723</v>
       </c>
       <c r="H170" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I170" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J170" s="2">
         <f t="shared" si="5"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K170" t="s">
         <v>12</v>
@@ -8964,15 +8964,15 @@
         <v>735</v>
       </c>
       <c r="H172" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I172" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J172" s="2">
         <f t="shared" si="5"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
       <c r="K172" t="s">
         <v>12</v>
@@ -9032,15 +9032,15 @@
         <v>725</v>
       </c>
       <c r="H174" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I174" s="2">
         <f t="shared" si="4"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J174" s="2">
         <f t="shared" si="5"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K174" t="s">
         <v>12</v>
@@ -9168,15 +9168,15 @@
         <v>730</v>
       </c>
       <c r="H178" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I178" s="2">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J178" s="2">
         <f t="shared" si="5"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="K178" t="s">
         <v>12</v>
@@ -9338,15 +9338,15 @@
         <v>11</v>
       </c>
       <c r="H183" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I183" s="2">
         <f t="shared" si="4"/>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J183" s="2">
         <f t="shared" si="5"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K183" t="s">
         <v>12</v>
@@ -9406,15 +9406,15 @@
         <v>727</v>
       </c>
       <c r="H185" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I185" s="2">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J185" s="2">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
       <c r="K185" t="s">
         <v>12</v>
@@ -9474,15 +9474,15 @@
         <v>727</v>
       </c>
       <c r="H187" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I187" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J187" s="2">
         <f t="shared" si="5"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="K187" t="s">
         <v>12</v>
@@ -9508,15 +9508,15 @@
         <v>727</v>
       </c>
       <c r="H188" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I188" s="2">
         <f t="shared" si="4"/>
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J188" s="2">
         <f t="shared" si="5"/>
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="K188" t="s">
         <v>12</v>
@@ -9542,15 +9542,15 @@
         <v>723</v>
       </c>
       <c r="H189" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I189" s="2">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J189" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="K189" t="s">
         <v>739</v>
@@ -9681,15 +9681,15 @@
         <v>11</v>
       </c>
       <c r="H193" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I193" s="2">
         <f t="shared" si="4"/>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J193" s="2">
         <f t="shared" si="5"/>
-        <v>22.75</v>
+        <v>21</v>
       </c>
       <c r="K193" t="s">
         <v>739</v>
@@ -9851,15 +9851,15 @@
         <v>10</v>
       </c>
       <c r="H198" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I198" s="2">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J198" s="2">
         <f t="shared" si="7"/>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K198" t="s">
         <v>739</v>
@@ -10024,15 +10024,15 @@
         <v>10</v>
       </c>
       <c r="H203" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I203" s="2">
         <f t="shared" si="6"/>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J203" s="2">
         <f t="shared" si="7"/>
-        <v>31.5</v>
+        <v>33.25</v>
       </c>
       <c r="K203" t="s">
         <v>739</v>
@@ -10126,15 +10126,15 @@
         <v>10</v>
       </c>
       <c r="H206" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I206" s="2">
         <f t="shared" si="6"/>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J206" s="2">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="K206" t="s">
         <v>739</v>
@@ -10367,15 +10367,15 @@
         <v>729</v>
       </c>
       <c r="H213" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I213" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J213" s="2">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K213" t="s">
         <v>739</v>
@@ -10435,15 +10435,15 @@
         <v>733</v>
       </c>
       <c r="H215" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I215" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J215" s="2">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K215" t="s">
         <v>739</v>
@@ -10832,15 +10832,15 @@
         <v>11</v>
       </c>
       <c r="H228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I228" s="2">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J228" s="2">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.2">
@@ -10919,15 +10919,15 @@
         <v>723</v>
       </c>
       <c r="H231">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I231" s="2">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J231" s="2">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.2">
@@ -11248,15 +11248,15 @@
         <v>11</v>
       </c>
       <c r="H242">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I242" s="2">
         <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J242" s="2">
         <f t="shared" si="7"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.2">
@@ -11819,15 +11819,15 @@
         <v>11</v>
       </c>
       <c r="H261">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I261" s="2">
         <f t="shared" si="8"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J261" s="2">
         <f t="shared" si="9"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.2">
@@ -12272,15 +12272,15 @@
         <v>723</v>
       </c>
       <c r="H276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I276" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J276" s="2">
         <f t="shared" si="9"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.2">
@@ -12750,15 +12750,15 @@
         <v>730</v>
       </c>
       <c r="H292">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I292" s="2">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J292" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.2">
@@ -12927,15 +12927,15 @@
         <v>723</v>
       </c>
       <c r="H298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I298" s="2">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J298" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.2">
@@ -12955,15 +12955,15 @@
         <v>11</v>
       </c>
       <c r="H299">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I299" s="2">
         <f t="shared" si="8"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J299" s="2">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.2">
@@ -13011,15 +13011,15 @@
         <v>723</v>
       </c>
       <c r="H301">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I301" s="2">
         <f t="shared" si="8"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J301" s="2">
         <f t="shared" si="9"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.2">
@@ -13129,15 +13129,15 @@
         <v>723</v>
       </c>
       <c r="H305">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I305" s="2">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J305" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.2">
@@ -13371,15 +13371,15 @@
         <v>82</v>
       </c>
       <c r="H313">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I313" s="2">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J313" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.2">
@@ -13427,15 +13427,15 @@
         <v>723</v>
       </c>
       <c r="H315">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I315" s="2">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J315" s="2">
         <f t="shared" si="9"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.2">
@@ -13545,15 +13545,15 @@
         <v>11</v>
       </c>
       <c r="H319">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I319" s="2">
         <f t="shared" si="8"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J319" s="2">
         <f t="shared" si="9"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.2">
@@ -14076,15 +14076,15 @@
         <v>723</v>
       </c>
       <c r="H337">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I337" s="2">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J337" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.2">
@@ -14669,15 +14669,15 @@
         <v>727</v>
       </c>
       <c r="H357">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I357" s="2">
         <f t="shared" si="10"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J357" s="2">
         <f t="shared" si="11"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.2">
@@ -14697,15 +14697,15 @@
         <v>723</v>
       </c>
       <c r="H358">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I358" s="2">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J358" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.2">
@@ -15091,15 +15091,15 @@
         <v>10</v>
       </c>
       <c r="H371">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I371" s="2">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J371" s="2">
         <f t="shared" si="11"/>
-        <v>17.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.2">
@@ -15119,15 +15119,15 @@
         <v>723</v>
       </c>
       <c r="H372">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I372" s="2">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J372" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.2">
@@ -15324,15 +15324,15 @@
         <v>82</v>
       </c>
       <c r="H379">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I379" s="2">
         <f t="shared" si="10"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J379" s="2">
         <f t="shared" si="11"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.2">
@@ -15473,15 +15473,15 @@
         <v>852</v>
       </c>
       <c r="H384">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I384" s="2">
         <f t="shared" si="10"/>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J384" s="2">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.2">
@@ -15501,15 +15501,15 @@
         <v>58</v>
       </c>
       <c r="H385">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I385" s="2">
         <f t="shared" si="10"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J385" s="2">
         <f t="shared" si="11"/>
-        <v>19.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.2">
@@ -15560,15 +15560,15 @@
         <v>724</v>
       </c>
       <c r="H387">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I387" s="2">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J387" s="2">
         <f t="shared" si="13"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.2">
@@ -15681,15 +15681,15 @@
         <v>723</v>
       </c>
       <c r="H391">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I391" s="2">
         <f t="shared" si="12"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J391" s="2">
         <f t="shared" si="13"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.2">
@@ -15979,15 +15979,15 @@
         <v>723</v>
       </c>
       <c r="H401">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I401" s="2">
         <f t="shared" si="12"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J401" s="2">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.2">
@@ -16066,15 +16066,15 @@
         <v>853</v>
       </c>
       <c r="H404">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I404" s="2">
         <f t="shared" si="12"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J404" s="2">
         <f t="shared" si="13"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.2">
@@ -16240,15 +16240,15 @@
         <v>10</v>
       </c>
       <c r="H410">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I410" s="2">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J410" s="2">
         <f t="shared" si="13"/>
-        <v>26.25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.2">
@@ -16479,15 +16479,15 @@
         <v>723</v>
       </c>
       <c r="H418">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I418" s="2">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J418" s="2">
         <f t="shared" si="13"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.2">
@@ -16622,15 +16622,15 @@
         <v>727</v>
       </c>
       <c r="H423">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I423" s="2">
         <f t="shared" si="12"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J423" s="2">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.2">
@@ -17072,15 +17072,15 @@
         <v>11</v>
       </c>
       <c r="H438">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I438" s="2">
         <f t="shared" si="12"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J438" s="2">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.2">
@@ -17184,15 +17184,15 @@
         <v>853</v>
       </c>
       <c r="H442">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I442" s="2">
         <f t="shared" si="12"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J442" s="2">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.2">
@@ -17904,15 +17904,15 @@
         <v>82</v>
       </c>
       <c r="H466">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I466" s="2">
         <f t="shared" si="14"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J466" s="2">
         <f t="shared" si="15"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.2">
@@ -17932,15 +17932,15 @@
         <v>11</v>
       </c>
       <c r="H467">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I467" s="2">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J467" s="2">
         <f t="shared" si="15"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.2">
@@ -18019,15 +18019,15 @@
         <v>725</v>
       </c>
       <c r="H470">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I470" s="2">
         <f t="shared" si="14"/>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J470" s="2">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.2">
@@ -18140,15 +18140,15 @@
         <v>82</v>
       </c>
       <c r="H474">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I474" s="2">
         <f t="shared" si="14"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J474" s="2">
         <f t="shared" si="15"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.2">
@@ -18593,15 +18593,15 @@
         <v>82</v>
       </c>
       <c r="H489">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I489" s="2">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J489" s="2">
         <f t="shared" si="15"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.2">
@@ -18649,15 +18649,15 @@
         <v>11</v>
       </c>
       <c r="H491">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I491" s="2">
         <f t="shared" si="14"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J491" s="2">
         <f t="shared" si="15"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.2">
@@ -19121,15 +19121,15 @@
         <v>58</v>
       </c>
       <c r="H507">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I507" s="2">
         <f t="shared" si="14"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J507" s="2">
         <f t="shared" si="15"/>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.2">
@@ -19149,15 +19149,15 @@
         <v>723</v>
       </c>
       <c r="H508">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I508" s="2">
         <f t="shared" si="14"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J508" s="2">
         <f t="shared" si="15"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.2">
@@ -19472,15 +19472,15 @@
         <v>727</v>
       </c>
       <c r="H519">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I519" s="2">
         <f t="shared" si="16"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J519" s="2">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.2">
@@ -19801,15 +19801,15 @@
         <v>727</v>
       </c>
       <c r="H530">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I530" s="2">
         <f t="shared" si="16"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J530" s="2">
         <f t="shared" si="17"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="531" spans="1:10" x14ac:dyDescent="0.2">
@@ -20267,15 +20267,15 @@
         <v>727</v>
       </c>
       <c r="H546">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I546" s="2">
         <f t="shared" si="16"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J546" s="2">
         <f t="shared" si="17"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="547" spans="1:10" x14ac:dyDescent="0.2">
@@ -20683,15 +20683,15 @@
         <v>727</v>
       </c>
       <c r="H560">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I560" s="2">
         <f t="shared" si="16"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J560" s="2">
         <f t="shared" si="17"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561" spans="1:10" x14ac:dyDescent="0.2">
@@ -21794,15 +21794,15 @@
         <v>727</v>
       </c>
       <c r="H597">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I597" s="2">
         <f t="shared" si="18"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J597" s="2">
         <f t="shared" si="19"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="598" spans="1:10" x14ac:dyDescent="0.2">
@@ -21884,15 +21884,15 @@
         <v>723</v>
       </c>
       <c r="H600">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I600" s="2">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J600" s="2">
         <f t="shared" si="19"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="601" spans="1:10" x14ac:dyDescent="0.2">
@@ -22406,15 +22406,15 @@
         <v>725</v>
       </c>
       <c r="H618">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I618" s="2">
         <f t="shared" si="18"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J618" s="2">
         <f t="shared" si="19"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="619" spans="1:10" x14ac:dyDescent="0.2">
@@ -22555,15 +22555,15 @@
         <v>729</v>
       </c>
       <c r="H623">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I623" s="2">
         <f t="shared" si="18"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J623" s="2">
         <f t="shared" si="19"/>
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="624" spans="1:10" x14ac:dyDescent="0.2">
@@ -22614,15 +22614,15 @@
         <v>11</v>
       </c>
       <c r="H625">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I625" s="2">
         <f t="shared" si="18"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J625" s="2">
         <f t="shared" si="19"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="626" spans="1:10" x14ac:dyDescent="0.2">
@@ -22642,15 +22642,15 @@
         <v>730</v>
       </c>
       <c r="H626">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I626" s="2">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J626" s="2">
         <f t="shared" si="19"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="627" spans="1:10" x14ac:dyDescent="0.2">
@@ -22816,15 +22816,15 @@
         <v>11</v>
       </c>
       <c r="H632">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I632" s="2">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J632" s="2">
         <f t="shared" si="19"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="633" spans="1:10" x14ac:dyDescent="0.2">
@@ -22959,15 +22959,15 @@
         <v>723</v>
       </c>
       <c r="H637">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I637" s="2">
         <f t="shared" si="18"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J637" s="2">
         <f t="shared" si="19"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="638" spans="1:10" x14ac:dyDescent="0.2">
@@ -23254,15 +23254,15 @@
         <v>723</v>
       </c>
       <c r="H647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I647" s="2">
         <f t="shared" si="20"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J647" s="2">
         <f t="shared" si="21"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="648" spans="1:10" x14ac:dyDescent="0.2">
@@ -23397,15 +23397,15 @@
         <v>11</v>
       </c>
       <c r="H652">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I652" s="2">
         <f t="shared" si="20"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J652" s="2">
         <f t="shared" si="21"/>
-        <v>17.5</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="653" spans="1:10" x14ac:dyDescent="0.2">
@@ -23425,15 +23425,15 @@
         <v>11</v>
       </c>
       <c r="H653">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I653" s="2">
         <f t="shared" si="20"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J653" s="2">
         <f t="shared" si="21"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="654" spans="1:10" x14ac:dyDescent="0.2">
@@ -23602,15 +23602,15 @@
         <v>11</v>
       </c>
       <c r="H659">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I659" s="2">
         <f t="shared" si="20"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J659" s="2">
         <f t="shared" si="21"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="660" spans="1:10" x14ac:dyDescent="0.2">
@@ -24307,15 +24307,15 @@
         <v>729</v>
       </c>
       <c r="H686">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I686" s="2">
         <f t="shared" si="20"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J686" s="2">
         <f t="shared" si="21"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="687" spans="1:10" x14ac:dyDescent="0.2">
@@ -24332,15 +24332,15 @@
         <v>729</v>
       </c>
       <c r="H687">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I687" s="2">
         <f t="shared" si="20"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J687" s="2">
         <f t="shared" si="21"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="688" spans="1:10" x14ac:dyDescent="0.2">
@@ -24657,15 +24657,15 @@
         <v>725</v>
       </c>
       <c r="H700">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I700" s="2">
         <f t="shared" si="20"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J700" s="2">
         <f t="shared" si="21"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.2">
@@ -24807,15 +24807,15 @@
         <v>729</v>
       </c>
       <c r="H706">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I706" s="2">
         <f t="shared" ref="I706:I769" si="22">H706/5</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J706" s="2">
         <f t="shared" ref="J706:J769" si="23">H706*1.75</f>
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.2">
@@ -25307,15 +25307,15 @@
         <v>58</v>
       </c>
       <c r="H726">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I726" s="2">
         <f t="shared" si="22"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J726" s="2">
         <f t="shared" si="23"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="727" spans="1:10" x14ac:dyDescent="0.2">
@@ -25332,15 +25332,15 @@
         <v>723</v>
       </c>
       <c r="H727">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I727" s="2">
         <f t="shared" si="22"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J727" s="2">
         <f t="shared" si="23"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="728" spans="1:10" x14ac:dyDescent="0.2">
@@ -25357,15 +25357,15 @@
         <v>723</v>
       </c>
       <c r="H728">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I728" s="2">
         <f t="shared" si="22"/>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J728" s="2">
         <f t="shared" si="23"/>
-        <v>12.25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="729" spans="1:10" x14ac:dyDescent="0.2">
@@ -25382,15 +25382,15 @@
         <v>58</v>
       </c>
       <c r="H729">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I729" s="2">
         <f t="shared" si="22"/>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J729" s="2">
         <f t="shared" si="23"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="730" spans="1:10" x14ac:dyDescent="0.2">
@@ -25407,15 +25407,15 @@
         <v>723</v>
       </c>
       <c r="H730">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I730" s="2">
         <f t="shared" si="22"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J730" s="2">
         <f t="shared" si="23"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="731" spans="1:10" x14ac:dyDescent="0.2">
@@ -25432,15 +25432,15 @@
         <v>723</v>
       </c>
       <c r="H731">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I731" s="2">
         <f t="shared" si="22"/>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J731" s="2">
         <f t="shared" si="23"/>
-        <v>10.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="732" spans="1:10" x14ac:dyDescent="0.2">
@@ -25457,15 +25457,15 @@
         <v>723</v>
       </c>
       <c r="H732">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I732" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J732" s="2">
         <f t="shared" si="23"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="733" spans="1:10" x14ac:dyDescent="0.2">
@@ -25482,15 +25482,15 @@
         <v>723</v>
       </c>
       <c r="H733">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I733" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J733" s="2">
         <f t="shared" si="23"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="734" spans="1:10" x14ac:dyDescent="0.2">
@@ -25582,15 +25582,15 @@
         <v>735</v>
       </c>
       <c r="H737">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I737" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J737" s="2">
         <f t="shared" si="23"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="738" spans="1:10" x14ac:dyDescent="0.2">
@@ -25607,15 +25607,15 @@
         <v>723</v>
       </c>
       <c r="H738">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I738" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J738" s="2">
         <f t="shared" si="23"/>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="739" spans="1:10" x14ac:dyDescent="0.2">
@@ -25707,15 +25707,15 @@
         <v>723</v>
       </c>
       <c r="H742">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I742" s="2">
         <f t="shared" si="22"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J742" s="2">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="743" spans="1:10" x14ac:dyDescent="0.2">
@@ -25807,15 +25807,15 @@
         <v>727</v>
       </c>
       <c r="H746">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I746" s="2">
         <f t="shared" si="22"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J746" s="2">
         <f t="shared" si="23"/>
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="747" spans="1:10" x14ac:dyDescent="0.2">
@@ -26132,15 +26132,15 @@
         <v>11</v>
       </c>
       <c r="H759">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I759" s="2">
         <f t="shared" si="22"/>
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J759" s="2">
         <f t="shared" si="23"/>
-        <v>21</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="760" spans="1:10" x14ac:dyDescent="0.2">
@@ -26157,15 +26157,15 @@
         <v>727</v>
       </c>
       <c r="H760">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I760" s="2">
         <f t="shared" si="22"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J760" s="2">
         <f t="shared" si="23"/>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="761" spans="1:10" x14ac:dyDescent="0.2">
@@ -26182,15 +26182,15 @@
         <v>11</v>
       </c>
       <c r="H761">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I761" s="2">
         <f t="shared" si="22"/>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J761" s="2">
         <f t="shared" si="23"/>
-        <v>15.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="762" spans="1:10" x14ac:dyDescent="0.2">
@@ -26232,15 +26232,15 @@
         <v>11</v>
       </c>
       <c r="H763">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I763" s="2">
         <f t="shared" si="22"/>
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J763" s="2">
         <f t="shared" si="23"/>
-        <v>14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="764" spans="1:10" x14ac:dyDescent="0.2">
@@ -26257,15 +26257,15 @@
         <v>11</v>
       </c>
       <c r="H764">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I764" s="2">
         <f t="shared" si="22"/>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J764" s="2">
         <f t="shared" si="23"/>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="765" spans="1:10" x14ac:dyDescent="0.2">
@@ -26332,15 +26332,15 @@
         <v>11</v>
       </c>
       <c r="H767">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I767" s="2">
         <f t="shared" si="22"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J767" s="2">
         <f t="shared" si="23"/>
-        <v>8.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="768" spans="1:10" x14ac:dyDescent="0.2">
@@ -26357,15 +26357,15 @@
         <v>727</v>
       </c>
       <c r="H768">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I768" s="2">
         <f t="shared" si="22"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J768" s="2">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="769" spans="1:10" x14ac:dyDescent="0.2">
@@ -26382,15 +26382,15 @@
         <v>11</v>
       </c>
       <c r="H769">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I769" s="2">
         <f t="shared" si="22"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J769" s="2">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="770" spans="1:10" x14ac:dyDescent="0.2">

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DDB59B2-2DB9-B140-95BB-EF34855B50A9}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916CAE73-22AE-1341-80C1-66C3D7FC9BD9}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
         <v>80</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="s">
         <v>43</v>
@@ -4781,7 +4781,7 @@
         <v>104</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
         <v>50</v>
@@ -5019,7 +5019,7 @@
         <v>102</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
         <v>75</v>
@@ -5121,7 +5121,7 @@
         <v>38</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="s">
         <v>39</v>
@@ -5810,7 +5810,7 @@
         <v>103</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="s">
         <v>17</v>
@@ -5949,7 +5949,7 @@
         <v>79</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -6360,7 +6360,7 @@
         <v>118</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -7250,7 +7250,7 @@
         <v>487</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
         <v>53</v>
@@ -7389,7 +7389,7 @@
         <v>146</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="s">
         <v>20</v>
@@ -8328,7 +8328,7 @@
         <v>86</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="s">
         <v>39</v>
@@ -9054,7 +9054,7 @@
         <v>90</v>
       </c>
       <c r="C175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="s">
         <v>23</v>
@@ -9394,7 +9394,7 @@
         <v>121</v>
       </c>
       <c r="C185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" t="s">
         <v>32</v>
@@ -9669,7 +9669,7 @@
         <v>101</v>
       </c>
       <c r="C193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="s">
         <v>45</v>
@@ -9839,7 +9839,7 @@
         <v>95</v>
       </c>
       <c r="C198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E198" t="s">
         <v>43</v>
@@ -26414,7 +26414,7 @@
         <v>0.6</v>
       </c>
       <c r="J770" s="2">
-        <f t="shared" ref="J770:J814" si="25">H770*1.75</f>
+        <f t="shared" ref="J770:J773" si="25">H770*1.75</f>
         <v>5.25</v>
       </c>
     </row>

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2C5ED3-B2D4-1C4A-97C1-257DB1B4B228}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{630311CC-E66A-5046-9718-518B471A10DF}"/>
   <bookViews>
     <workbookView xWindow="15100" yWindow="660" windowWidth="15140" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista calciatori" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2336,11 +2336,11 @@
         <v>1</v>
       </c>
       <c r="I2" s="2">
-        <f>H2*0.2</f>
+        <f t="shared" ref="I2:I65" si="0">H2*0.2</f>
         <v>0.2</v>
       </c>
       <c r="J2" s="2">
-        <f>H2*1.75</f>
+        <f t="shared" ref="J2:J65" si="1">H2*1.75</f>
         <v>1.75</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -2373,11 +2373,11 @@
         <v>5</v>
       </c>
       <c r="I3" s="2">
-        <f>H3*0.2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J3" s="2">
-        <f>H3*1.75</f>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
       <c r="K3" t="s">
@@ -2410,11 +2410,11 @@
         <v>10</v>
       </c>
       <c r="I4" s="2">
-        <f>H4*0.2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J4" s="2">
-        <f>H4*1.75</f>
+        <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
       <c r="K4" t="s">
@@ -2447,11 +2447,11 @@
         <v>10</v>
       </c>
       <c r="I5" s="2">
-        <f>H5*0.2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J5" s="2">
-        <f>H5*1.75</f>
+        <f t="shared" si="1"/>
         <v>17.5</v>
       </c>
       <c r="K5" t="s">
@@ -2481,11 +2481,11 @@
         <v>1</v>
       </c>
       <c r="I6" s="2">
-        <f>H6*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J6" s="2">
-        <f>H6*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -2515,11 +2515,11 @@
         <v>9</v>
       </c>
       <c r="I7" s="2">
-        <f>H7*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J7" s="2">
-        <f>H7*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K7" t="s">
@@ -2552,11 +2552,11 @@
         <v>6</v>
       </c>
       <c r="I8" s="2">
-        <f>H8*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J8" s="2">
-        <f>H8*1.75</f>
+        <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
       <c r="K8" t="s">
@@ -2586,11 +2586,11 @@
         <v>1</v>
       </c>
       <c r="I9" s="2">
-        <f>H9*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J9" s="2">
-        <f>H9*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -2617,11 +2617,11 @@
         <v>2</v>
       </c>
       <c r="I10" s="2">
-        <f>H10*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="J10" s="2">
-        <f>H10*1.75</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -2651,11 +2651,11 @@
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <f>H11*0.2</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="J11" s="2">
-        <f>H11*1.75</f>
+        <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
       <c r="K11" t="s">
@@ -2688,11 +2688,11 @@
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <f>H12*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J12" s="2">
-        <f>H12*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
       <c r="K12" t="s">
@@ -2725,11 +2725,11 @@
         <v>15</v>
       </c>
       <c r="I13" s="2">
-        <f>H13*0.2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J13" s="2">
-        <f>H13*1.75</f>
+        <f t="shared" si="1"/>
         <v>26.25</v>
       </c>
       <c r="K13" t="s">
@@ -2759,11 +2759,11 @@
         <v>3</v>
       </c>
       <c r="I14" s="2">
-        <f>H14*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J14" s="2">
-        <f>H14*1.75</f>
+        <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
     </row>
@@ -2790,11 +2790,11 @@
         <v>1</v>
       </c>
       <c r="I15" s="2">
-        <f>H15*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J15" s="2">
-        <f>H15*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -2821,11 +2821,11 @@
         <v>5</v>
       </c>
       <c r="I16" s="2">
-        <f>H16*0.2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J16" s="2">
-        <f>H16*1.75</f>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
     </row>
@@ -2852,11 +2852,11 @@
         <v>2</v>
       </c>
       <c r="I17" s="2">
-        <f>H17*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="J17" s="2">
-        <f>H17*1.75</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -2883,11 +2883,11 @@
         <v>1</v>
       </c>
       <c r="I18" s="2">
-        <f>H18*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J18" s="2">
-        <f>H18*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -2917,11 +2917,11 @@
         <v>7</v>
       </c>
       <c r="I19" s="2">
-        <f>H19*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J19" s="2">
-        <f>H19*1.75</f>
+        <f t="shared" si="1"/>
         <v>12.25</v>
       </c>
       <c r="K19" t="s">
@@ -2951,11 +2951,11 @@
         <v>1</v>
       </c>
       <c r="I20" s="2">
-        <f>H20*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J20" s="2">
-        <f>H20*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -2982,11 +2982,11 @@
         <v>2</v>
       </c>
       <c r="I21" s="2">
-        <f>H21*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="J21" s="2">
-        <f>H21*1.75</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -3016,11 +3016,11 @@
         <v>19</v>
       </c>
       <c r="I22" s="2">
-        <f>H22*0.2</f>
+        <f t="shared" si="0"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="J22" s="2">
-        <f>H22*1.75</f>
+        <f t="shared" si="1"/>
         <v>33.25</v>
       </c>
       <c r="K22" t="s">
@@ -3053,11 +3053,11 @@
         <v>9</v>
       </c>
       <c r="I23" s="2">
-        <f>H23*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J23" s="2">
-        <f>H23*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K23" t="s">
@@ -3087,11 +3087,11 @@
         <v>1</v>
       </c>
       <c r="I24" s="2">
-        <f>H24*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J24" s="2">
-        <f>H24*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -3121,11 +3121,11 @@
         <v>8</v>
       </c>
       <c r="I25" s="2">
-        <f>H25*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="J25" s="2">
-        <f>H25*1.75</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="K25" t="s">
@@ -3158,11 +3158,11 @@
         <v>11</v>
       </c>
       <c r="I26" s="2">
-        <f>H26*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J26" s="2">
-        <f>H26*1.75</f>
+        <f t="shared" si="1"/>
         <v>19.25</v>
       </c>
       <c r="K26" t="s">
@@ -3192,11 +3192,11 @@
         <v>6</v>
       </c>
       <c r="I27" s="2">
-        <f>H27*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J27" s="2">
-        <f>H27*1.75</f>
+        <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
     </row>
@@ -3226,11 +3226,11 @@
         <v>1</v>
       </c>
       <c r="I28" s="2">
-        <f>H28*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J28" s="2">
-        <f>H28*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
       <c r="K28" t="s">
@@ -3263,11 +3263,11 @@
         <v>15</v>
       </c>
       <c r="I29" s="2">
-        <f>H29*0.2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J29" s="2">
-        <f>H29*1.75</f>
+        <f t="shared" si="1"/>
         <v>26.25</v>
       </c>
       <c r="K29" t="s">
@@ -3300,11 +3300,11 @@
         <v>9</v>
       </c>
       <c r="I30" s="2">
-        <f>H30*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J30" s="2">
-        <f>H30*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K30" t="s">
@@ -3337,11 +3337,11 @@
         <v>7</v>
       </c>
       <c r="I31" s="2">
-        <f>H31*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J31" s="2">
-        <f>H31*1.75</f>
+        <f t="shared" si="1"/>
         <v>12.25</v>
       </c>
       <c r="K31" t="s">
@@ -3371,11 +3371,11 @@
         <v>2</v>
       </c>
       <c r="I32" s="2">
-        <f>H32*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="J32" s="2">
-        <f>H32*1.75</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -3405,11 +3405,11 @@
         <v>9</v>
       </c>
       <c r="I33" s="2">
-        <f>H33*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J33" s="2">
-        <f>H33*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K33" t="s">
@@ -3442,11 +3442,11 @@
         <v>8</v>
       </c>
       <c r="I34" s="2">
-        <f>H34*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="J34" s="2">
-        <f>H34*1.75</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="K34" t="s">
@@ -3479,11 +3479,11 @@
         <v>17</v>
       </c>
       <c r="I35" s="2">
-        <f>H35*0.2</f>
+        <f t="shared" si="0"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J35" s="2">
-        <f>H35*1.75</f>
+        <f t="shared" si="1"/>
         <v>29.75</v>
       </c>
       <c r="K35" t="s">
@@ -3513,11 +3513,11 @@
         <v>3</v>
       </c>
       <c r="I36" s="2">
-        <f>H36*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J36" s="2">
-        <f>H36*1.75</f>
+        <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
     </row>
@@ -3544,11 +3544,11 @@
         <v>1</v>
       </c>
       <c r="I37" s="2">
-        <f>H37*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J37" s="2">
-        <f>H37*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -3575,11 +3575,11 @@
         <v>1</v>
       </c>
       <c r="I38" s="2">
-        <f>H38*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J38" s="2">
-        <f>H38*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -3609,11 +3609,11 @@
         <v>9</v>
       </c>
       <c r="I39" s="2">
-        <f>H39*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J39" s="2">
-        <f>H39*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K39" t="s">
@@ -3646,11 +3646,11 @@
         <v>12</v>
       </c>
       <c r="I40" s="2">
-        <f>H40*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J40" s="2">
-        <f>H40*1.75</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="K40" t="s">
@@ -3680,11 +3680,11 @@
         <v>15</v>
       </c>
       <c r="I41" s="2">
-        <f>H41*0.2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J41" s="2">
-        <f>H41*1.75</f>
+        <f t="shared" si="1"/>
         <v>26.25</v>
       </c>
     </row>
@@ -3714,11 +3714,11 @@
         <v>9</v>
       </c>
       <c r="I42" s="2">
-        <f>H42*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J42" s="2">
-        <f>H42*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K42" t="s">
@@ -3751,11 +3751,11 @@
         <v>25</v>
       </c>
       <c r="I43" s="2">
-        <f>H43*0.2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J43" s="2">
-        <f>H43*1.75</f>
+        <f t="shared" si="1"/>
         <v>43.75</v>
       </c>
       <c r="K43" t="s">
@@ -3785,11 +3785,11 @@
         <v>4</v>
       </c>
       <c r="I44" s="2">
-        <f>H44*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="J44" s="2">
-        <f>H44*1.75</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -3819,11 +3819,11 @@
         <v>14</v>
       </c>
       <c r="I45" s="2">
-        <f>H45*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J45" s="2">
-        <f>H45*1.75</f>
+        <f t="shared" si="1"/>
         <v>24.5</v>
       </c>
       <c r="K45" t="s">
@@ -3856,11 +3856,11 @@
         <v>8</v>
       </c>
       <c r="I46" s="2">
-        <f>H46*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="J46" s="2">
-        <f>H46*1.75</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="K46" t="s">
@@ -3893,11 +3893,11 @@
         <v>18</v>
       </c>
       <c r="I47" s="2">
-        <f>H47*0.2</f>
+        <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="J47" s="2">
-        <f>H47*1.75</f>
+        <f t="shared" si="1"/>
         <v>31.5</v>
       </c>
       <c r="K47" t="s">
@@ -3927,11 +3927,11 @@
         <v>8</v>
       </c>
       <c r="I48" s="2">
-        <f>H48*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="J48" s="2">
-        <f>H48*1.75</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -3961,11 +3961,11 @@
         <v>25</v>
       </c>
       <c r="I49" s="2">
-        <f>H49*0.2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J49" s="2">
-        <f>H49*1.75</f>
+        <f t="shared" si="1"/>
         <v>43.75</v>
       </c>
       <c r="K49" t="s">
@@ -3998,11 +3998,11 @@
         <v>5</v>
       </c>
       <c r="I50" s="2">
-        <f>H50*0.2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J50" s="2">
-        <f>H50*1.75</f>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
       <c r="K50" t="s">
@@ -4035,11 +4035,11 @@
         <v>6</v>
       </c>
       <c r="I51" s="2">
-        <f>H51*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J51" s="2">
-        <f>H51*1.75</f>
+        <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
       <c r="K51" t="s">
@@ -4072,11 +4072,11 @@
         <v>28</v>
       </c>
       <c r="I52" s="2">
-        <f>H52*0.2</f>
+        <f t="shared" si="0"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="J52" s="2">
-        <f>H52*1.75</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="K52" t="s">
@@ -4106,11 +4106,11 @@
         <v>2</v>
       </c>
       <c r="I53" s="2">
-        <f>H53*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="J53" s="2">
-        <f>H53*1.75</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         <v>15</v>
       </c>
       <c r="I54" s="2">
-        <f>H54*0.2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J54" s="2">
-        <f>H54*1.75</f>
+        <f t="shared" si="1"/>
         <v>26.25</v>
       </c>
       <c r="K54" t="s">
@@ -4174,11 +4174,11 @@
         <v>1</v>
       </c>
       <c r="I55" s="2">
-        <f>H55*0.2</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="J55" s="2">
-        <f>H55*1.75</f>
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
     </row>
@@ -4208,11 +4208,11 @@
         <v>22</v>
       </c>
       <c r="I56" s="2">
-        <f>H56*0.2</f>
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="J56" s="2">
-        <f>H56*1.75</f>
+        <f t="shared" si="1"/>
         <v>38.5</v>
       </c>
       <c r="K56" t="s">
@@ -4245,11 +4245,11 @@
         <v>23</v>
       </c>
       <c r="I57" s="2">
-        <f>H57*0.2</f>
+        <f t="shared" si="0"/>
         <v>4.6000000000000005</v>
       </c>
       <c r="J57" s="2">
-        <f>H57*1.75</f>
+        <f t="shared" si="1"/>
         <v>40.25</v>
       </c>
       <c r="K57" t="s">
@@ -4279,11 +4279,11 @@
         <v>12</v>
       </c>
       <c r="I58" s="2">
-        <f>H58*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J58" s="2">
-        <f>H58*1.75</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
     </row>
@@ -4313,11 +4313,11 @@
         <v>14</v>
       </c>
       <c r="I59" s="2">
-        <f>H59*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J59" s="2">
-        <f>H59*1.75</f>
+        <f t="shared" si="1"/>
         <v>24.5</v>
       </c>
       <c r="K59" t="s">
@@ -4350,11 +4350,11 @@
         <v>13</v>
       </c>
       <c r="I60" s="2">
-        <f>H60*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
       <c r="J60" s="2">
-        <f>H60*1.75</f>
+        <f t="shared" si="1"/>
         <v>22.75</v>
       </c>
       <c r="K60" t="s">
@@ -4384,11 +4384,11 @@
         <v>6</v>
       </c>
       <c r="I61" s="2">
-        <f>H61*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J61" s="2">
-        <f>H61*1.75</f>
+        <f t="shared" si="1"/>
         <v>10.5</v>
       </c>
     </row>
@@ -4418,11 +4418,11 @@
         <v>5</v>
       </c>
       <c r="I62" s="2">
-        <f>H62*0.2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J62" s="2">
-        <f>H62*1.75</f>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
       <c r="K62" t="s">
@@ -4455,11 +4455,11 @@
         <v>9</v>
       </c>
       <c r="I63" s="2">
-        <f>H63*0.2</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="J63" s="2">
-        <f>H63*1.75</f>
+        <f t="shared" si="1"/>
         <v>15.75</v>
       </c>
       <c r="K63" t="s">
@@ -4492,11 +4492,11 @@
         <v>5</v>
       </c>
       <c r="I64" s="2">
-        <f>H64*0.2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J64" s="2">
-        <f>H64*1.75</f>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
       <c r="K64" t="s">
@@ -4529,11 +4529,11 @@
         <v>13</v>
       </c>
       <c r="I65" s="2">
-        <f>H65*0.2</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
       <c r="J65" s="2">
-        <f>H65*1.75</f>
+        <f t="shared" si="1"/>
         <v>22.75</v>
       </c>
       <c r="K65" t="s">
@@ -4566,11 +4566,11 @@
         <v>6</v>
       </c>
       <c r="I66" s="2">
-        <f>H66*0.2</f>
+        <f t="shared" ref="I66:I129" si="2">H66*0.2</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="J66" s="2">
-        <f>H66*1.75</f>
+        <f t="shared" ref="J66:J129" si="3">H66*1.75</f>
         <v>10.5</v>
       </c>
       <c r="K66" t="s">
@@ -4603,11 +4603,11 @@
         <v>7</v>
       </c>
       <c r="I67" s="2">
-        <f>H67*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J67" s="2">
-        <f>H67*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K67" t="s">
@@ -4637,11 +4637,11 @@
         <v>2</v>
       </c>
       <c r="I68" s="2">
-        <f>H68*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="J68" s="2">
-        <f>H68*1.75</f>
+        <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
     </row>
@@ -4668,11 +4668,11 @@
         <v>8</v>
       </c>
       <c r="I69" s="2">
-        <f>H69*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="J69" s="2">
-        <f>H69*1.75</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -4702,11 +4702,11 @@
         <v>35</v>
       </c>
       <c r="I70" s="2">
-        <f>H70*0.2</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="J70" s="2">
-        <f>H70*1.75</f>
+        <f t="shared" si="3"/>
         <v>61.25</v>
       </c>
       <c r="K70" t="s">
@@ -4739,11 +4739,11 @@
         <v>7</v>
       </c>
       <c r="I71" s="2">
-        <f>H71*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J71" s="2">
-        <f>H71*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K71" t="s">
@@ -4776,11 +4776,11 @@
         <v>17</v>
       </c>
       <c r="I72" s="2">
-        <f>H72*0.2</f>
+        <f t="shared" si="2"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J72" s="2">
-        <f>H72*1.75</f>
+        <f t="shared" si="3"/>
         <v>29.75</v>
       </c>
       <c r="K72" t="s">
@@ -4813,11 +4813,11 @@
         <v>15</v>
       </c>
       <c r="I73" s="2">
-        <f>H73*0.2</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="J73" s="2">
-        <f>H73*1.75</f>
+        <f t="shared" si="3"/>
         <v>26.25</v>
       </c>
       <c r="K73" t="s">
@@ -4847,11 +4847,11 @@
         <v>1</v>
       </c>
       <c r="I74" s="2">
-        <f>H74*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="J74" s="2">
-        <f>H74*1.75</f>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
     </row>
@@ -4881,11 +4881,11 @@
         <v>2</v>
       </c>
       <c r="I75" s="2">
-        <f>H75*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="J75" s="2">
-        <f>H75*1.75</f>
+        <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
       <c r="K75" t="s">
@@ -4918,11 +4918,11 @@
         <v>1</v>
       </c>
       <c r="I76" s="2">
-        <f>H76*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="J76" s="2">
-        <f>H76*1.75</f>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
       <c r="K76" t="s">
@@ -4952,11 +4952,11 @@
         <v>12</v>
       </c>
       <c r="I77" s="2">
-        <f>H77*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J77" s="2">
-        <f>H77*1.75</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
     </row>
@@ -4986,11 +4986,11 @@
         <v>7</v>
       </c>
       <c r="I78" s="2">
-        <f>H78*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J78" s="2">
-        <f>H78*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K78" t="s">
@@ -5020,11 +5020,11 @@
         <v>1</v>
       </c>
       <c r="I79" s="2">
-        <f>H79*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="J79" s="2">
-        <f>H79*1.75</f>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
     </row>
@@ -5051,11 +5051,11 @@
         <v>7</v>
       </c>
       <c r="I80" s="2">
-        <f>H80*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J80" s="2">
-        <f>H80*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5082,11 +5082,11 @@
         <v>5</v>
       </c>
       <c r="I81" s="2">
-        <f>H81*0.2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J81" s="2">
-        <f>H81*1.75</f>
+        <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
     </row>
@@ -5116,11 +5116,11 @@
         <v>16</v>
       </c>
       <c r="I82" s="2">
-        <f>H82*0.2</f>
+        <f t="shared" si="2"/>
         <v>3.2</v>
       </c>
       <c r="J82" s="2">
-        <f>H82*1.75</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="K82" t="s">
@@ -5150,11 +5150,11 @@
         <v>7</v>
       </c>
       <c r="I83" s="2">
-        <f>H83*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J83" s="2">
-        <f>H83*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5184,11 +5184,11 @@
         <v>4</v>
       </c>
       <c r="I84" s="2">
-        <f>H84*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J84" s="2">
-        <f>H84*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="K84" t="s">
@@ -5221,11 +5221,11 @@
         <v>8</v>
       </c>
       <c r="I85" s="2">
-        <f>H85*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="J85" s="2">
-        <f>H85*1.75</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="K85" t="s">
@@ -5258,11 +5258,11 @@
         <v>11</v>
       </c>
       <c r="I86" s="2">
-        <f>H86*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J86" s="2">
-        <f>H86*1.75</f>
+        <f t="shared" si="3"/>
         <v>19.25</v>
       </c>
       <c r="K86" t="s">
@@ -5292,11 +5292,11 @@
         <v>7</v>
       </c>
       <c r="I87" s="2">
-        <f>H87*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J87" s="2">
-        <f>H87*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5323,11 +5323,11 @@
         <v>7</v>
       </c>
       <c r="I88" s="2">
-        <f>H88*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J88" s="2">
-        <f>H88*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5354,11 +5354,11 @@
         <v>4</v>
       </c>
       <c r="I89" s="2">
-        <f>H89*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J89" s="2">
-        <f>H89*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -5388,11 +5388,11 @@
         <v>8</v>
       </c>
       <c r="I90" s="2">
-        <f>H90*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="J90" s="2">
-        <f>H90*1.75</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="K90" t="s">
@@ -5425,11 +5425,11 @@
         <v>15</v>
       </c>
       <c r="I91" s="2">
-        <f>H91*0.2</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="J91" s="2">
-        <f>H91*1.75</f>
+        <f t="shared" si="3"/>
         <v>26.25</v>
       </c>
       <c r="K91" t="s">
@@ -5462,11 +5462,11 @@
         <v>13</v>
       </c>
       <c r="I92" s="2">
-        <f>H92*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.6</v>
       </c>
       <c r="J92" s="2">
-        <f>H92*1.75</f>
+        <f t="shared" si="3"/>
         <v>22.75</v>
       </c>
       <c r="K92" t="s">
@@ -5496,11 +5496,11 @@
         <v>7</v>
       </c>
       <c r="I93" s="2">
-        <f>H93*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J93" s="2">
-        <f>H93*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5527,11 +5527,11 @@
         <v>7</v>
       </c>
       <c r="I94" s="2">
-        <f>H94*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J94" s="2">
-        <f>H94*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5558,11 +5558,11 @@
         <v>9</v>
       </c>
       <c r="I95" s="2">
-        <f>H95*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
       <c r="J95" s="2">
-        <f>H95*1.75</f>
+        <f t="shared" si="3"/>
         <v>15.75</v>
       </c>
     </row>
@@ -5589,11 +5589,11 @@
         <v>8</v>
       </c>
       <c r="I96" s="2">
-        <f>H96*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="J96" s="2">
-        <f>H96*1.75</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -5623,11 +5623,11 @@
         <v>14</v>
       </c>
       <c r="I97" s="2">
-        <f>H97*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J97" s="2">
-        <f>H97*1.75</f>
+        <f t="shared" si="3"/>
         <v>24.5</v>
       </c>
       <c r="K97" t="s">
@@ -5657,11 +5657,11 @@
         <v>4</v>
       </c>
       <c r="I98" s="2">
-        <f>H98*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J98" s="2">
-        <f>H98*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -5691,11 +5691,11 @@
         <v>3</v>
       </c>
       <c r="I99" s="2">
-        <f>H99*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J99" s="2">
-        <f>H99*1.75</f>
+        <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
       <c r="K99" t="s">
@@ -5725,11 +5725,11 @@
         <v>4</v>
       </c>
       <c r="I100" s="2">
-        <f>H100*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J100" s="2">
-        <f>H100*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -5759,11 +5759,11 @@
         <v>7</v>
       </c>
       <c r="I101" s="2">
-        <f>H101*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J101" s="2">
-        <f>H101*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K101" t="s">
@@ -5796,11 +5796,11 @@
         <v>14</v>
       </c>
       <c r="I102" s="2">
-        <f>H102*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J102" s="2">
-        <f>H102*1.75</f>
+        <f t="shared" si="3"/>
         <v>24.5</v>
       </c>
       <c r="K102" t="s">
@@ -5833,11 +5833,11 @@
         <v>16</v>
       </c>
       <c r="I103" s="2">
-        <f>H103*0.2</f>
+        <f t="shared" si="2"/>
         <v>3.2</v>
       </c>
       <c r="J103" s="2">
-        <f>H103*1.75</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="K103" t="s">
@@ -5870,11 +5870,11 @@
         <v>6</v>
       </c>
       <c r="I104" s="2">
-        <f>H104*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J104" s="2">
-        <f>H104*1.75</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="K104" t="s">
@@ -5907,11 +5907,11 @@
         <v>7</v>
       </c>
       <c r="I105" s="2">
-        <f>H105*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J105" s="2">
-        <f>H105*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K105" t="s">
@@ -5941,11 +5941,11 @@
         <v>7</v>
       </c>
       <c r="I106" s="2">
-        <f>H106*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J106" s="2">
-        <f>H106*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -5975,11 +5975,11 @@
         <v>4</v>
       </c>
       <c r="I107" s="2">
-        <f>H107*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J107" s="2">
-        <f>H107*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="K107" t="s">
@@ -6012,11 +6012,11 @@
         <v>14</v>
       </c>
       <c r="I108" s="2">
-        <f>H108*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J108" s="2">
-        <f>H108*1.75</f>
+        <f t="shared" si="3"/>
         <v>24.5</v>
       </c>
       <c r="K108" t="s">
@@ -6049,11 +6049,11 @@
         <v>9</v>
       </c>
       <c r="I109" s="2">
-        <f>H109*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
       <c r="J109" s="2">
-        <f>H109*1.75</f>
+        <f t="shared" si="3"/>
         <v>15.75</v>
       </c>
       <c r="K109" t="s">
@@ -6083,11 +6083,11 @@
         <v>5</v>
       </c>
       <c r="I110" s="2">
-        <f>H110*0.2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J110" s="2">
-        <f>H110*1.75</f>
+        <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
     </row>
@@ -6117,11 +6117,11 @@
         <v>6</v>
       </c>
       <c r="I111" s="2">
-        <f>H111*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J111" s="2">
-        <f>H111*1.75</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="K111" t="s">
@@ -6154,11 +6154,11 @@
         <v>19</v>
       </c>
       <c r="I112" s="2">
-        <f>H112*0.2</f>
+        <f t="shared" si="2"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="J112" s="2">
-        <f>H112*1.75</f>
+        <f t="shared" si="3"/>
         <v>33.25</v>
       </c>
       <c r="K112" t="s">
@@ -6188,11 +6188,11 @@
         <v>1</v>
       </c>
       <c r="I113" s="2">
-        <f>H113*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="J113" s="2">
-        <f>H113*1.75</f>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
     </row>
@@ -6222,11 +6222,11 @@
         <v>9</v>
       </c>
       <c r="I114" s="2">
-        <f>H114*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
       <c r="J114" s="2">
-        <f>H114*1.75</f>
+        <f t="shared" si="3"/>
         <v>15.75</v>
       </c>
       <c r="K114" t="s">
@@ -6259,11 +6259,11 @@
         <v>6</v>
       </c>
       <c r="I115" s="2">
-        <f>H115*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J115" s="2">
-        <f>H115*1.75</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="K115" t="s">
@@ -6296,11 +6296,11 @@
         <v>14</v>
       </c>
       <c r="I116" s="2">
-        <f>H116*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J116" s="2">
-        <f>H116*1.75</f>
+        <f t="shared" si="3"/>
         <v>24.5</v>
       </c>
       <c r="K116" t="s">
@@ -6333,11 +6333,11 @@
         <v>8</v>
       </c>
       <c r="I117" s="2">
-        <f>H117*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
       <c r="J117" s="2">
-        <f>H117*1.75</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="K117" t="s">
@@ -6370,11 +6370,11 @@
         <v>7</v>
       </c>
       <c r="I118" s="2">
-        <f>H118*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J118" s="2">
-        <f>H118*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
       <c r="K118" t="s">
@@ -6407,11 +6407,11 @@
         <v>28</v>
       </c>
       <c r="I119" s="2">
-        <f>H119*0.2</f>
+        <f t="shared" si="2"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="J119" s="2">
-        <f>H119*1.75</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="K119" t="s">
@@ -6444,11 +6444,11 @@
         <v>10</v>
       </c>
       <c r="I120" s="2">
-        <f>H120*0.2</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="J120" s="2">
-        <f>H120*1.75</f>
+        <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
       <c r="K120" t="s">
@@ -6478,11 +6478,11 @@
         <v>5</v>
       </c>
       <c r="I121" s="2">
-        <f>H121*0.2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J121" s="2">
-        <f>H121*1.75</f>
+        <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
     </row>
@@ -6509,11 +6509,11 @@
         <v>4</v>
       </c>
       <c r="I122" s="2">
-        <f>H122*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="J122" s="2">
-        <f>H122*1.75</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -6540,11 +6540,11 @@
         <v>5</v>
       </c>
       <c r="I123" s="2">
-        <f>H123*0.2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J123" s="2">
-        <f>H123*1.75</f>
+        <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
     </row>
@@ -6571,11 +6571,11 @@
         <v>1</v>
       </c>
       <c r="I124" s="2">
-        <f>H124*0.2</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="J124" s="2">
-        <f>H124*1.75</f>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
     </row>
@@ -6602,11 +6602,11 @@
         <v>7</v>
       </c>
       <c r="I125" s="2">
-        <f>H125*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J125" s="2">
-        <f>H125*1.75</f>
+        <f t="shared" si="3"/>
         <v>12.25</v>
       </c>
     </row>
@@ -6636,11 +6636,11 @@
         <v>29</v>
       </c>
       <c r="I126" s="2">
-        <f>H126*0.2</f>
+        <f t="shared" si="2"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="J126" s="2">
-        <f>H126*1.75</f>
+        <f t="shared" si="3"/>
         <v>50.75</v>
       </c>
       <c r="K126" t="s">
@@ -6673,11 +6673,11 @@
         <v>6</v>
       </c>
       <c r="I127" s="2">
-        <f>H127*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J127" s="2">
-        <f>H127*1.75</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="K127" t="s">
@@ -6710,11 +6710,11 @@
         <v>11</v>
       </c>
       <c r="I128" s="2">
-        <f>H128*0.2</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J128" s="2">
-        <f>H128*1.75</f>
+        <f t="shared" si="3"/>
         <v>19.25</v>
       </c>
       <c r="K128" t="s">
@@ -6747,11 +6747,11 @@
         <v>6</v>
       </c>
       <c r="I129" s="2">
-        <f>H129*0.2</f>
+        <f t="shared" si="2"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J129" s="2">
-        <f>H129*1.75</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="K129" t="s">
@@ -6781,11 +6781,11 @@
         <v>4</v>
       </c>
       <c r="I130" s="2">
-        <f>H130*0.2</f>
+        <f t="shared" ref="I130:I193" si="4">H130*0.2</f>
         <v>0.8</v>
       </c>
       <c r="J130" s="2">
-        <f>H130*1.75</f>
+        <f t="shared" ref="J130:J193" si="5">H130*1.75</f>
         <v>7</v>
       </c>
     </row>
@@ -6812,11 +6812,11 @@
         <v>10</v>
       </c>
       <c r="I131" s="2">
-        <f>H131*0.2</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J131" s="2">
-        <f>H131*1.75</f>
+        <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
     </row>
@@ -6843,11 +6843,11 @@
         <v>4</v>
       </c>
       <c r="I132" s="2">
-        <f>H132*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="J132" s="2">
-        <f>H132*1.75</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -6874,11 +6874,11 @@
         <v>1</v>
       </c>
       <c r="I133" s="2">
-        <f>H133*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J133" s="2">
-        <f>H133*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -6905,11 +6905,11 @@
         <v>3</v>
       </c>
       <c r="I134" s="2">
-        <f>H134*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J134" s="2">
-        <f>H134*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
     </row>
@@ -6936,11 +6936,11 @@
         <v>6</v>
       </c>
       <c r="I135" s="2">
-        <f>H135*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J135" s="2">
-        <f>H135*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
     </row>
@@ -6967,11 +6967,11 @@
         <v>3</v>
       </c>
       <c r="I136" s="2">
-        <f>H136*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J136" s="2">
-        <f>H136*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
     </row>
@@ -7001,11 +7001,11 @@
         <v>17</v>
       </c>
       <c r="I137" s="2">
-        <f>H137*0.2</f>
+        <f t="shared" si="4"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J137" s="2">
-        <f>H137*1.75</f>
+        <f t="shared" si="5"/>
         <v>29.75</v>
       </c>
       <c r="K137" t="s">
@@ -7038,11 +7038,11 @@
         <v>14</v>
       </c>
       <c r="I138" s="2">
-        <f>H138*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J138" s="2">
-        <f>H138*1.75</f>
+        <f t="shared" si="5"/>
         <v>24.5</v>
       </c>
       <c r="K138" t="s">
@@ -7075,11 +7075,11 @@
         <v>8</v>
       </c>
       <c r="I139" s="2">
-        <f>H139*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="J139" s="2">
-        <f>H139*1.75</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="K139" t="s">
@@ -7109,11 +7109,11 @@
         <v>1</v>
       </c>
       <c r="I140" s="2">
-        <f>H140*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J140" s="2">
-        <f>H140*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7143,11 +7143,11 @@
         <v>7</v>
       </c>
       <c r="I141" s="2">
-        <f>H141*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J141" s="2">
-        <f>H141*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
       <c r="K141" t="s">
@@ -7180,11 +7180,11 @@
         <v>14</v>
       </c>
       <c r="I142" s="2">
-        <f>H142*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="J142" s="2">
-        <f>H142*1.75</f>
+        <f t="shared" si="5"/>
         <v>24.5</v>
       </c>
       <c r="K142" t="s">
@@ -7214,11 +7214,11 @@
         <v>8</v>
       </c>
       <c r="I143" s="2">
-        <f>H143*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="J143" s="2">
-        <f>H143*1.75</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
@@ -7245,11 +7245,11 @@
         <v>6</v>
       </c>
       <c r="I144" s="2">
-        <f>H144*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J144" s="2">
-        <f>H144*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
     </row>
@@ -7279,11 +7279,11 @@
         <v>17</v>
       </c>
       <c r="I145" s="2">
-        <f>H145*0.2</f>
+        <f t="shared" si="4"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J145" s="2">
-        <f>H145*1.75</f>
+        <f t="shared" si="5"/>
         <v>29.75</v>
       </c>
       <c r="K145" t="s">
@@ -7313,11 +7313,11 @@
         <v>12</v>
       </c>
       <c r="I146" s="2">
-        <f>H146*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J146" s="2">
-        <f>H146*1.75</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
     </row>
@@ -7344,11 +7344,11 @@
         <v>3</v>
       </c>
       <c r="I147" s="2">
-        <f>H147*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J147" s="2">
-        <f>H147*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
     </row>
@@ -7378,11 +7378,11 @@
         <v>3</v>
       </c>
       <c r="I148" s="2">
-        <f>H148*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J148" s="2">
-        <f>H148*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
       <c r="K148" t="s">
@@ -7412,11 +7412,11 @@
         <v>2</v>
       </c>
       <c r="I149" s="2">
-        <f>H149*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="J149" s="2">
-        <f>H149*1.75</f>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
     </row>
@@ -7443,11 +7443,11 @@
         <v>7</v>
       </c>
       <c r="I150" s="2">
-        <f>H150*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J150" s="2">
-        <f>H150*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
@@ -7477,11 +7477,11 @@
         <v>5</v>
       </c>
       <c r="I151" s="2">
-        <f>H151*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J151" s="2">
-        <f>H151*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
       <c r="K151" t="s">
@@ -7511,11 +7511,11 @@
         <v>4</v>
       </c>
       <c r="I152" s="2">
-        <f>H152*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="J152" s="2">
-        <f>H152*1.75</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -7542,11 +7542,11 @@
         <v>5</v>
       </c>
       <c r="I153" s="2">
-        <f>H153*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J153" s="2">
-        <f>H153*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
     </row>
@@ -7573,11 +7573,11 @@
         <v>1</v>
       </c>
       <c r="I154" s="2">
-        <f>H154*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J154" s="2">
-        <f>H154*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7604,11 +7604,11 @@
         <v>8</v>
       </c>
       <c r="I155" s="2">
-        <f>H155*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="J155" s="2">
-        <f>H155*1.75</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
@@ -7635,11 +7635,11 @@
         <v>1</v>
       </c>
       <c r="I156" s="2">
-        <f>H156*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J156" s="2">
-        <f>H156*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7669,11 +7669,11 @@
         <v>5</v>
       </c>
       <c r="I157" s="2">
-        <f>H157*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J157" s="2">
-        <f>H157*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
       <c r="K157" t="s">
@@ -7703,11 +7703,11 @@
         <v>1</v>
       </c>
       <c r="I158" s="2">
-        <f>H158*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J158" s="2">
-        <f>H158*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7734,11 +7734,11 @@
         <v>6</v>
       </c>
       <c r="I159" s="2">
-        <f>H159*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J159" s="2">
-        <f>H159*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
     </row>
@@ -7765,11 +7765,11 @@
         <v>5</v>
       </c>
       <c r="I160" s="2">
-        <f>H160*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J160" s="2">
-        <f>H160*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
     </row>
@@ -7796,11 +7796,11 @@
         <v>4</v>
       </c>
       <c r="I161" s="2">
-        <f>H161*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="J161" s="2">
-        <f>H161*1.75</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -7827,11 +7827,11 @@
         <v>2</v>
       </c>
       <c r="I162" s="2">
-        <f>H162*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="J162" s="2">
-        <f>H162*1.75</f>
+        <f t="shared" si="5"/>
         <v>3.5</v>
       </c>
     </row>
@@ -7858,11 +7858,11 @@
         <v>1</v>
       </c>
       <c r="I163" s="2">
-        <f>H163*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J163" s="2">
-        <f>H163*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7889,11 +7889,11 @@
         <v>1</v>
       </c>
       <c r="I164" s="2">
-        <f>H164*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J164" s="2">
-        <f>H164*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -7920,11 +7920,11 @@
         <v>3</v>
       </c>
       <c r="I165" s="2">
-        <f>H165*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J165" s="2">
-        <f>H165*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
     </row>
@@ -7951,11 +7951,11 @@
         <v>8</v>
       </c>
       <c r="I166" s="2">
-        <f>H166*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="J166" s="2">
-        <f>H166*1.75</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
     </row>
@@ -7982,11 +7982,11 @@
         <v>7</v>
       </c>
       <c r="I167" s="2">
-        <f>H167*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J167" s="2">
-        <f>H167*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
@@ -8013,11 +8013,11 @@
         <v>6</v>
       </c>
       <c r="I168" s="2">
-        <f>H168*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J168" s="2">
-        <f>H168*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
     </row>
@@ -8047,11 +8047,11 @@
         <v>10</v>
       </c>
       <c r="I169" s="2">
-        <f>H169*0.2</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J169" s="2">
-        <f>H169*1.75</f>
+        <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
       <c r="K169" t="s">
@@ -8084,11 +8084,11 @@
         <v>10</v>
       </c>
       <c r="I170" s="2">
-        <f>H170*0.2</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J170" s="2">
-        <f>H170*1.75</f>
+        <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
       <c r="K170" t="s">
@@ -8121,11 +8121,11 @@
         <v>10</v>
       </c>
       <c r="I171" s="2">
-        <f>H171*0.2</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J171" s="2">
-        <f>H171*1.75</f>
+        <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
       <c r="K171" t="s">
@@ -8155,11 +8155,11 @@
         <v>4</v>
       </c>
       <c r="I172" s="2">
-        <f>H172*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="J172" s="2">
-        <f>H172*1.75</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
         <v>100</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="s">
         <v>590</v>
@@ -8189,15 +8189,15 @@
         <v>8</v>
       </c>
       <c r="I173" s="2">
-        <f>H173*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="J173" s="2">
-        <f>H173*1.75</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="K173" t="s">
-        <v>64</v>
+        <v>473</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
@@ -8226,11 +8226,11 @@
         <v>6</v>
       </c>
       <c r="I174" s="2">
-        <f>H174*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J174" s="2">
-        <f>H174*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
       <c r="K174" t="s">
@@ -8263,11 +8263,11 @@
         <v>18</v>
       </c>
       <c r="I175" s="2">
-        <f>H175*0.2</f>
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
       <c r="J175" s="2">
-        <f>H175*1.75</f>
+        <f t="shared" si="5"/>
         <v>31.5</v>
       </c>
       <c r="K175" t="s">
@@ -8300,11 +8300,11 @@
         <v>10</v>
       </c>
       <c r="I176" s="2">
-        <f>H176*0.2</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="J176" s="2">
-        <f>H176*1.75</f>
+        <f t="shared" si="5"/>
         <v>17.5</v>
       </c>
       <c r="K176" t="s">
@@ -8334,11 +8334,11 @@
         <v>3</v>
       </c>
       <c r="I177" s="2">
-        <f>H177*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J177" s="2">
-        <f>H177*1.75</f>
+        <f t="shared" si="5"/>
         <v>5.25</v>
       </c>
     </row>
@@ -8368,11 +8368,11 @@
         <v>34</v>
       </c>
       <c r="I178" s="2">
-        <f>H178*0.2</f>
+        <f t="shared" si="4"/>
         <v>6.8000000000000007</v>
       </c>
       <c r="J178" s="2">
-        <f>H178*1.75</f>
+        <f t="shared" si="5"/>
         <v>59.5</v>
       </c>
       <c r="K178" t="s">
@@ -8405,11 +8405,11 @@
         <v>11</v>
       </c>
       <c r="I179" s="2">
-        <f>H179*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J179" s="2">
-        <f>H179*1.75</f>
+        <f t="shared" si="5"/>
         <v>19.25</v>
       </c>
       <c r="K179" t="s">
@@ -8442,11 +8442,11 @@
         <v>4</v>
       </c>
       <c r="I180" s="2">
-        <f>H180*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="J180" s="2">
-        <f>H180*1.75</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="K180" t="s">
@@ -8479,11 +8479,11 @@
         <v>6</v>
       </c>
       <c r="I181" s="2">
-        <f>H181*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J181" s="2">
-        <f>H181*1.75</f>
+        <f t="shared" si="5"/>
         <v>10.5</v>
       </c>
       <c r="K181" t="s">
@@ -8516,11 +8516,11 @@
         <v>19</v>
       </c>
       <c r="I182" s="2">
-        <f>H182*0.2</f>
+        <f t="shared" si="4"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="J182" s="2">
-        <f>H182*1.75</f>
+        <f t="shared" si="5"/>
         <v>33.25</v>
       </c>
       <c r="K182" t="s">
@@ -8550,11 +8550,11 @@
         <v>11</v>
       </c>
       <c r="I183" s="2">
-        <f>H183*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J183" s="2">
-        <f>H183*1.75</f>
+        <f t="shared" si="5"/>
         <v>19.25</v>
       </c>
     </row>
@@ -8581,11 +8581,11 @@
         <v>7</v>
       </c>
       <c r="I184" s="2">
-        <f>H184*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J184" s="2">
-        <f>H184*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
@@ -8615,11 +8615,11 @@
         <v>5</v>
       </c>
       <c r="I185" s="2">
-        <f>H185*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J185" s="2">
-        <f>H185*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
       <c r="K185" t="s">
@@ -8649,11 +8649,11 @@
         <v>5</v>
       </c>
       <c r="I186" s="2">
-        <f>H186*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J186" s="2">
-        <f>H186*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
     </row>
@@ -8683,11 +8683,11 @@
         <v>13</v>
       </c>
       <c r="I187" s="2">
-        <f>H187*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
       <c r="J187" s="2">
-        <f>H187*1.75</f>
+        <f t="shared" si="5"/>
         <v>22.75</v>
       </c>
       <c r="K187" t="s">
@@ -8717,11 +8717,11 @@
         <v>5</v>
       </c>
       <c r="I188" s="2">
-        <f>H188*0.2</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J188" s="2">
-        <f>H188*1.75</f>
+        <f t="shared" si="5"/>
         <v>8.75</v>
       </c>
     </row>
@@ -8748,11 +8748,11 @@
         <v>7</v>
       </c>
       <c r="I189" s="2">
-        <f>H189*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J189" s="2">
-        <f>H189*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
@@ -8779,11 +8779,11 @@
         <v>1</v>
       </c>
       <c r="I190" s="2">
-        <f>H190*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J190" s="2">
-        <f>H190*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -8810,11 +8810,11 @@
         <v>1</v>
       </c>
       <c r="I191" s="2">
-        <f>H191*0.2</f>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="J191" s="2">
-        <f>H191*1.75</f>
+        <f t="shared" si="5"/>
         <v>1.75</v>
       </c>
     </row>
@@ -8844,11 +8844,11 @@
         <v>13</v>
       </c>
       <c r="I192" s="2">
-        <f>H192*0.2</f>
+        <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
       <c r="J192" s="2">
-        <f>H192*1.75</f>
+        <f t="shared" si="5"/>
         <v>22.75</v>
       </c>
       <c r="K192" t="s">
@@ -8878,11 +8878,11 @@
         <v>7</v>
       </c>
       <c r="I193" s="2">
-        <f>H193*0.2</f>
+        <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J193" s="2">
-        <f>H193*1.75</f>
+        <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
@@ -8912,11 +8912,11 @@
         <v>4</v>
       </c>
       <c r="I194" s="2">
-        <f>H194*0.2</f>
+        <f t="shared" ref="I194:I257" si="6">H194*0.2</f>
         <v>0.8</v>
       </c>
       <c r="J194" s="2">
-        <f>H194*1.75</f>
+        <f t="shared" ref="J194:J257" si="7">H194*1.75</f>
         <v>7</v>
       </c>
       <c r="K194" t="s">
@@ -8949,11 +8949,11 @@
         <v>11</v>
       </c>
       <c r="I195" s="2">
-        <f>H195*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J195" s="2">
-        <f>H195*1.75</f>
+        <f t="shared" si="7"/>
         <v>19.25</v>
       </c>
       <c r="K195" t="s">
@@ -8983,11 +8983,11 @@
         <v>3</v>
       </c>
       <c r="I196" s="2">
-        <f>H196*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J196" s="2">
-        <f>H196*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -9014,11 +9014,11 @@
         <v>5</v>
       </c>
       <c r="I197" s="2">
-        <f>H197*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J197" s="2">
-        <f>H197*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -9048,11 +9048,11 @@
         <v>8</v>
       </c>
       <c r="I198" s="2">
-        <f>H198*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J198" s="2">
-        <f>H198*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K198" t="s">
@@ -9085,11 +9085,11 @@
         <v>13</v>
       </c>
       <c r="I199" s="2">
-        <f>H199*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.6</v>
       </c>
       <c r="J199" s="2">
-        <f>H199*1.75</f>
+        <f t="shared" si="7"/>
         <v>22.75</v>
       </c>
       <c r="K199" t="s">
@@ -9122,11 +9122,11 @@
         <v>12</v>
       </c>
       <c r="I200" s="2">
-        <f>H200*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J200" s="2">
-        <f>H200*1.75</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="K200" t="s">
@@ -9156,11 +9156,11 @@
         <v>3</v>
       </c>
       <c r="I201" s="2">
-        <f>H201*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J201" s="2">
-        <f>H201*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -9187,11 +9187,11 @@
         <v>6</v>
       </c>
       <c r="I202" s="2">
-        <f>H202*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J202" s="2">
-        <f>H202*1.75</f>
+        <f t="shared" si="7"/>
         <v>10.5</v>
       </c>
     </row>
@@ -9218,11 +9218,11 @@
         <v>10</v>
       </c>
       <c r="I203" s="2">
-        <f>H203*0.2</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="J203" s="2">
-        <f>H203*1.75</f>
+        <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
     </row>
@@ -9252,11 +9252,11 @@
         <v>4</v>
       </c>
       <c r="I204" s="2">
-        <f>H204*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="J204" s="2">
-        <f>H204*1.75</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="K204" t="s">
@@ -9289,11 +9289,11 @@
         <v>12</v>
       </c>
       <c r="I205" s="2">
-        <f>H205*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J205" s="2">
-        <f>H205*1.75</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="K205" t="s">
@@ -9323,11 +9323,11 @@
         <v>5</v>
       </c>
       <c r="I206" s="2">
-        <f>H206*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J206" s="2">
-        <f>H206*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -9354,11 +9354,11 @@
         <v>6</v>
       </c>
       <c r="I207" s="2">
-        <f>H207*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J207" s="2">
-        <f>H207*1.75</f>
+        <f t="shared" si="7"/>
         <v>10.5</v>
       </c>
     </row>
@@ -9388,11 +9388,11 @@
         <v>18</v>
       </c>
       <c r="I208" s="2">
-        <f>H208*0.2</f>
+        <f t="shared" si="6"/>
         <v>3.6</v>
       </c>
       <c r="J208" s="2">
-        <f>H208*1.75</f>
+        <f t="shared" si="7"/>
         <v>31.5</v>
       </c>
       <c r="K208" t="s">
@@ -9425,11 +9425,11 @@
         <v>10</v>
       </c>
       <c r="I209" s="2">
-        <f>H209*0.2</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="J209" s="2">
-        <f>H209*1.75</f>
+        <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
       <c r="K209" t="s">
@@ -9462,11 +9462,11 @@
         <v>4</v>
       </c>
       <c r="I210" s="2">
-        <f>H210*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="J210" s="2">
-        <f>H210*1.75</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="K210" t="s">
@@ -9496,11 +9496,11 @@
         <v>8</v>
       </c>
       <c r="I211" s="2">
-        <f>H211*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J211" s="2">
-        <f>H211*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
@@ -9530,11 +9530,11 @@
         <v>8</v>
       </c>
       <c r="I212" s="2">
-        <f>H212*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J212" s="2">
-        <f>H212*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K212" t="s">
@@ -9564,11 +9564,11 @@
         <v>3</v>
       </c>
       <c r="I213" s="2">
-        <f>H213*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J213" s="2">
-        <f>H213*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -9598,11 +9598,11 @@
         <v>9</v>
       </c>
       <c r="I214" s="2">
-        <f>H214*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.8</v>
       </c>
       <c r="J214" s="2">
-        <f>H214*1.75</f>
+        <f t="shared" si="7"/>
         <v>15.75</v>
       </c>
       <c r="K214" t="s">
@@ -9635,11 +9635,11 @@
         <v>8</v>
       </c>
       <c r="I215" s="2">
-        <f>H215*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J215" s="2">
-        <f>H215*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K215" t="s">
@@ -9669,11 +9669,11 @@
         <v>7</v>
       </c>
       <c r="I216" s="2">
-        <f>H216*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J216" s="2">
-        <f>H216*1.75</f>
+        <f t="shared" si="7"/>
         <v>12.25</v>
       </c>
     </row>
@@ -9700,11 +9700,11 @@
         <v>2</v>
       </c>
       <c r="I217" s="2">
-        <f>H217*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="J217" s="2">
-        <f>H217*1.75</f>
+        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
     </row>
@@ -9731,11 +9731,11 @@
         <v>5</v>
       </c>
       <c r="I218" s="2">
-        <f>H218*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J218" s="2">
-        <f>H218*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -9765,11 +9765,11 @@
         <v>10</v>
       </c>
       <c r="I219" s="2">
-        <f>H219*0.2</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="J219" s="2">
-        <f>H219*1.75</f>
+        <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
       <c r="K219" t="s">
@@ -9802,11 +9802,11 @@
         <v>10</v>
       </c>
       <c r="I220" s="2">
-        <f>H220*0.2</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="J220" s="2">
-        <f>H220*1.75</f>
+        <f t="shared" si="7"/>
         <v>17.5</v>
       </c>
       <c r="K220" t="s">
@@ -9836,11 +9836,11 @@
         <v>6</v>
       </c>
       <c r="I221" s="2">
-        <f>H221*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J221" s="2">
-        <f>H221*1.75</f>
+        <f t="shared" si="7"/>
         <v>10.5</v>
       </c>
     </row>
@@ -9867,11 +9867,11 @@
         <v>26</v>
       </c>
       <c r="I222" s="2">
-        <f>H222*0.2</f>
+        <f t="shared" si="6"/>
         <v>5.2</v>
       </c>
       <c r="J222" s="2">
-        <f>H222*1.75</f>
+        <f t="shared" si="7"/>
         <v>45.5</v>
       </c>
     </row>
@@ -9898,11 +9898,11 @@
         <v>2</v>
       </c>
       <c r="I223" s="2">
-        <f>H223*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="J223" s="2">
-        <f>H223*1.75</f>
+        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
     </row>
@@ -9932,11 +9932,11 @@
         <v>18</v>
       </c>
       <c r="I224" s="2">
-        <f>H224*0.2</f>
+        <f t="shared" si="6"/>
         <v>3.6</v>
       </c>
       <c r="J224" s="2">
-        <f>H224*1.75</f>
+        <f t="shared" si="7"/>
         <v>31.5</v>
       </c>
       <c r="K224" t="s">
@@ -9969,11 +9969,11 @@
         <v>4</v>
       </c>
       <c r="I225" s="2">
-        <f>H225*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="J225" s="2">
-        <f>H225*1.75</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="K225" t="s">
@@ -10003,11 +10003,11 @@
         <v>5</v>
       </c>
       <c r="I226" s="2">
-        <f>H226*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J226" s="2">
-        <f>H226*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -10037,11 +10037,11 @@
         <v>8</v>
       </c>
       <c r="I227" s="2">
-        <f>H227*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J227" s="2">
-        <f>H227*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K227" t="s">
@@ -10071,11 +10071,11 @@
         <v>5</v>
       </c>
       <c r="I228" s="2">
-        <f>H228*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J228" s="2">
-        <f>H228*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -10102,11 +10102,11 @@
         <v>7</v>
       </c>
       <c r="I229" s="2">
-        <f>H229*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J229" s="2">
-        <f>H229*1.75</f>
+        <f t="shared" si="7"/>
         <v>12.25</v>
       </c>
     </row>
@@ -10133,11 +10133,11 @@
         <v>1</v>
       </c>
       <c r="I230" s="2">
-        <f>H230*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J230" s="2">
-        <f>H230*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10164,11 +10164,11 @@
         <v>3</v>
       </c>
       <c r="I231" s="2">
-        <f>H231*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J231" s="2">
-        <f>H231*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -10195,11 +10195,11 @@
         <v>1</v>
       </c>
       <c r="I232" s="2">
-        <f>H232*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J232" s="2">
-        <f>H232*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10229,11 +10229,11 @@
         <v>8</v>
       </c>
       <c r="I233" s="2">
-        <f>H233*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J233" s="2">
-        <f>H233*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K233" t="s">
@@ -10266,11 +10266,11 @@
         <v>8</v>
       </c>
       <c r="I234" s="2">
-        <f>H234*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J234" s="2">
-        <f>H234*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="K234" t="s">
@@ -10303,11 +10303,11 @@
         <v>28</v>
       </c>
       <c r="I235" s="2">
-        <f>H235*0.2</f>
+        <f t="shared" si="6"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="J235" s="2">
-        <f>H235*1.75</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="K235" t="s">
@@ -10337,11 +10337,11 @@
         <v>4</v>
       </c>
       <c r="I236" s="2">
-        <f>H236*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="J236" s="2">
-        <f>H236*1.75</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -10368,11 +10368,11 @@
         <v>16</v>
       </c>
       <c r="I237" s="2">
-        <f>H237*0.2</f>
+        <f t="shared" si="6"/>
         <v>3.2</v>
       </c>
       <c r="J237" s="2">
-        <f>H237*1.75</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
     </row>
@@ -10399,11 +10399,11 @@
         <v>1</v>
       </c>
       <c r="I238" s="2">
-        <f>H238*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J238" s="2">
-        <f>H238*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10433,11 +10433,11 @@
         <v>11</v>
       </c>
       <c r="I239" s="2">
-        <f>H239*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J239" s="2">
-        <f>H239*1.75</f>
+        <f t="shared" si="7"/>
         <v>19.25</v>
       </c>
       <c r="K239" t="s">
@@ -10467,11 +10467,11 @@
         <v>8</v>
       </c>
       <c r="I240" s="2">
-        <f>H240*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
       <c r="J240" s="2">
-        <f>H240*1.75</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
@@ -10498,11 +10498,11 @@
         <v>6</v>
       </c>
       <c r="I241" s="2">
-        <f>H241*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J241" s="2">
-        <f>H241*1.75</f>
+        <f t="shared" si="7"/>
         <v>10.5</v>
       </c>
     </row>
@@ -10529,11 +10529,11 @@
         <v>1</v>
       </c>
       <c r="I242" s="2">
-        <f>H242*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J242" s="2">
-        <f>H242*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10563,11 +10563,11 @@
         <v>5</v>
       </c>
       <c r="I243" s="2">
-        <f>H243*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J243" s="2">
-        <f>H243*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
       <c r="K243" t="s">
@@ -10597,11 +10597,11 @@
         <v>1</v>
       </c>
       <c r="I244" s="2">
-        <f>H244*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J244" s="2">
-        <f>H244*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10631,11 +10631,11 @@
         <v>6</v>
       </c>
       <c r="I245" s="2">
-        <f>H245*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J245" s="2">
-        <f>H245*1.75</f>
+        <f t="shared" si="7"/>
         <v>10.5</v>
       </c>
       <c r="K245" t="s">
@@ -10665,11 +10665,11 @@
         <v>5</v>
       </c>
       <c r="I246" s="2">
-        <f>H246*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J246" s="2">
-        <f>H246*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -10696,11 +10696,11 @@
         <v>4</v>
       </c>
       <c r="I247" s="2">
-        <f>H247*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="J247" s="2">
-        <f>H247*1.75</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -10727,11 +10727,11 @@
         <v>3</v>
       </c>
       <c r="I248" s="2">
-        <f>H248*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J248" s="2">
-        <f>H248*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -10758,11 +10758,11 @@
         <v>1</v>
       </c>
       <c r="I249" s="2">
-        <f>H249*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="J249" s="2">
-        <f>H249*1.75</f>
+        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
     </row>
@@ -10789,11 +10789,11 @@
         <v>3</v>
       </c>
       <c r="I250" s="2">
-        <f>H250*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J250" s="2">
-        <f>H250*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -10823,11 +10823,11 @@
         <v>11</v>
       </c>
       <c r="I251" s="2">
-        <f>H251*0.2</f>
+        <f t="shared" si="6"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J251" s="2">
-        <f>H251*1.75</f>
+        <f t="shared" si="7"/>
         <v>19.25</v>
       </c>
       <c r="K251" t="s">
@@ -10857,11 +10857,11 @@
         <v>7</v>
       </c>
       <c r="I252" s="2">
-        <f>H252*0.2</f>
+        <f t="shared" si="6"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J252" s="2">
-        <f>H252*1.75</f>
+        <f t="shared" si="7"/>
         <v>12.25</v>
       </c>
     </row>
@@ -10888,11 +10888,11 @@
         <v>2</v>
       </c>
       <c r="I253" s="2">
-        <f>H253*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="J253" s="2">
-        <f>H253*1.75</f>
+        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
     </row>
@@ -10919,11 +10919,11 @@
         <v>2</v>
       </c>
       <c r="I254" s="2">
-        <f>H254*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="J254" s="2">
-        <f>H254*1.75</f>
+        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
     </row>
@@ -10950,11 +10950,11 @@
         <v>5</v>
       </c>
       <c r="I255" s="2">
-        <f>H255*0.2</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J255" s="2">
-        <f>H255*1.75</f>
+        <f t="shared" si="7"/>
         <v>8.75</v>
       </c>
     </row>
@@ -10981,11 +10981,11 @@
         <v>3</v>
       </c>
       <c r="I256" s="2">
-        <f>H256*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J256" s="2">
-        <f>H256*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -11012,11 +11012,11 @@
         <v>3</v>
       </c>
       <c r="I257" s="2">
-        <f>H257*0.2</f>
+        <f t="shared" si="6"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J257" s="2">
-        <f>H257*1.75</f>
+        <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
     </row>
@@ -11043,11 +11043,11 @@
         <v>1</v>
       </c>
       <c r="I258" s="2">
-        <f>H258*0.2</f>
+        <f t="shared" ref="I258:I321" si="8">H258*0.2</f>
         <v>0.2</v>
       </c>
       <c r="J258" s="2">
-        <f>H258*1.75</f>
+        <f t="shared" ref="J258:J321" si="9">H258*1.75</f>
         <v>1.75</v>
       </c>
     </row>
@@ -11074,11 +11074,11 @@
         <v>1</v>
       </c>
       <c r="I259" s="2">
-        <f>H259*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J259" s="2">
-        <f>H259*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -11105,11 +11105,11 @@
         <v>2</v>
       </c>
       <c r="I260" s="2">
-        <f>H260*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.4</v>
       </c>
       <c r="J260" s="2">
-        <f>H260*1.75</f>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
     </row>
@@ -11136,11 +11136,11 @@
         <v>6</v>
       </c>
       <c r="I261" s="2">
-        <f>H261*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J261" s="2">
-        <f>H261*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -11167,11 +11167,11 @@
         <v>4</v>
       </c>
       <c r="I262" s="2">
-        <f>H262*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J262" s="2">
-        <f>H262*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -11201,11 +11201,11 @@
         <v>5</v>
       </c>
       <c r="I263" s="2">
-        <f>H263*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J263" s="2">
-        <f>H263*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
       <c r="K263" t="s">
@@ -11235,11 +11235,11 @@
         <v>9</v>
       </c>
       <c r="I264" s="2">
-        <f>H264*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.8</v>
       </c>
       <c r="J264" s="2">
-        <f>H264*1.75</f>
+        <f t="shared" si="9"/>
         <v>15.75</v>
       </c>
     </row>
@@ -11266,11 +11266,11 @@
         <v>8</v>
       </c>
       <c r="I265" s="2">
-        <f>H265*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="J265" s="2">
-        <f>H265*1.75</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
@@ -11297,11 +11297,11 @@
         <v>7</v>
       </c>
       <c r="I266" s="2">
-        <f>H266*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J266" s="2">
-        <f>H266*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
     </row>
@@ -11328,11 +11328,11 @@
         <v>27</v>
       </c>
       <c r="I267" s="2">
-        <f>H267*0.2</f>
+        <f t="shared" si="8"/>
         <v>5.4</v>
       </c>
       <c r="J267" s="2">
-        <f>H267*1.75</f>
+        <f t="shared" si="9"/>
         <v>47.25</v>
       </c>
     </row>
@@ -11362,11 +11362,11 @@
         <v>8</v>
       </c>
       <c r="I268" s="2">
-        <f>H268*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="J268" s="2">
-        <f>H268*1.75</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="K268" t="s">
@@ -11396,11 +11396,11 @@
         <v>1</v>
       </c>
       <c r="I269" s="2">
-        <f>H269*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J269" s="2">
-        <f>H269*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -11427,11 +11427,11 @@
         <v>1</v>
       </c>
       <c r="I270" s="2">
-        <f>H270*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J270" s="2">
-        <f>H270*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -11458,11 +11458,11 @@
         <v>4</v>
       </c>
       <c r="I271" s="2">
-        <f>H271*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J271" s="2">
-        <f>H271*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -11489,11 +11489,11 @@
         <v>4</v>
       </c>
       <c r="I272" s="2">
-        <f>H272*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J272" s="2">
-        <f>H272*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -11520,11 +11520,11 @@
         <v>5</v>
       </c>
       <c r="I273" s="2">
-        <f>H273*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J273" s="2">
-        <f>H273*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
     </row>
@@ -11554,11 +11554,11 @@
         <v>24</v>
       </c>
       <c r="I274" s="2">
-        <f>H274*0.2</f>
+        <f t="shared" si="8"/>
         <v>4.8000000000000007</v>
       </c>
       <c r="J274" s="2">
-        <f>H274*1.75</f>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="K274" t="s">
@@ -11591,11 +11591,11 @@
         <v>17</v>
       </c>
       <c r="I275" s="2">
-        <f>H275*0.2</f>
+        <f t="shared" si="8"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J275" s="2">
-        <f>H275*1.75</f>
+        <f t="shared" si="9"/>
         <v>29.75</v>
       </c>
       <c r="K275" t="s">
@@ -11625,11 +11625,11 @@
         <v>9</v>
       </c>
       <c r="I276" s="2">
-        <f>H276*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.8</v>
       </c>
       <c r="J276" s="2">
-        <f>H276*1.75</f>
+        <f t="shared" si="9"/>
         <v>15.75</v>
       </c>
     </row>
@@ -11656,11 +11656,11 @@
         <v>9</v>
       </c>
       <c r="I277" s="2">
-        <f>H277*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.8</v>
       </c>
       <c r="J277" s="2">
-        <f>H277*1.75</f>
+        <f t="shared" si="9"/>
         <v>15.75</v>
       </c>
     </row>
@@ -11690,11 +11690,11 @@
         <v>8</v>
       </c>
       <c r="I278" s="2">
-        <f>H278*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="J278" s="2">
-        <f>H278*1.75</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="K278" t="s">
@@ -11727,11 +11727,11 @@
         <v>6</v>
       </c>
       <c r="I279" s="2">
-        <f>H279*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J279" s="2">
-        <f>H279*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
       <c r="K279" t="s">
@@ -11764,11 +11764,11 @@
         <v>8</v>
       </c>
       <c r="I280" s="2">
-        <f>H280*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="J280" s="2">
-        <f>H280*1.75</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="K280" t="s">
@@ -11798,11 +11798,11 @@
         <v>3</v>
       </c>
       <c r="I281" s="2">
-        <f>H281*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J281" s="2">
-        <f>H281*1.75</f>
+        <f t="shared" si="9"/>
         <v>5.25</v>
       </c>
     </row>
@@ -11829,11 +11829,11 @@
         <v>2</v>
       </c>
       <c r="I282" s="2">
-        <f>H282*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.4</v>
       </c>
       <c r="J282" s="2">
-        <f>H282*1.75</f>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
     </row>
@@ -11860,11 +11860,11 @@
         <v>4</v>
       </c>
       <c r="I283" s="2">
-        <f>H283*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J283" s="2">
-        <f>H283*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -11891,11 +11891,11 @@
         <v>1</v>
       </c>
       <c r="I284" s="2">
-        <f>H284*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J284" s="2">
-        <f>H284*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -11922,11 +11922,11 @@
         <v>10</v>
       </c>
       <c r="I285" s="2">
-        <f>H285*0.2</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J285" s="2">
-        <f>H285*1.75</f>
+        <f t="shared" si="9"/>
         <v>17.5</v>
       </c>
     </row>
@@ -11953,11 +11953,11 @@
         <v>9</v>
       </c>
       <c r="I286" s="2">
-        <f>H286*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.8</v>
       </c>
       <c r="J286" s="2">
-        <f>H286*1.75</f>
+        <f t="shared" si="9"/>
         <v>15.75</v>
       </c>
     </row>
@@ -11984,11 +11984,11 @@
         <v>5</v>
       </c>
       <c r="I287" s="2">
-        <f>H287*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J287" s="2">
-        <f>H287*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
     </row>
@@ -12015,11 +12015,11 @@
         <v>6</v>
       </c>
       <c r="I288" s="2">
-        <f>H288*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J288" s="2">
-        <f>H288*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -12046,11 +12046,11 @@
         <v>1</v>
       </c>
       <c r="I289" s="2">
-        <f>H289*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J289" s="2">
-        <f>H289*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -12080,11 +12080,11 @@
         <v>13</v>
       </c>
       <c r="I290" s="2">
-        <f>H290*0.2</f>
+        <f t="shared" si="8"/>
         <v>2.6</v>
       </c>
       <c r="J290" s="2">
-        <f>H290*1.75</f>
+        <f t="shared" si="9"/>
         <v>22.75</v>
       </c>
       <c r="K290" t="s">
@@ -12114,11 +12114,11 @@
         <v>6</v>
       </c>
       <c r="I291" s="2">
-        <f>H291*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J291" s="2">
-        <f>H291*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -12145,11 +12145,11 @@
         <v>6</v>
       </c>
       <c r="I292" s="2">
-        <f>H292*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J292" s="2">
-        <f>H292*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -12176,11 +12176,11 @@
         <v>5</v>
       </c>
       <c r="I293" s="2">
-        <f>H293*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J293" s="2">
-        <f>H293*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
     </row>
@@ -12210,11 +12210,11 @@
         <v>4</v>
       </c>
       <c r="I294" s="2">
-        <f>H294*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J294" s="2">
-        <f>H294*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="K294" t="s">
@@ -12247,11 +12247,11 @@
         <v>5</v>
       </c>
       <c r="I295" s="2">
-        <f>H295*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J295" s="2">
-        <f>H295*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
       <c r="K295" t="s">
@@ -12281,11 +12281,11 @@
         <v>2</v>
       </c>
       <c r="I296" s="2">
-        <f>H296*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.4</v>
       </c>
       <c r="J296" s="2">
-        <f>H296*1.75</f>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
     </row>
@@ -12312,11 +12312,11 @@
         <v>4</v>
       </c>
       <c r="I297" s="2">
-        <f>H297*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J297" s="2">
-        <f>H297*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -12343,11 +12343,11 @@
         <v>7</v>
       </c>
       <c r="I298" s="2">
-        <f>H298*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J298" s="2">
-        <f>H298*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
     </row>
@@ -12377,11 +12377,11 @@
         <v>7</v>
       </c>
       <c r="I299" s="2">
-        <f>H299*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J299" s="2">
-        <f>H299*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
       <c r="K299" t="s">
@@ -12411,11 +12411,11 @@
         <v>7</v>
       </c>
       <c r="I300" s="2">
-        <f>H300*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J300" s="2">
-        <f>H300*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
     </row>
@@ -12445,11 +12445,11 @@
         <v>10</v>
       </c>
       <c r="I301" s="2">
-        <f>H301*0.2</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J301" s="2">
-        <f>H301*1.75</f>
+        <f t="shared" si="9"/>
         <v>17.5</v>
       </c>
       <c r="K301" t="s">
@@ -12479,11 +12479,11 @@
         <v>1</v>
       </c>
       <c r="I302" s="2">
-        <f>H302*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J302" s="2">
-        <f>H302*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -12510,11 +12510,11 @@
         <v>4</v>
       </c>
       <c r="I303" s="2">
-        <f>H303*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J303" s="2">
-        <f>H303*1.75</f>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -12541,11 +12541,11 @@
         <v>6</v>
       </c>
       <c r="I304" s="2">
-        <f>H304*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J304" s="2">
-        <f>H304*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -12572,11 +12572,11 @@
         <v>1</v>
       </c>
       <c r="I305" s="2">
-        <f>H305*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J305" s="2">
-        <f>H305*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -12603,11 +12603,11 @@
         <v>6</v>
       </c>
       <c r="I306" s="2">
-        <f>H306*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J306" s="2">
-        <f>H306*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
     </row>
@@ -12637,11 +12637,11 @@
         <v>8</v>
       </c>
       <c r="I307" s="2">
-        <f>H307*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
       <c r="J307" s="2">
-        <f>H307*1.75</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="K307" t="s">
@@ -12674,11 +12674,11 @@
         <v>7</v>
       </c>
       <c r="I308" s="2">
-        <f>H308*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J308" s="2">
-        <f>H308*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
       <c r="K308" t="s">
@@ -12711,11 +12711,11 @@
         <v>6</v>
       </c>
       <c r="I309" s="2">
-        <f>H309*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J309" s="2">
-        <f>H309*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
       <c r="K309" t="s">
@@ -12745,11 +12745,11 @@
         <v>1</v>
       </c>
       <c r="I310" s="2">
-        <f>H310*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J310" s="2">
-        <f>H310*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -12776,11 +12776,11 @@
         <v>7</v>
       </c>
       <c r="I311" s="2">
-        <f>H311*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J311" s="2">
-        <f>H311*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
     </row>
@@ -12807,11 +12807,11 @@
         <v>3</v>
       </c>
       <c r="I312" s="2">
-        <f>H312*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J312" s="2">
-        <f>H312*1.75</f>
+        <f t="shared" si="9"/>
         <v>5.25</v>
       </c>
     </row>
@@ -12838,11 +12838,11 @@
         <v>16</v>
       </c>
       <c r="I313" s="2">
-        <f>H313*0.2</f>
+        <f t="shared" si="8"/>
         <v>3.2</v>
       </c>
       <c r="J313" s="2">
-        <f>H313*1.75</f>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
     </row>
@@ -12869,11 +12869,11 @@
         <v>5</v>
       </c>
       <c r="I314" s="2">
-        <f>H314*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J314" s="2">
-        <f>H314*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
     </row>
@@ -12900,11 +12900,11 @@
         <v>5</v>
       </c>
       <c r="I315" s="2">
-        <f>H315*0.2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J315" s="2">
-        <f>H315*1.75</f>
+        <f t="shared" si="9"/>
         <v>8.75</v>
       </c>
     </row>
@@ -12931,11 +12931,11 @@
         <v>7</v>
       </c>
       <c r="I316" s="2">
-        <f>H316*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J316" s="2">
-        <f>H316*1.75</f>
+        <f t="shared" si="9"/>
         <v>12.25</v>
       </c>
     </row>
@@ -12962,11 +12962,11 @@
         <v>2</v>
       </c>
       <c r="I317" s="2">
-        <f>H317*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.4</v>
       </c>
       <c r="J317" s="2">
-        <f>H317*1.75</f>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
     </row>
@@ -12993,11 +12993,11 @@
         <v>1</v>
       </c>
       <c r="I318" s="2">
-        <f>H318*0.2</f>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="J318" s="2">
-        <f>H318*1.75</f>
+        <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
     </row>
@@ -13027,11 +13027,11 @@
         <v>10</v>
       </c>
       <c r="I319" s="2">
-        <f>H319*0.2</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J319" s="2">
-        <f>H319*1.75</f>
+        <f t="shared" si="9"/>
         <v>17.5</v>
       </c>
       <c r="K319" t="s">
@@ -13064,11 +13064,11 @@
         <v>9</v>
       </c>
       <c r="I320" s="2">
-        <f>H320*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.8</v>
       </c>
       <c r="J320" s="2">
-        <f>H320*1.75</f>
+        <f t="shared" si="9"/>
         <v>15.75</v>
       </c>
       <c r="K320" t="s">
@@ -13101,11 +13101,11 @@
         <v>6</v>
       </c>
       <c r="I321" s="2">
-        <f>H321*0.2</f>
+        <f t="shared" si="8"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J321" s="2">
-        <f>H321*1.75</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
       <c r="K321" t="s">
@@ -13135,11 +13135,11 @@
         <v>6</v>
       </c>
       <c r="I322" s="2">
-        <f>H322*0.2</f>
+        <f t="shared" ref="I322:I385" si="10">H322*0.2</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="J322" s="2">
-        <f>H322*1.75</f>
+        <f t="shared" ref="J322:J385" si="11">H322*1.75</f>
         <v>10.5</v>
       </c>
     </row>
@@ -13166,11 +13166,11 @@
         <v>1</v>
       </c>
       <c r="I323" s="2">
-        <f>H323*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J323" s="2">
-        <f>H323*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -13197,11 +13197,11 @@
         <v>1</v>
       </c>
       <c r="I324" s="2">
-        <f>H324*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J324" s="2">
-        <f>H324*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -13231,11 +13231,11 @@
         <v>8</v>
       </c>
       <c r="I325" s="2">
-        <f>H325*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
       <c r="J325" s="2">
-        <f>H325*1.75</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="K325" t="s">
@@ -13265,11 +13265,11 @@
         <v>2</v>
       </c>
       <c r="I326" s="2">
-        <f>H326*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J326" s="2">
-        <f>H326*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -13296,11 +13296,11 @@
         <v>3</v>
       </c>
       <c r="I327" s="2">
-        <f>H327*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J327" s="2">
-        <f>H327*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -13327,11 +13327,11 @@
         <v>3</v>
       </c>
       <c r="I328" s="2">
-        <f>H328*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J328" s="2">
-        <f>H328*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -13358,11 +13358,11 @@
         <v>3</v>
       </c>
       <c r="I329" s="2">
-        <f>H329*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J329" s="2">
-        <f>H329*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -13392,11 +13392,11 @@
         <v>7</v>
       </c>
       <c r="I330" s="2">
-        <f>H330*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J330" s="2">
-        <f>H330*1.75</f>
+        <f t="shared" si="11"/>
         <v>12.25</v>
       </c>
       <c r="K330" t="s">
@@ -13429,11 +13429,11 @@
         <v>11</v>
       </c>
       <c r="I331" s="2">
-        <f>H331*0.2</f>
+        <f t="shared" si="10"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J331" s="2">
-        <f>H331*1.75</f>
+        <f t="shared" si="11"/>
         <v>19.25</v>
       </c>
       <c r="K331" t="s">
@@ -13463,11 +13463,11 @@
         <v>6</v>
       </c>
       <c r="I332" s="2">
-        <f>H332*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J332" s="2">
-        <f>H332*1.75</f>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
     </row>
@@ -13497,11 +13497,11 @@
         <v>10</v>
       </c>
       <c r="I333" s="2">
-        <f>H333*0.2</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J333" s="2">
-        <f>H333*1.75</f>
+        <f t="shared" si="11"/>
         <v>17.5</v>
       </c>
       <c r="K333" t="s">
@@ -13534,11 +13534,11 @@
         <v>28</v>
       </c>
       <c r="I334" s="2">
-        <f>H334*0.2</f>
+        <f t="shared" si="10"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="J334" s="2">
-        <f>H334*1.75</f>
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
       <c r="K334" t="s">
@@ -13568,11 +13568,11 @@
         <v>2</v>
       </c>
       <c r="I335" s="2">
-        <f>H335*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J335" s="2">
-        <f>H335*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -13602,11 +13602,11 @@
         <v>11</v>
       </c>
       <c r="I336" s="2">
-        <f>H336*0.2</f>
+        <f t="shared" si="10"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J336" s="2">
-        <f>H336*1.75</f>
+        <f t="shared" si="11"/>
         <v>19.25</v>
       </c>
       <c r="K336" t="s">
@@ -13636,11 +13636,11 @@
         <v>1</v>
       </c>
       <c r="I337" s="2">
-        <f>H337*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J337" s="2">
-        <f>H337*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -13667,11 +13667,11 @@
         <v>5</v>
       </c>
       <c r="I338" s="2">
-        <f>H338*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J338" s="2">
-        <f>H338*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
     </row>
@@ -13698,11 +13698,11 @@
         <v>3</v>
       </c>
       <c r="I339" s="2">
-        <f>H339*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J339" s="2">
-        <f>H339*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -13732,11 +13732,11 @@
         <v>5</v>
       </c>
       <c r="I340" s="2">
-        <f>H340*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J340" s="2">
-        <f>H340*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
       <c r="K340" t="s">
@@ -13766,11 +13766,11 @@
         <v>2</v>
       </c>
       <c r="I341" s="2">
-        <f>H341*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J341" s="2">
-        <f>H341*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -13797,11 +13797,11 @@
         <v>2</v>
       </c>
       <c r="I342" s="2">
-        <f>H342*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J342" s="2">
-        <f>H342*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -13831,11 +13831,11 @@
         <v>6</v>
       </c>
       <c r="I343" s="2">
-        <f>H343*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J343" s="2">
-        <f>H343*1.75</f>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
       <c r="K343" t="s">
@@ -13865,11 +13865,11 @@
         <v>2</v>
       </c>
       <c r="I344" s="2">
-        <f>H344*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J344" s="2">
-        <f>H344*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -13896,11 +13896,11 @@
         <v>8</v>
       </c>
       <c r="I345" s="2">
-        <f>H345*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
       <c r="J345" s="2">
-        <f>H345*1.75</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
     </row>
@@ -13930,11 +13930,11 @@
         <v>17</v>
       </c>
       <c r="I346" s="2">
-        <f>H346*0.2</f>
+        <f t="shared" si="10"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="J346" s="2">
-        <f>H346*1.75</f>
+        <f t="shared" si="11"/>
         <v>29.75</v>
       </c>
       <c r="K346" t="s">
@@ -13967,11 +13967,11 @@
         <v>7</v>
       </c>
       <c r="I347" s="2">
-        <f>H347*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J347" s="2">
-        <f>H347*1.75</f>
+        <f t="shared" si="11"/>
         <v>12.25</v>
       </c>
       <c r="K347" t="s">
@@ -14001,11 +14001,11 @@
         <v>2</v>
       </c>
       <c r="I348" s="2">
-        <f>H348*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J348" s="2">
-        <f>H348*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -14032,11 +14032,11 @@
         <v>2</v>
       </c>
       <c r="I349" s="2">
-        <f>H349*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J349" s="2">
-        <f>H349*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -14066,11 +14066,11 @@
         <v>13</v>
       </c>
       <c r="I350" s="2">
-        <f>H350*0.2</f>
+        <f t="shared" si="10"/>
         <v>2.6</v>
       </c>
       <c r="J350" s="2">
-        <f>H350*1.75</f>
+        <f t="shared" si="11"/>
         <v>22.75</v>
       </c>
       <c r="K350" t="s">
@@ -14103,11 +14103,11 @@
         <v>16</v>
       </c>
       <c r="I351" s="2">
-        <f>H351*0.2</f>
+        <f t="shared" si="10"/>
         <v>3.2</v>
       </c>
       <c r="J351" s="2">
-        <f>H351*1.75</f>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="K351" t="s">
@@ -14140,11 +14140,11 @@
         <v>12</v>
       </c>
       <c r="I352" s="2">
-        <f>H352*0.2</f>
+        <f t="shared" si="10"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J352" s="2">
-        <f>H352*1.75</f>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="K352" t="s">
@@ -14174,11 +14174,11 @@
         <v>2</v>
       </c>
       <c r="I353" s="2">
-        <f>H353*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J353" s="2">
-        <f>H353*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -14205,11 +14205,11 @@
         <v>2</v>
       </c>
       <c r="I354" s="2">
-        <f>H354*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J354" s="2">
-        <f>H354*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -14236,11 +14236,11 @@
         <v>1</v>
       </c>
       <c r="I355" s="2">
-        <f>H355*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J355" s="2">
-        <f>H355*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -14270,11 +14270,11 @@
         <v>4</v>
       </c>
       <c r="I356" s="2">
-        <f>H356*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="J356" s="2">
-        <f>H356*1.75</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="K356" t="s">
@@ -14304,11 +14304,11 @@
         <v>3</v>
       </c>
       <c r="I357" s="2">
-        <f>H357*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J357" s="2">
-        <f>H357*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -14338,11 +14338,11 @@
         <v>6</v>
       </c>
       <c r="I358" s="2">
-        <f>H358*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J358" s="2">
-        <f>H358*1.75</f>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
       <c r="K358" t="s">
@@ -14372,11 +14372,11 @@
         <v>7</v>
       </c>
       <c r="I359" s="2">
-        <f>H359*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J359" s="2">
-        <f>H359*1.75</f>
+        <f t="shared" si="11"/>
         <v>12.25</v>
       </c>
     </row>
@@ -14403,11 +14403,11 @@
         <v>5</v>
       </c>
       <c r="I360" s="2">
-        <f>H360*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J360" s="2">
-        <f>H360*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
     </row>
@@ -14434,11 +14434,11 @@
         <v>5</v>
       </c>
       <c r="I361" s="2">
-        <f>H361*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J361" s="2">
-        <f>H361*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
     </row>
@@ -14465,11 +14465,11 @@
         <v>4</v>
       </c>
       <c r="I362" s="2">
-        <f>H362*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="J362" s="2">
-        <f>H362*1.75</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -14499,11 +14499,11 @@
         <v>5</v>
       </c>
       <c r="I363" s="2">
-        <f>H363*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J363" s="2">
-        <f>H363*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
       <c r="K363" t="s">
@@ -14536,11 +14536,11 @@
         <v>3</v>
       </c>
       <c r="I364" s="2">
-        <f>H364*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J364" s="2">
-        <f>H364*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
       <c r="K364" t="s">
@@ -14570,11 +14570,11 @@
         <v>4</v>
       </c>
       <c r="I365" s="2">
-        <f>H365*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="J365" s="2">
-        <f>H365*1.75</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -14604,11 +14604,11 @@
         <v>20</v>
       </c>
       <c r="I366" s="2">
-        <f>H366*0.2</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J366" s="2">
-        <f>H366*1.75</f>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
       <c r="K366" t="s">
@@ -14641,11 +14641,11 @@
         <v>15</v>
       </c>
       <c r="I367" s="2">
-        <f>H367*0.2</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J367" s="2">
-        <f>H367*1.75</f>
+        <f t="shared" si="11"/>
         <v>26.25</v>
       </c>
       <c r="K367" t="s">
@@ -14675,11 +14675,11 @@
         <v>1</v>
       </c>
       <c r="I368" s="2">
-        <f>H368*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J368" s="2">
-        <f>H368*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -14706,11 +14706,11 @@
         <v>5</v>
       </c>
       <c r="I369" s="2">
-        <f>H369*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J369" s="2">
-        <f>H369*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
     </row>
@@ -14737,11 +14737,11 @@
         <v>1</v>
       </c>
       <c r="I370" s="2">
-        <f>H370*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J370" s="2">
-        <f>H370*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -14768,11 +14768,11 @@
         <v>6</v>
       </c>
       <c r="I371" s="2">
-        <f>H371*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J371" s="2">
-        <f>H371*1.75</f>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
     </row>
@@ -14802,11 +14802,11 @@
         <v>5</v>
       </c>
       <c r="I372" s="2">
-        <f>H372*0.2</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J372" s="2">
-        <f>H372*1.75</f>
+        <f t="shared" si="11"/>
         <v>8.75</v>
       </c>
       <c r="K372" t="s">
@@ -14839,11 +14839,11 @@
         <v>8</v>
       </c>
       <c r="I373" s="2">
-        <f>H373*0.2</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
       <c r="J373" s="2">
-        <f>H373*1.75</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="K373" t="s">
@@ -14876,11 +14876,11 @@
         <v>16</v>
       </c>
       <c r="I374" s="2">
-        <f>H374*0.2</f>
+        <f t="shared" si="10"/>
         <v>3.2</v>
       </c>
       <c r="J374" s="2">
-        <f>H374*1.75</f>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="K374" t="s">
@@ -14910,11 +14910,11 @@
         <v>3</v>
       </c>
       <c r="I375" s="2">
-        <f>H375*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J375" s="2">
-        <f>H375*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -14941,11 +14941,11 @@
         <v>3</v>
       </c>
       <c r="I376" s="2">
-        <f>H376*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J376" s="2">
-        <f>H376*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -14975,11 +14975,11 @@
         <v>18</v>
       </c>
       <c r="I377" s="2">
-        <f>H377*0.2</f>
+        <f t="shared" si="10"/>
         <v>3.6</v>
       </c>
       <c r="J377" s="2">
-        <f>H377*1.75</f>
+        <f t="shared" si="11"/>
         <v>31.5</v>
       </c>
       <c r="K377" t="s">
@@ -15012,11 +15012,11 @@
         <v>4</v>
       </c>
       <c r="I378" s="2">
-        <f>H378*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="J378" s="2">
-        <f>H378*1.75</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="K378" t="s">
@@ -15046,11 +15046,11 @@
         <v>4</v>
       </c>
       <c r="I379" s="2">
-        <f>H379*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
       <c r="J379" s="2">
-        <f>H379*1.75</f>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -15080,11 +15080,11 @@
         <v>11</v>
       </c>
       <c r="I380" s="2">
-        <f>H380*0.2</f>
+        <f t="shared" si="10"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J380" s="2">
-        <f>H380*1.75</f>
+        <f t="shared" si="11"/>
         <v>19.25</v>
       </c>
       <c r="K380" t="s">
@@ -15114,11 +15114,11 @@
         <v>3</v>
       </c>
       <c r="I381" s="2">
-        <f>H381*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J381" s="2">
-        <f>H381*1.75</f>
+        <f t="shared" si="11"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15145,11 +15145,11 @@
         <v>2</v>
       </c>
       <c r="I382" s="2">
-        <f>H382*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="J382" s="2">
-        <f>H382*1.75</f>
+        <f t="shared" si="11"/>
         <v>3.5</v>
       </c>
     </row>
@@ -15176,11 +15176,11 @@
         <v>1</v>
       </c>
       <c r="I383" s="2">
-        <f>H383*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J383" s="2">
-        <f>H383*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15207,11 +15207,11 @@
         <v>1</v>
       </c>
       <c r="I384" s="2">
-        <f>H384*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J384" s="2">
-        <f>H384*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15238,11 +15238,11 @@
         <v>1</v>
       </c>
       <c r="I385" s="2">
-        <f>H385*0.2</f>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="J385" s="2">
-        <f>H385*1.75</f>
+        <f t="shared" si="11"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15269,11 +15269,11 @@
         <v>1</v>
       </c>
       <c r="I386" s="2">
-        <f>H386*0.2</f>
+        <f t="shared" ref="I386:I449" si="12">H386*0.2</f>
         <v>0.2</v>
       </c>
       <c r="J386" s="2">
-        <f>H386*1.75</f>
+        <f t="shared" ref="J386:J449" si="13">H386*1.75</f>
         <v>1.75</v>
       </c>
     </row>
@@ -15300,11 +15300,11 @@
         <v>4</v>
       </c>
       <c r="I387" s="2">
-        <f>H387*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J387" s="2">
-        <f>H387*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
     </row>
@@ -15331,11 +15331,11 @@
         <v>1</v>
       </c>
       <c r="I388" s="2">
-        <f>H388*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J388" s="2">
-        <f>H388*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15362,11 +15362,11 @@
         <v>1</v>
       </c>
       <c r="I389" s="2">
-        <f>H389*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J389" s="2">
-        <f>H389*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15393,11 +15393,11 @@
         <v>1</v>
       </c>
       <c r="I390" s="2">
-        <f>H390*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J390" s="2">
-        <f>H390*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15427,11 +15427,11 @@
         <v>3</v>
       </c>
       <c r="I391" s="2">
-        <f>H391*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J391" s="2">
-        <f>H391*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
       <c r="K391" t="s">
@@ -15464,11 +15464,11 @@
         <v>16</v>
       </c>
       <c r="I392" s="2">
-        <f>H392*0.2</f>
+        <f t="shared" si="12"/>
         <v>3.2</v>
       </c>
       <c r="J392" s="2">
-        <f>H392*1.75</f>
+        <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="K392" t="s">
@@ -15498,11 +15498,11 @@
         <v>1</v>
       </c>
       <c r="I393" s="2">
-        <f>H393*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J393" s="2">
-        <f>H393*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15529,11 +15529,11 @@
         <v>2</v>
       </c>
       <c r="I394" s="2">
-        <f>H394*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="J394" s="2">
-        <f>H394*1.75</f>
+        <f t="shared" si="13"/>
         <v>3.5</v>
       </c>
     </row>
@@ -15560,11 +15560,11 @@
         <v>6</v>
       </c>
       <c r="I395" s="2">
-        <f>H395*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J395" s="2">
-        <f>H395*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
     </row>
@@ -15591,11 +15591,11 @@
         <v>1</v>
       </c>
       <c r="I396" s="2">
-        <f>H396*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J396" s="2">
-        <f>H396*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -15625,11 +15625,11 @@
         <v>4</v>
       </c>
       <c r="I397" s="2">
-        <f>H397*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J397" s="2">
-        <f>H397*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="K397" t="s">
@@ -15659,11 +15659,11 @@
         <v>3</v>
       </c>
       <c r="I398" s="2">
-        <f>H398*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J398" s="2">
-        <f>H398*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15690,11 +15690,11 @@
         <v>3</v>
       </c>
       <c r="I399" s="2">
-        <f>H399*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J399" s="2">
-        <f>H399*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15721,11 +15721,11 @@
         <v>3</v>
       </c>
       <c r="I400" s="2">
-        <f>H400*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J400" s="2">
-        <f>H400*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15755,11 +15755,11 @@
         <v>7</v>
       </c>
       <c r="I401" s="2">
-        <f>H401*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J401" s="2">
-        <f>H401*1.75</f>
+        <f t="shared" si="13"/>
         <v>12.25</v>
       </c>
       <c r="K401" t="s">
@@ -15789,11 +15789,11 @@
         <v>5</v>
       </c>
       <c r="I402" s="2">
-        <f>H402*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J402" s="2">
-        <f>H402*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -15823,11 +15823,11 @@
         <v>6</v>
       </c>
       <c r="I403" s="2">
-        <f>H403*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J403" s="2">
-        <f>H403*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
       <c r="K403" t="s">
@@ -15860,11 +15860,11 @@
         <v>8</v>
       </c>
       <c r="I404" s="2">
-        <f>H404*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.6</v>
       </c>
       <c r="J404" s="2">
-        <f>H404*1.75</f>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="K404" t="s">
@@ -15894,11 +15894,11 @@
         <v>3</v>
       </c>
       <c r="I405" s="2">
-        <f>H405*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J405" s="2">
-        <f>H405*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15925,11 +15925,11 @@
         <v>3</v>
       </c>
       <c r="I406" s="2">
-        <f>H406*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J406" s="2">
-        <f>H406*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -15956,11 +15956,11 @@
         <v>4</v>
       </c>
       <c r="I407" s="2">
-        <f>H407*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J407" s="2">
-        <f>H407*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
     </row>
@@ -15987,11 +15987,11 @@
         <v>1</v>
       </c>
       <c r="I408" s="2">
-        <f>H408*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J408" s="2">
-        <f>H408*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16018,11 +16018,11 @@
         <v>2</v>
       </c>
       <c r="I409" s="2">
-        <f>H409*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="J409" s="2">
-        <f>H409*1.75</f>
+        <f t="shared" si="13"/>
         <v>3.5</v>
       </c>
     </row>
@@ -16052,11 +16052,11 @@
         <v>6</v>
       </c>
       <c r="I410" s="2">
-        <f>H410*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J410" s="2">
-        <f>H410*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
       <c r="K410" t="s">
@@ -16086,11 +16086,11 @@
         <v>6</v>
       </c>
       <c r="I411" s="2">
-        <f>H411*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J411" s="2">
-        <f>H411*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
     </row>
@@ -16117,11 +16117,11 @@
         <v>4</v>
       </c>
       <c r="I412" s="2">
-        <f>H412*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J412" s="2">
-        <f>H412*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
     </row>
@@ -16148,11 +16148,11 @@
         <v>1</v>
       </c>
       <c r="I413" s="2">
-        <f>H413*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J413" s="2">
-        <f>H413*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16179,11 +16179,11 @@
         <v>4</v>
       </c>
       <c r="I414" s="2">
-        <f>H414*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J414" s="2">
-        <f>H414*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
     </row>
@@ -16210,11 +16210,11 @@
         <v>3</v>
       </c>
       <c r="I415" s="2">
-        <f>H415*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J415" s="2">
-        <f>H415*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -16241,11 +16241,11 @@
         <v>6</v>
       </c>
       <c r="I416" s="2">
-        <f>H416*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J416" s="2">
-        <f>H416*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
     </row>
@@ -16272,11 +16272,11 @@
         <v>1</v>
       </c>
       <c r="I417" s="2">
-        <f>H417*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J417" s="2">
-        <f>H417*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16303,11 +16303,11 @@
         <v>7</v>
       </c>
       <c r="I418" s="2">
-        <f>H418*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J418" s="2">
-        <f>H418*1.75</f>
+        <f t="shared" si="13"/>
         <v>12.25</v>
       </c>
     </row>
@@ -16334,11 +16334,11 @@
         <v>1</v>
       </c>
       <c r="I419" s="2">
-        <f>H419*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J419" s="2">
-        <f>H419*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16365,11 +16365,11 @@
         <v>6</v>
       </c>
       <c r="I420" s="2">
-        <f>H420*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J420" s="2">
-        <f>H420*1.75</f>
+        <f t="shared" si="13"/>
         <v>10.5</v>
       </c>
     </row>
@@ -16396,11 +16396,11 @@
         <v>4</v>
       </c>
       <c r="I421" s="2">
-        <f>H421*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="J421" s="2">
-        <f>H421*1.75</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
     </row>
@@ -16427,11 +16427,11 @@
         <v>9</v>
       </c>
       <c r="I422" s="2">
-        <f>H422*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.8</v>
       </c>
       <c r="J422" s="2">
-        <f>H422*1.75</f>
+        <f t="shared" si="13"/>
         <v>15.75</v>
       </c>
     </row>
@@ -16461,11 +16461,11 @@
         <v>13</v>
       </c>
       <c r="I423" s="2">
-        <f>H423*0.2</f>
+        <f t="shared" si="12"/>
         <v>2.6</v>
       </c>
       <c r="J423" s="2">
-        <f>H423*1.75</f>
+        <f t="shared" si="13"/>
         <v>22.75</v>
       </c>
       <c r="K423" t="s">
@@ -16495,11 +16495,11 @@
         <v>1</v>
       </c>
       <c r="I424" s="2">
-        <f>H424*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J424" s="2">
-        <f>H424*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16526,11 +16526,11 @@
         <v>5</v>
       </c>
       <c r="I425" s="2">
-        <f>H425*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J425" s="2">
-        <f>H425*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -16557,11 +16557,11 @@
         <v>1</v>
       </c>
       <c r="I426" s="2">
-        <f>H426*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J426" s="2">
-        <f>H426*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16588,11 +16588,11 @@
         <v>5</v>
       </c>
       <c r="I427" s="2">
-        <f>H427*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J427" s="2">
-        <f>H427*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -16619,11 +16619,11 @@
         <v>2</v>
       </c>
       <c r="I428" s="2">
-        <f>H428*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
       <c r="J428" s="2">
-        <f>H428*1.75</f>
+        <f t="shared" si="13"/>
         <v>3.5</v>
       </c>
     </row>
@@ -16650,11 +16650,11 @@
         <v>8</v>
       </c>
       <c r="I429" s="2">
-        <f>H429*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.6</v>
       </c>
       <c r="J429" s="2">
-        <f>H429*1.75</f>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
@@ -16681,11 +16681,11 @@
         <v>1</v>
       </c>
       <c r="I430" s="2">
-        <f>H430*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J430" s="2">
-        <f>H430*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16712,11 +16712,11 @@
         <v>1</v>
       </c>
       <c r="I431" s="2">
-        <f>H431*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J431" s="2">
-        <f>H431*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16743,11 +16743,11 @@
         <v>5</v>
       </c>
       <c r="I432" s="2">
-        <f>H432*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J432" s="2">
-        <f>H432*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -16774,11 +16774,11 @@
         <v>3</v>
       </c>
       <c r="I433" s="2">
-        <f>H433*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J433" s="2">
-        <f>H433*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -16805,11 +16805,11 @@
         <v>1</v>
       </c>
       <c r="I434" s="2">
-        <f>H434*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J434" s="2">
-        <f>H434*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16836,11 +16836,11 @@
         <v>1</v>
       </c>
       <c r="I435" s="2">
-        <f>H435*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J435" s="2">
-        <f>H435*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -16867,11 +16867,11 @@
         <v>9</v>
       </c>
       <c r="I436" s="2">
-        <f>H436*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.8</v>
       </c>
       <c r="J436" s="2">
-        <f>H436*1.75</f>
+        <f t="shared" si="13"/>
         <v>15.75</v>
       </c>
     </row>
@@ -16898,11 +16898,11 @@
         <v>3</v>
       </c>
       <c r="I437" s="2">
-        <f>H437*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J437" s="2">
-        <f>H437*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -16932,11 +16932,11 @@
         <v>15</v>
       </c>
       <c r="I438" s="2">
-        <f>H438*0.2</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="J438" s="2">
-        <f>H438*1.75</f>
+        <f t="shared" si="13"/>
         <v>26.25</v>
       </c>
       <c r="K438" t="s">
@@ -16969,11 +16969,11 @@
         <v>1</v>
       </c>
       <c r="I439" s="2">
-        <f>H439*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J439" s="2">
-        <f>H439*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
       <c r="K439" t="s">
@@ -17003,11 +17003,11 @@
         <v>1</v>
       </c>
       <c r="I440" s="2">
-        <f>H440*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J440" s="2">
-        <f>H440*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17034,11 +17034,11 @@
         <v>1</v>
       </c>
       <c r="I441" s="2">
-        <f>H441*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J441" s="2">
-        <f>H441*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17065,11 +17065,11 @@
         <v>3</v>
       </c>
       <c r="I442" s="2">
-        <f>H442*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J442" s="2">
-        <f>H442*1.75</f>
+        <f t="shared" si="13"/>
         <v>5.25</v>
       </c>
     </row>
@@ -17096,11 +17096,11 @@
         <v>1</v>
       </c>
       <c r="I443" s="2">
-        <f>H443*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J443" s="2">
-        <f>H443*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17127,11 +17127,11 @@
         <v>1</v>
       </c>
       <c r="I444" s="2">
-        <f>H444*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J444" s="2">
-        <f>H444*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17158,11 +17158,11 @@
         <v>1</v>
       </c>
       <c r="I445" s="2">
-        <f>H445*0.2</f>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="J445" s="2">
-        <f>H445*1.75</f>
+        <f t="shared" si="13"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17189,11 +17189,11 @@
         <v>5</v>
       </c>
       <c r="I446" s="2">
-        <f>H446*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J446" s="2">
-        <f>H446*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -17220,11 +17220,11 @@
         <v>7</v>
       </c>
       <c r="I447" s="2">
-        <f>H447*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J447" s="2">
-        <f>H447*1.75</f>
+        <f t="shared" si="13"/>
         <v>12.25</v>
       </c>
     </row>
@@ -17251,11 +17251,11 @@
         <v>7</v>
       </c>
       <c r="I448" s="2">
-        <f>H448*0.2</f>
+        <f t="shared" si="12"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J448" s="2">
-        <f>H448*1.75</f>
+        <f t="shared" si="13"/>
         <v>12.25</v>
       </c>
     </row>
@@ -17282,11 +17282,11 @@
         <v>5</v>
       </c>
       <c r="I449" s="2">
-        <f>H449*0.2</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J449" s="2">
-        <f>H449*1.75</f>
+        <f t="shared" si="13"/>
         <v>8.75</v>
       </c>
     </row>
@@ -17313,11 +17313,11 @@
         <v>2</v>
       </c>
       <c r="I450" s="2">
-        <f>H450*0.2</f>
+        <f t="shared" ref="I450:I513" si="14">H450*0.2</f>
         <v>0.4</v>
       </c>
       <c r="J450" s="2">
-        <f>H450*1.75</f>
+        <f t="shared" ref="J450:J512" si="15">H450*1.75</f>
         <v>3.5</v>
       </c>
     </row>
@@ -17344,11 +17344,11 @@
         <v>7</v>
       </c>
       <c r="I451" s="2">
-        <f>H451*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J451" s="2">
-        <f>H451*1.75</f>
+        <f t="shared" si="15"/>
         <v>12.25</v>
       </c>
     </row>
@@ -17375,11 +17375,11 @@
         <v>2</v>
       </c>
       <c r="I452" s="2">
-        <f>H452*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J452" s="2">
-        <f>H452*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -17406,11 +17406,11 @@
         <v>12</v>
       </c>
       <c r="I453" s="2">
-        <f>H453*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="J453" s="2">
-        <f>H453*1.75</f>
+        <f t="shared" si="15"/>
         <v>21</v>
       </c>
     </row>
@@ -17437,11 +17437,11 @@
         <v>7</v>
       </c>
       <c r="I454" s="2">
-        <f>H454*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J454" s="2">
-        <f>H454*1.75</f>
+        <f t="shared" si="15"/>
         <v>12.25</v>
       </c>
     </row>
@@ -17468,11 +17468,11 @@
         <v>3</v>
       </c>
       <c r="I455" s="2">
-        <f>H455*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J455" s="2">
-        <f>H455*1.75</f>
+        <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
     </row>
@@ -17499,11 +17499,11 @@
         <v>1</v>
       </c>
       <c r="I456" s="2">
-        <f>H456*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J456" s="2">
-        <f>H456*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17530,11 +17530,11 @@
         <v>1</v>
       </c>
       <c r="I457" s="2">
-        <f>H457*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J457" s="2">
-        <f>H457*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17561,11 +17561,11 @@
         <v>1</v>
       </c>
       <c r="I458" s="2">
-        <f>H458*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J458" s="2">
-        <f>H458*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17592,11 +17592,11 @@
         <v>2</v>
       </c>
       <c r="I459" s="2">
-        <f>H459*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J459" s="2">
-        <f>H459*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -17623,11 +17623,11 @@
         <v>7</v>
       </c>
       <c r="I460" s="2">
-        <f>H460*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J460" s="2">
-        <f>H460*1.75</f>
+        <f t="shared" si="15"/>
         <v>12.25</v>
       </c>
     </row>
@@ -17654,11 +17654,11 @@
         <v>1</v>
       </c>
       <c r="I461" s="2">
-        <f>H461*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J461" s="2">
-        <f>H461*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17685,11 +17685,11 @@
         <v>4</v>
       </c>
       <c r="I462" s="2">
-        <f>H462*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J462" s="2">
-        <f>H462*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -17716,11 +17716,11 @@
         <v>1</v>
       </c>
       <c r="I463" s="2">
-        <f>H463*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J463" s="2">
-        <f>H463*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17747,11 +17747,11 @@
         <v>5</v>
       </c>
       <c r="I464" s="2">
-        <f>H464*0.2</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J464" s="2">
-        <f>H464*1.75</f>
+        <f t="shared" si="15"/>
         <v>8.75</v>
       </c>
     </row>
@@ -17778,11 +17778,11 @@
         <v>1</v>
       </c>
       <c r="I465" s="2">
-        <f>H465*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J465" s="2">
-        <f>H465*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17809,11 +17809,11 @@
         <v>1</v>
       </c>
       <c r="I466" s="2">
-        <f>H466*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J466" s="2">
-        <f>H466*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17840,11 +17840,11 @@
         <v>8</v>
       </c>
       <c r="I467" s="2">
-        <f>H467*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J467" s="2">
-        <f>H467*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
     </row>
@@ -17871,11 +17871,11 @@
         <v>4</v>
       </c>
       <c r="I468" s="2">
-        <f>H468*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J468" s="2">
-        <f>H468*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -17902,11 +17902,11 @@
         <v>4</v>
       </c>
       <c r="I469" s="2">
-        <f>H469*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J469" s="2">
-        <f>H469*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -17933,11 +17933,11 @@
         <v>1</v>
       </c>
       <c r="I470" s="2">
-        <f>H470*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J470" s="2">
-        <f>H470*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17964,11 +17964,11 @@
         <v>1</v>
       </c>
       <c r="I471" s="2">
-        <f>H471*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J471" s="2">
-        <f>H471*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -17995,11 +17995,11 @@
         <v>3</v>
       </c>
       <c r="I472" s="2">
-        <f>H472*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J472" s="2">
-        <f>H472*1.75</f>
+        <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
     </row>
@@ -18026,11 +18026,11 @@
         <v>2</v>
       </c>
       <c r="I473" s="2">
-        <f>H473*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J473" s="2">
-        <f>H473*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -18057,11 +18057,11 @@
         <v>1</v>
       </c>
       <c r="I474" s="2">
-        <f>H474*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J474" s="2">
-        <f>H474*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18088,11 +18088,11 @@
         <v>1</v>
       </c>
       <c r="I475" s="2">
-        <f>H475*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J475" s="2">
-        <f>H475*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18119,11 +18119,11 @@
         <v>2</v>
       </c>
       <c r="I476" s="2">
-        <f>H476*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J476" s="2">
-        <f>H476*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -18150,11 +18150,11 @@
         <v>11</v>
       </c>
       <c r="I477" s="2">
-        <f>H477*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J477" s="2">
-        <f>H477*1.75</f>
+        <f t="shared" si="15"/>
         <v>19.25</v>
       </c>
     </row>
@@ -18181,11 +18181,11 @@
         <v>6</v>
       </c>
       <c r="I478" s="2">
-        <f>H478*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J478" s="2">
-        <f>H478*1.75</f>
+        <f t="shared" si="15"/>
         <v>10.5</v>
       </c>
     </row>
@@ -18212,11 +18212,11 @@
         <v>3</v>
       </c>
       <c r="I479" s="2">
-        <f>H479*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J479" s="2">
-        <f>H479*1.75</f>
+        <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
     </row>
@@ -18243,11 +18243,11 @@
         <v>2</v>
       </c>
       <c r="I480" s="2">
-        <f>H480*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J480" s="2">
-        <f>H480*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -18274,11 +18274,11 @@
         <v>4</v>
       </c>
       <c r="I481" s="2">
-        <f>H481*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J481" s="2">
-        <f>H481*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -18305,11 +18305,11 @@
         <v>6</v>
       </c>
       <c r="I482" s="2">
-        <f>H482*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="J482" s="2">
-        <f>H482*1.75</f>
+        <f t="shared" si="15"/>
         <v>10.5</v>
       </c>
     </row>
@@ -18336,11 +18336,11 @@
         <v>8</v>
       </c>
       <c r="I483" s="2">
-        <f>H483*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J483" s="2">
-        <f>H483*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
     </row>
@@ -18367,11 +18367,11 @@
         <v>1</v>
       </c>
       <c r="I484" s="2">
-        <f>H484*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J484" s="2">
-        <f>H484*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18398,11 +18398,11 @@
         <v>5</v>
       </c>
       <c r="I485" s="2">
-        <f>H485*0.2</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J485" s="2">
-        <f>H485*1.75</f>
+        <f t="shared" si="15"/>
         <v>8.75</v>
       </c>
     </row>
@@ -18429,11 +18429,11 @@
         <v>1</v>
       </c>
       <c r="I486" s="2">
-        <f>H486*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J486" s="2">
-        <f>H486*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18460,11 +18460,11 @@
         <v>1</v>
       </c>
       <c r="I487" s="2">
-        <f>H487*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J487" s="2">
-        <f>H487*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18491,11 +18491,11 @@
         <v>5</v>
       </c>
       <c r="I488" s="2">
-        <f>H488*0.2</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J488" s="2">
-        <f>H488*1.75</f>
+        <f t="shared" si="15"/>
         <v>8.75</v>
       </c>
     </row>
@@ -18522,11 +18522,11 @@
         <v>2</v>
       </c>
       <c r="I489" s="2">
-        <f>H489*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="J489" s="2">
-        <f>H489*1.75</f>
+        <f t="shared" si="15"/>
         <v>3.5</v>
       </c>
     </row>
@@ -18553,11 +18553,11 @@
         <v>4</v>
       </c>
       <c r="I490" s="2">
-        <f>H490*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J490" s="2">
-        <f>H490*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -18584,11 +18584,11 @@
         <v>4</v>
       </c>
       <c r="I491" s="2">
-        <f>H491*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J491" s="2">
-        <f>H491*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -18615,11 +18615,11 @@
         <v>3</v>
       </c>
       <c r="I492" s="2">
-        <f>H492*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J492" s="2">
-        <f>H492*1.75</f>
+        <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
     </row>
@@ -18649,11 +18649,11 @@
         <v>4</v>
       </c>
       <c r="I493" s="2">
-        <f>H493*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J493" s="2">
-        <f>H493*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="K493" t="s">
@@ -18686,11 +18686,11 @@
         <v>8</v>
       </c>
       <c r="I494" s="2">
-        <f>H494*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J494" s="2">
-        <f>H494*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="K494" t="s">
@@ -18723,11 +18723,11 @@
         <v>5</v>
       </c>
       <c r="I495" s="2">
-        <f>H495*0.2</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J495" s="2">
-        <f>H495*1.75</f>
+        <f t="shared" si="15"/>
         <v>8.75</v>
       </c>
       <c r="K495" t="s">
@@ -18760,11 +18760,11 @@
         <v>13</v>
       </c>
       <c r="I496" s="2">
-        <f>H496*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.6</v>
       </c>
       <c r="J496" s="2">
-        <f>H496*1.75</f>
+        <f t="shared" si="15"/>
         <v>22.75</v>
       </c>
       <c r="K496" t="s">
@@ -18797,11 +18797,11 @@
         <v>8</v>
       </c>
       <c r="I497" s="2">
-        <f>H497*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J497" s="2">
-        <f>H497*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="K497" t="s">
@@ -18834,11 +18834,11 @@
         <v>1</v>
       </c>
       <c r="I498" s="2">
-        <f>H498*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J498" s="2">
-        <f>H498*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
       <c r="K498" t="s">
@@ -18871,11 +18871,11 @@
         <v>11</v>
       </c>
       <c r="I499" s="2">
-        <f>H499*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J499" s="2">
-        <f>H499*1.75</f>
+        <f t="shared" si="15"/>
         <v>19.25</v>
       </c>
       <c r="K499" t="s">
@@ -18905,11 +18905,11 @@
         <v>1</v>
       </c>
       <c r="I500" s="2">
-        <f>H500*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J500" s="2">
-        <f>H500*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
     </row>
@@ -18939,11 +18939,11 @@
         <v>16</v>
       </c>
       <c r="I501" s="2">
-        <f>H501*0.2</f>
+        <f t="shared" si="14"/>
         <v>3.2</v>
       </c>
       <c r="J501" s="2">
-        <f>H501*1.75</f>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
       <c r="K501" t="s">
@@ -18976,11 +18976,11 @@
         <v>8</v>
       </c>
       <c r="I502" s="2">
-        <f>H502*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J502" s="2">
-        <f>H502*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="K502" t="s">
@@ -19010,11 +19010,11 @@
         <v>3</v>
       </c>
       <c r="I503" s="2">
-        <f>H503*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="J503" s="2">
-        <f>H503*1.75</f>
+        <f t="shared" si="15"/>
         <v>5.25</v>
       </c>
     </row>
@@ -19041,11 +19041,11 @@
         <v>8</v>
       </c>
       <c r="I504" s="2">
-        <f>H504*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.6</v>
       </c>
       <c r="J504" s="2">
-        <f>H504*1.75</f>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
     </row>
@@ -19075,11 +19075,11 @@
         <v>7</v>
       </c>
       <c r="I505" s="2">
-        <f>H505*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J505" s="2">
-        <f>H505*1.75</f>
+        <f t="shared" si="15"/>
         <v>12.25</v>
       </c>
       <c r="K505" t="s">
@@ -19112,11 +19112,11 @@
         <v>1</v>
       </c>
       <c r="I506" s="2">
-        <f>H506*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J506" s="2">
-        <f>H506*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
       <c r="K506" t="s">
@@ -19149,11 +19149,11 @@
         <v>4</v>
       </c>
       <c r="I507" s="2">
-        <f>H507*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.8</v>
       </c>
       <c r="J507" s="2">
-        <f>H507*1.75</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="K507" t="s">
@@ -19186,11 +19186,11 @@
         <v>16</v>
       </c>
       <c r="I508" s="2">
-        <f>H508*0.2</f>
+        <f t="shared" si="14"/>
         <v>3.2</v>
       </c>
       <c r="J508" s="2">
-        <f>H508*1.75</f>
+        <f t="shared" si="15"/>
         <v>28</v>
       </c>
       <c r="K508" t="s">
@@ -19223,11 +19223,11 @@
         <v>11</v>
       </c>
       <c r="I509" s="2">
-        <f>H509*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="J509" s="2">
-        <f>H509*1.75</f>
+        <f t="shared" si="15"/>
         <v>19.25</v>
       </c>
       <c r="K509" t="s">
@@ -19260,11 +19260,11 @@
         <v>9</v>
       </c>
       <c r="I510" s="2">
-        <f>H510*0.2</f>
+        <f t="shared" si="14"/>
         <v>1.8</v>
       </c>
       <c r="J510" s="2">
-        <f>H510*1.75</f>
+        <f t="shared" si="15"/>
         <v>15.75</v>
       </c>
       <c r="K510" t="s">
@@ -19297,11 +19297,11 @@
         <v>13</v>
       </c>
       <c r="I511" s="2">
-        <f>H511*0.2</f>
+        <f t="shared" si="14"/>
         <v>2.6</v>
       </c>
       <c r="J511" s="2">
-        <f>H511*1.75</f>
+        <f t="shared" si="15"/>
         <v>22.75</v>
       </c>
       <c r="K511" t="s">
@@ -19334,11 +19334,11 @@
         <v>1</v>
       </c>
       <c r="I512" s="2">
-        <f>H512*0.2</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="J512" s="2">
-        <f>H512*1.75</f>
+        <f t="shared" si="15"/>
         <v>1.75</v>
       </c>
       <c r="K512" t="s">

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/84b50a9ff1aa4084/Desktop/fanta-manageriale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="595" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4C412A-E625-4F43-BBCA-1A50DE38D3AA}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="8_{F7D04CEF-6BBF-4FEA-AF21-5114652F8278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25BF026A-8BEB-0A42-808C-A5016CF10F41}"/>
   <bookViews>
-    <workbookView xWindow="15100" yWindow="660" windowWidth="15140" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15100" yWindow="660" windowWidth="15140" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista calciatori" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="596">
   <si>
     <t>#</t>
   </si>
@@ -1903,10 +1903,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3256,36 +3252,36 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>530</v>
+        <v>779</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
       </c>
       <c r="F27">
-        <v>30</v>
-      </c>
-      <c r="G27" t="s">
-        <v>462</v>
-      </c>
-      <c r="H27" s="2">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="H27">
+        <v>9</v>
       </c>
       <c r="I27" s="2">
         <f>H27*0.2</f>
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" s="2">
         <f>H27*1.75</f>
-        <v>22.75</v>
+        <v>15.75</v>
       </c>
       <c r="K27" t="s">
         <v>28</v>
@@ -3293,10 +3289,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>779</v>
+        <v>2120</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -3305,24 +3301,24 @@
         <v>590</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2">
         <f>H28*0.2</f>
-        <v>1.8</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J28" s="2">
         <f>H28*1.75</f>
-        <v>15.75</v>
+        <v>24.5</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -3330,10 +3326,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>2120</v>
+        <v>2423</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -3342,24 +3338,24 @@
         <v>590</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="H29">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I29" s="2">
         <f>H29*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="J29" s="2">
         <f>H29*1.75</f>
-        <v>24.5</v>
+        <v>40.25</v>
       </c>
       <c r="K29" t="s">
         <v>28</v>
@@ -3367,10 +3363,10 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>2423</v>
+        <v>2606</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -3382,21 +3378,21 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H30">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I30" s="2">
         <f>H30*0.2</f>
-        <v>4.6000000000000005</v>
+        <v>2.6</v>
       </c>
       <c r="J30" s="2">
         <f>H30*1.75</f>
-        <v>40.25</v>
+        <v>22.75</v>
       </c>
       <c r="K30" t="s">
         <v>28</v>
@@ -3404,10 +3400,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>2606</v>
+        <v>2766</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3416,24 +3412,24 @@
         <v>590</v>
       </c>
       <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31">
         <v>27</v>
       </c>
-      <c r="F31">
-        <v>41</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="H31">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I31" s="2">
         <f>H31*0.2</f>
-        <v>2.6</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J31" s="2">
         <f>H31*1.75</f>
-        <v>22.75</v>
+        <v>29.75</v>
       </c>
       <c r="K31" t="s">
         <v>28</v>
@@ -3441,10 +3437,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>2766</v>
+        <v>2815</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>431</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -3453,24 +3449,24 @@
         <v>590</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>467</v>
+        <v>47</v>
       </c>
       <c r="H32">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2">
         <f>H32*0.2</f>
-        <v>3.4000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="J32" s="2">
         <f>H32*1.75</f>
-        <v>29.75</v>
+        <v>1.75</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -3478,36 +3474,36 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>2815</v>
+        <v>4137</v>
       </c>
       <c r="B33" t="s">
-        <v>431</v>
+        <v>259</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>36</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="2">
+        <v>8</v>
       </c>
       <c r="I33" s="2">
         <f>H33*0.2</f>
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J33" s="2">
         <f>H33*1.75</f>
-        <v>1.75</v>
+        <v>14</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
@@ -3515,36 +3511,36 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>4137</v>
+        <v>4312</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>48</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34" s="2">
-        <v>8</v>
+        <v>31</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34">
+        <v>15</v>
       </c>
       <c r="I34" s="2">
         <f>H34*0.2</f>
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J34" s="2">
         <f>H34*1.75</f>
-        <v>14</v>
+        <v>26.25</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
@@ -3552,10 +3548,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>4312</v>
+        <v>4728</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -3567,21 +3563,21 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2">
         <f>H35*0.2</f>
-        <v>3</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J35" s="2">
         <f>H35*1.75</f>
-        <v>26.25</v>
+        <v>24.5</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
@@ -3589,10 +3585,10 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>4728</v>
+        <v>4807</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -3601,24 +3597,24 @@
         <v>590</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36">
         <v>10</v>
-      </c>
-      <c r="H36">
-        <v>14</v>
       </c>
       <c r="I36" s="2">
         <f>H36*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
         <f>H36*1.75</f>
-        <v>24.5</v>
+        <v>17.5</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
@@ -3626,10 +3622,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>4807</v>
+        <v>4896</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3638,24 +3634,24 @@
         <v>590</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2">
         <f>H37*0.2</f>
-        <v>2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J37" s="2">
         <f>H37*1.75</f>
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="K37" t="s">
         <v>28</v>
@@ -3663,10 +3659,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>4896</v>
+        <v>5273</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -3675,24 +3671,24 @@
         <v>590</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I38" s="2">
         <f>H38*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J38" s="2">
         <f>H38*1.75</f>
-        <v>10.5</v>
+        <v>5.25</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -3700,10 +3696,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>5273</v>
+        <v>5422</v>
       </c>
       <c r="B39" t="s">
-        <v>290</v>
+        <v>125</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -3712,24 +3708,24 @@
         <v>590</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I39" s="2">
         <f>H39*0.2</f>
-        <v>0.60000000000000009</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2">
         <f>H39*1.75</f>
-        <v>5.25</v>
+        <v>8.75</v>
       </c>
       <c r="K39" t="s">
         <v>28</v>
@@ -3737,10 +3733,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>5422</v>
+        <v>5589</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -3749,24 +3745,24 @@
         <v>590</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>77</v>
+        <v>459</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I40" s="2">
         <f>H40*0.2</f>
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J40" s="2">
         <f>H40*1.75</f>
-        <v>8.75</v>
+        <v>19.25</v>
       </c>
       <c r="K40" t="s">
         <v>28</v>
@@ -3774,10 +3770,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>5589</v>
+        <v>5678</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>368</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -3786,24 +3782,24 @@
         <v>590</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="H41">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I41" s="2">
         <f>H41*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2">
         <f>H41*1.75</f>
-        <v>19.25</v>
+        <v>8.75</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
@@ -3811,10 +3807,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>5678</v>
+        <v>5687</v>
       </c>
       <c r="B42" t="s">
-        <v>368</v>
+        <v>59</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -3823,24 +3819,24 @@
         <v>590</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>468</v>
+        <v>58</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I42" s="2">
         <f>H42*0.2</f>
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J42" s="2">
         <f>H42*1.75</f>
-        <v>8.75</v>
+        <v>22.75</v>
       </c>
       <c r="K42" t="s">
         <v>28</v>
@@ -3848,36 +3844,36 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>5687</v>
+        <v>5995</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
         <v>590</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F43">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="H43">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I43" s="2">
         <f>H43*0.2</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J43" s="2">
         <f>H43*1.75</f>
-        <v>22.75</v>
+        <v>31.5</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
@@ -3885,36 +3881,36 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>5995</v>
+        <v>6047</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F44">
-        <v>25</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H44">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="G44" t="s">
+        <v>468</v>
+      </c>
+      <c r="H44" s="2">
+        <v>7</v>
       </c>
       <c r="I44" s="2">
         <f>H44*0.2</f>
-        <v>3.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J44" s="2">
         <f>H44*1.75</f>
-        <v>31.5</v>
+        <v>12.25</v>
       </c>
       <c r="K44" t="s">
         <v>28</v>
@@ -3922,36 +3918,36 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>6047</v>
+        <v>6271</v>
       </c>
       <c r="B45" t="s">
-        <v>337</v>
+        <v>205</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F45">
-        <v>31</v>
-      </c>
-      <c r="G45" t="s">
-        <v>468</v>
-      </c>
-      <c r="H45" s="2">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
       </c>
       <c r="I45" s="2">
         <f>H45*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2">
         <f>H45*1.75</f>
-        <v>12.25</v>
+        <v>8.75</v>
       </c>
       <c r="K45" t="s">
         <v>28</v>
@@ -3959,10 +3955,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>6271</v>
+        <v>6495</v>
       </c>
       <c r="B46" t="s">
-        <v>205</v>
+        <v>282</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -3971,24 +3967,24 @@
         <v>590</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="2">
         <f>H46*0.2</f>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J46" s="2">
         <f>H46*1.75</f>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K46" t="s">
         <v>28</v>
@@ -3996,10 +3992,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>6495</v>
+        <v>6496</v>
       </c>
       <c r="B47" t="s">
-        <v>282</v>
+        <v>167</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -4008,24 +4004,24 @@
         <v>590</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="F47">
         <v>21</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>67</v>
+        <v>464</v>
       </c>
       <c r="H47">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I47" s="2">
         <f>H47*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J47" s="2">
         <f>H47*1.75</f>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="K47" t="s">
         <v>28</v>
@@ -4033,10 +4029,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>6496</v>
+        <v>6632</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -4045,24 +4041,24 @@
         <v>590</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="F48">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>464</v>
+        <v>67</v>
       </c>
       <c r="H48">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I48" s="2">
         <f>H48*0.2</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J48" s="2">
         <f>H48*1.75</f>
-        <v>14</v>
+        <v>8.75</v>
       </c>
       <c r="K48" t="s">
         <v>28</v>
@@ -4070,10 +4066,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>6632</v>
+        <v>6664</v>
       </c>
       <c r="B49" t="s">
-        <v>254</v>
+        <v>148</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -4082,24 +4078,24 @@
         <v>590</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F49">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>67</v>
+        <v>469</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I49" s="2">
         <f>H49*0.2</f>
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J49" s="2">
         <f>H49*1.75</f>
-        <v>8.75</v>
+        <v>14</v>
       </c>
       <c r="K49" t="s">
         <v>28</v>
@@ -4107,36 +4103,36 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>6664</v>
+        <v>6956</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>590</v>
       </c>
       <c r="E50" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F50">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>469</v>
+        <v>67</v>
       </c>
       <c r="H50">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I50" s="2">
         <f>H50*0.2</f>
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J50" s="2">
         <f>H50*1.75</f>
-        <v>14</v>
+        <v>22.75</v>
       </c>
       <c r="K50" t="s">
         <v>28</v>
@@ -4144,36 +4140,36 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>6956</v>
+        <v>7008</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>316</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
         <v>590</v>
       </c>
       <c r="E51" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H51">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I51" s="2">
         <f>H51*0.2</f>
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J51" s="2">
         <f>H51*1.75</f>
-        <v>22.75</v>
+        <v>8.75</v>
       </c>
       <c r="K51" t="s">
         <v>28</v>
@@ -4181,10 +4177,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>7008</v>
+        <v>7012</v>
       </c>
       <c r="B52" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -4193,24 +4189,24 @@
         <v>590</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F52">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I52" s="2">
         <f>H52*0.2</f>
-        <v>1</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J52" s="2">
         <f>H52*1.75</f>
-        <v>8.75</v>
+        <v>5.25</v>
       </c>
       <c r="K52" t="s">
         <v>28</v>
@@ -4218,10 +4214,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>7012</v>
+        <v>7203</v>
       </c>
       <c r="B53" t="s">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -4230,24 +4226,24 @@
         <v>590</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="F53">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="2">
         <f>H53*0.2</f>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="J53" s="2">
         <f>H53*1.75</f>
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="K53" t="s">
         <v>28</v>
@@ -4255,10 +4251,10 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>7203</v>
+        <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>441</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -4267,35 +4263,35 @@
         <v>590</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F54">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I54" s="2">
         <f>H54*0.2</f>
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J54" s="2">
         <f>H54*1.75</f>
-        <v>7</v>
-      </c>
-      <c r="K54" t="s">
-        <v>28</v>
+        <v>1.75</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>4</v>
+        <v>309</v>
       </c>
       <c r="B55" t="s">
-        <v>441</v>
+        <v>131</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -4304,35 +4300,35 @@
         <v>590</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F55">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I55" s="2">
         <f>H55*0.2</f>
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="2">
         <f>H55*1.75</f>
-        <v>1.75</v>
-      </c>
-      <c r="K55" s="4" t="s">
+        <v>26.25</v>
+      </c>
+      <c r="K55" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>309</v>
+        <v>554</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -4341,24 +4337,24 @@
         <v>590</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F56">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>10</v>
+        <v>468</v>
       </c>
       <c r="H56">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I56" s="2">
         <f>H56*0.2</f>
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J56" s="2">
         <f>H56*1.75</f>
-        <v>26.25</v>
+        <v>14</v>
       </c>
       <c r="K56" t="s">
         <v>64</v>
@@ -4366,36 +4362,36 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>554</v>
+        <v>632</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
         <v>590</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F57">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H57">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2">
         <f>H57*0.2</f>
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J57" s="2">
         <f>H57*1.75</f>
-        <v>14</v>
+        <v>26.25</v>
       </c>
       <c r="K57" t="s">
         <v>64</v>
@@ -4403,36 +4399,36 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>632</v>
+        <v>787</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="s">
         <v>590</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="F58">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="H58">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I58" s="2">
         <f>H58*0.2</f>
-        <v>3</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J58" s="2">
         <f>H58*1.75</f>
-        <v>26.25</v>
+        <v>12.25</v>
       </c>
       <c r="K58" t="s">
         <v>64</v>
@@ -4440,10 +4436,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>787</v>
+        <v>1870</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -4452,24 +4448,24 @@
         <v>590</v>
       </c>
       <c r="E59" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="F59">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="H59">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I59" s="2">
         <f>H59*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J59" s="2">
         <f>H59*1.75</f>
-        <v>12.25</v>
+        <v>29.75</v>
       </c>
       <c r="K59" t="s">
         <v>64</v>
@@ -4477,36 +4473,36 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>1870</v>
+        <v>2097</v>
       </c>
       <c r="B60" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
         <v>590</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F60">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H60">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I60" s="2">
         <f>H60*0.2</f>
-        <v>3.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="J60" s="2">
         <f>H60*1.75</f>
-        <v>29.75</v>
+        <v>43.75</v>
       </c>
       <c r="K60" t="s">
         <v>64</v>
@@ -4514,36 +4510,36 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>2097</v>
+        <v>2832</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
         <v>590</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F61">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>11</v>
+        <v>463</v>
       </c>
       <c r="H61">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I61" s="2">
         <f>H61*0.2</f>
-        <v>5</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J61" s="2">
         <f>H61*1.75</f>
-        <v>43.75</v>
+        <v>12.25</v>
       </c>
       <c r="K61" t="s">
         <v>64</v>
@@ -4551,10 +4547,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>2832</v>
+        <v>4317</v>
       </c>
       <c r="B62" t="s">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -4563,24 +4559,24 @@
         <v>590</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F62">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="H62">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I62" s="2">
         <f>H62*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="J62" s="2">
         <f>H62*1.75</f>
-        <v>12.25</v>
+        <v>22.75</v>
       </c>
       <c r="K62" t="s">
         <v>64</v>
@@ -4588,10 +4584,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>4317</v>
+        <v>4409</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -4600,24 +4596,24 @@
         <v>590</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H63">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I63" s="2">
         <f>H63*0.2</f>
-        <v>2.6</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J63" s="2">
         <f>H63*1.75</f>
-        <v>22.75</v>
+        <v>24.5</v>
       </c>
       <c r="K63" t="s">
         <v>64</v>
@@ -4625,10 +4621,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>4409</v>
+        <v>4431</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -4637,24 +4633,24 @@
         <v>590</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F64">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="H64">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I64" s="2">
         <f>H64*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J64" s="2">
         <f>H64*1.75</f>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="K64" t="s">
         <v>64</v>
@@ -4662,10 +4658,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>4431</v>
+        <v>4436</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>191</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -4674,24 +4670,24 @@
         <v>590</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F65">
         <v>26</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>47</v>
+        <v>463</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I65" s="2">
         <f>H65*0.2</f>
-        <v>3.2</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J65" s="2">
         <f>H65*1.75</f>
-        <v>28</v>
+        <v>12.25</v>
       </c>
       <c r="K65" t="s">
         <v>64</v>
@@ -4699,10 +4695,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>4436</v>
+        <v>4887</v>
       </c>
       <c r="B66" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -4711,24 +4707,24 @@
         <v>590</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F66">
         <v>26</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="H66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I66" s="2">
         <f>H66*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J66" s="2">
         <f>H66*1.75</f>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K66" t="s">
         <v>64</v>
@@ -4736,10 +4732,10 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>4887</v>
+        <v>5301</v>
       </c>
       <c r="B67" t="s">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -4748,24 +4744,24 @@
         <v>590</v>
       </c>
       <c r="E67" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="F67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I67" s="2">
         <f>H67*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J67" s="2">
         <f>H67*1.75</f>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K67" t="s">
         <v>64</v>
@@ -4773,10 +4769,10 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>5301</v>
+        <v>5526</v>
       </c>
       <c r="B68" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -4785,24 +4781,24 @@
         <v>590</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F68">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>471</v>
+        <v>67</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I68" s="2">
         <f>H68*0.2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" s="2">
         <f>H68*1.75</f>
-        <v>8.75</v>
+        <v>17.5</v>
       </c>
       <c r="K68" t="s">
         <v>64</v>
@@ -4810,10 +4806,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>5526</v>
+        <v>5791</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="C69">
         <v>2</v>
@@ -4822,24 +4818,24 @@
         <v>590</v>
       </c>
       <c r="E69" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F69">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>67</v>
+        <v>459</v>
       </c>
       <c r="H69">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I69" s="2">
         <f>H69*0.2</f>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J69" s="2">
         <f>H69*1.75</f>
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="K69" t="s">
         <v>64</v>
@@ -4847,10 +4843,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>5791</v>
+        <v>5998</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -4859,24 +4855,24 @@
         <v>590</v>
       </c>
       <c r="E70" t="s">
-        <v>88</v>
+        <v>585</v>
       </c>
       <c r="F70">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="H70">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I70" s="2">
         <f>H70*0.2</f>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J70" s="2">
         <f>H70*1.75</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K70" t="s">
         <v>64</v>
@@ -4884,10 +4880,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>5998</v>
+        <v>6151</v>
       </c>
       <c r="B71" t="s">
-        <v>271</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -4896,24 +4892,24 @@
         <v>590</v>
       </c>
       <c r="E71" t="s">
-        <v>585</v>
+        <v>20</v>
       </c>
       <c r="F71">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>77</v>
+        <v>459</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I71" s="2">
         <f>H71*0.2</f>
-        <v>0.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J71" s="2">
         <f>H71*1.75</f>
-        <v>7</v>
+        <v>19.25</v>
       </c>
       <c r="K71" t="s">
         <v>64</v>
@@ -4921,10 +4917,10 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>6151</v>
+        <v>6202</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>284</v>
       </c>
       <c r="C72">
         <v>2</v>
@@ -4933,24 +4929,24 @@
         <v>590</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F72">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H72">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I72" s="2">
         <f>H72*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J72" s="2">
         <f>H72*1.75</f>
-        <v>19.25</v>
+        <v>10.5</v>
       </c>
       <c r="K72" t="s">
         <v>64</v>
@@ -4958,10 +4954,10 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>6202</v>
+        <v>6485</v>
       </c>
       <c r="B73" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -4970,24 +4966,24 @@
         <v>590</v>
       </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F73">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>67</v>
+        <v>466</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I73" s="2">
         <f>H73*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J73" s="2">
         <f>H73*1.75</f>
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="K73" t="s">
         <v>64</v>
@@ -4995,10 +4991,10 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>6485</v>
+        <v>6646</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="C74">
         <v>2</v>
@@ -5007,24 +5003,24 @@
         <v>590</v>
       </c>
       <c r="E74" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F74">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>466</v>
+        <v>10</v>
       </c>
       <c r="H74">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I74" s="2">
         <f>H74*0.2</f>
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2">
         <f>H74*1.75</f>
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="K74" t="s">
         <v>64</v>
@@ -5032,10 +5028,10 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>6646</v>
+        <v>6916</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -5044,24 +5040,24 @@
         <v>590</v>
       </c>
       <c r="E75" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F75">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>10</v>
+        <v>460</v>
       </c>
       <c r="H75">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I75" s="2">
         <f>H75*0.2</f>
-        <v>2</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J75" s="2">
         <f>H75*1.75</f>
-        <v>17.5</v>
+        <v>12.25</v>
       </c>
       <c r="K75" t="s">
         <v>64</v>
@@ -5069,36 +5065,36 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>6916</v>
+        <v>7181</v>
       </c>
       <c r="B76" t="s">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="s">
         <v>590</v>
       </c>
       <c r="E76" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F76">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>460</v>
+        <v>14</v>
       </c>
       <c r="H76">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I76" s="2">
         <f>H76*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J76" s="2">
         <f>H76*1.75</f>
-        <v>12.25</v>
+        <v>28</v>
       </c>
       <c r="K76" t="s">
         <v>64</v>
@@ -5106,36 +5102,36 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>7181</v>
+        <v>7252</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="s">
         <v>590</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="F77">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H77">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I77" s="2">
         <f>H77*0.2</f>
-        <v>3.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J77" s="2">
         <f>H77*1.75</f>
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="K77" t="s">
         <v>64</v>
@@ -5143,10 +5139,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>7252</v>
+        <v>2167</v>
       </c>
       <c r="B78" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -5155,24 +5151,24 @@
         <v>590</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="F78">
+        <v>29</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H78">
         <v>25</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78">
-        <v>6</v>
       </c>
       <c r="I78" s="2">
         <f>H78*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>5</v>
       </c>
       <c r="J78" s="2">
         <f>H78*1.75</f>
-        <v>10.5</v>
+        <v>43.75</v>
       </c>
       <c r="K78" t="s">
         <v>64</v>
@@ -6068,10 +6064,10 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>2167</v>
+        <v>2531</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="C103">
         <v>2</v>
@@ -6080,24 +6076,24 @@
         <v>590</v>
       </c>
       <c r="E103" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F103">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c r="H103">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I103" s="2">
         <f>H103*0.2</f>
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J103" s="2">
         <f>H103*1.75</f>
-        <v>43.75</v>
+        <v>15.75</v>
       </c>
       <c r="K103" t="s">
         <v>15</v>
@@ -6105,10 +6101,10 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>2531</v>
+        <v>2788</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -6117,24 +6113,24 @@
         <v>590</v>
       </c>
       <c r="E104" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F104">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H104">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I104" s="2">
         <f>H104*0.2</f>
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J104" s="2">
         <f>H104*1.75</f>
-        <v>15.75</v>
+        <v>26.25</v>
       </c>
       <c r="K104" t="s">
         <v>15</v>
@@ -6142,10 +6138,10 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>2788</v>
+        <v>4401</v>
       </c>
       <c r="B105" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="C105">
         <v>2</v>
@@ -6154,24 +6150,24 @@
         <v>590</v>
       </c>
       <c r="E105" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F105">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H105">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I105" s="2">
         <f>H105*0.2</f>
-        <v>3</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J105" s="2">
         <f>H105*1.75</f>
-        <v>26.25</v>
+        <v>12.25</v>
       </c>
       <c r="K105" t="s">
         <v>15</v>
@@ -6179,10 +6175,10 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>4401</v>
+        <v>4463</v>
       </c>
       <c r="B106" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="C106">
         <v>2</v>
@@ -6191,24 +6187,24 @@
         <v>590</v>
       </c>
       <c r="E106" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F106">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H106">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I106" s="2">
         <f>H106*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J106" s="2">
         <f>H106*1.75</f>
-        <v>12.25</v>
+        <v>24.5</v>
       </c>
       <c r="K106" t="s">
         <v>15</v>
@@ -6216,10 +6212,10 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>4463</v>
+        <v>4973</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -6228,24 +6224,24 @@
         <v>590</v>
       </c>
       <c r="E107" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F107">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H107">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I107" s="2">
         <f>H107*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J107" s="2">
         <f>H107*1.75</f>
-        <v>24.5</v>
+        <v>29.75</v>
       </c>
       <c r="K107" t="s">
         <v>15</v>
@@ -6253,10 +6249,10 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>4973</v>
+        <v>5022</v>
       </c>
       <c r="B108" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -6265,24 +6261,24 @@
         <v>590</v>
       </c>
       <c r="E108" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F108">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="H108">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I108" s="2">
         <f>H108*0.2</f>
-        <v>3.4000000000000004</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J108" s="2">
         <f>H108*1.75</f>
-        <v>29.75</v>
+        <v>24.5</v>
       </c>
       <c r="K108" t="s">
         <v>15</v>
@@ -6290,10 +6286,10 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>5022</v>
+        <v>5637</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C109">
         <v>2</v>
@@ -6302,24 +6298,24 @@
         <v>590</v>
       </c>
       <c r="E109" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="F109">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H109">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I109" s="2">
         <f>H109*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J109" s="2">
         <f>H109*1.75</f>
-        <v>24.5</v>
+        <v>33.25</v>
       </c>
       <c r="K109" t="s">
         <v>15</v>
@@ -6327,10 +6323,10 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>5637</v>
+        <v>5876</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -6339,24 +6335,24 @@
         <v>590</v>
       </c>
       <c r="E110" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F110">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H110">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I110" s="2">
         <f>H110*0.2</f>
-        <v>3.8000000000000003</v>
+        <v>1.8</v>
       </c>
       <c r="J110" s="2">
         <f>H110*1.75</f>
-        <v>33.25</v>
+        <v>15.75</v>
       </c>
       <c r="K110" t="s">
         <v>15</v>
@@ -6364,10 +6360,10 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>5876</v>
+        <v>5877</v>
       </c>
       <c r="B111" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -6376,24 +6372,24 @@
         <v>590</v>
       </c>
       <c r="E111" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F111">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>47</v>
+        <v>460</v>
       </c>
       <c r="H111">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I111" s="2">
         <f>H111*0.2</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J111" s="2">
         <f>H111*1.75</f>
-        <v>15.75</v>
+        <v>14</v>
       </c>
       <c r="K111" t="s">
         <v>15</v>
@@ -6401,10 +6397,10 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>5877</v>
+        <v>5888</v>
       </c>
       <c r="B112" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -6413,24 +6409,24 @@
         <v>590</v>
       </c>
       <c r="E112" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F112">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H112">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I112" s="2">
         <f>H112*0.2</f>
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J112" s="2">
         <f>H112*1.75</f>
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="K112" t="s">
         <v>15</v>
@@ -6438,10 +6434,10 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>5888</v>
+        <v>6010</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
+        <v>362</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -6450,7 +6446,7 @@
         <v>590</v>
       </c>
       <c r="E113" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F113">
         <v>23</v>
@@ -6459,15 +6455,15 @@
         <v>462</v>
       </c>
       <c r="H113">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I113" s="2">
         <f>H113*0.2</f>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J113" s="2">
         <f>H113*1.75</f>
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="K113" t="s">
         <v>15</v>
@@ -6475,10 +6471,10 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>6010</v>
+        <v>6434</v>
       </c>
       <c r="B114" t="s">
-        <v>362</v>
+        <v>22</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -6487,24 +6483,24 @@
         <v>590</v>
       </c>
       <c r="E114" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F114">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>462</v>
+        <v>10</v>
       </c>
       <c r="H114">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I114" s="2">
         <f>H114*0.2</f>
-        <v>1.6</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="J114" s="2">
         <f>H114*1.75</f>
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K114" t="s">
         <v>15</v>
@@ -6512,36 +6508,36 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>6434</v>
+        <v>6575</v>
       </c>
       <c r="B115" t="s">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E115" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F115">
-        <v>21</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H115">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G115" t="s">
+        <v>463</v>
+      </c>
+      <c r="H115" s="2">
+        <v>4</v>
       </c>
       <c r="I115" s="2">
         <f>H115*0.2</f>
-        <v>4.8000000000000007</v>
+        <v>0.8</v>
       </c>
       <c r="J115" s="2">
         <f>H115*1.75</f>
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="K115" t="s">
         <v>15</v>
@@ -6549,36 +6545,36 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>6575</v>
+        <v>6717</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F116">
-        <v>25</v>
-      </c>
-      <c r="G116" t="s">
-        <v>463</v>
-      </c>
-      <c r="H116" s="2">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H116">
+        <v>9</v>
       </c>
       <c r="I116" s="2">
         <f>H116*0.2</f>
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J116" s="2">
         <f>H116*1.75</f>
-        <v>7</v>
+        <v>15.75</v>
       </c>
       <c r="K116" t="s">
         <v>15</v>
@@ -6586,36 +6582,36 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>6717</v>
+        <v>6869</v>
       </c>
       <c r="B117" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" t="s">
         <v>590</v>
       </c>
       <c r="E117" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F117">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="H117">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I117" s="2">
         <f>H117*0.2</f>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J117" s="2">
         <f>H117*1.75</f>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K117" t="s">
         <v>15</v>
@@ -6623,36 +6619,36 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>6869</v>
+        <v>6984</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>326</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="s">
         <v>590</v>
       </c>
       <c r="E118" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F118">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>67</v>
+        <v>463</v>
       </c>
       <c r="H118">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I118" s="2">
         <f>H118*0.2</f>
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J118" s="2">
         <f>H118*1.75</f>
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="K118" t="s">
         <v>15</v>
@@ -6660,10 +6656,10 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>6984</v>
+        <v>7071</v>
       </c>
       <c r="B119" t="s">
-        <v>326</v>
+        <v>113</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -6672,24 +6668,24 @@
         <v>590</v>
       </c>
       <c r="E119" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="F119">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c r="H119">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I119" s="2">
         <f>H119*0.2</f>
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J119" s="2">
         <f>H119*1.75</f>
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="K119" t="s">
         <v>15</v>
@@ -6697,36 +6693,36 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>7071</v>
+        <v>7143</v>
       </c>
       <c r="B120" t="s">
-        <v>113</v>
+        <v>275</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E120" t="s">
+        <v>141</v>
+      </c>
+      <c r="F120">
+        <v>23</v>
+      </c>
+      <c r="G120" t="s">
+        <v>464</v>
+      </c>
+      <c r="H120" s="2">
         <v>9</v>
-      </c>
-      <c r="F120">
-        <v>21</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H120">
-        <v>16</v>
       </c>
       <c r="I120" s="2">
         <f>H120*0.2</f>
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J120" s="2">
         <f>H120*1.75</f>
-        <v>28</v>
+        <v>15.75</v>
       </c>
       <c r="K120" t="s">
         <v>15</v>
@@ -6734,36 +6730,36 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>7143</v>
+        <v>7212</v>
       </c>
       <c r="B121" t="s">
-        <v>275</v>
+        <v>197</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E121" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="F121">
-        <v>23</v>
-      </c>
-      <c r="G121" t="s">
-        <v>464</v>
-      </c>
-      <c r="H121" s="2">
-        <v>9</v>
+        <v>27</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H121">
+        <v>7</v>
       </c>
       <c r="I121" s="2">
         <f>H121*0.2</f>
-        <v>1.8</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J121" s="2">
         <f>H121*1.75</f>
-        <v>15.75</v>
+        <v>12.25</v>
       </c>
       <c r="K121" t="s">
         <v>15</v>
@@ -6771,10 +6767,10 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>7212</v>
+        <v>7219</v>
       </c>
       <c r="B122" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -6783,24 +6779,24 @@
         <v>590</v>
       </c>
       <c r="E122" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F122">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I122" s="2">
         <f>H122*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J122" s="2">
         <f>H122*1.75</f>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="K122" t="s">
         <v>15</v>
@@ -6808,36 +6804,36 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>7219</v>
+        <v>7277</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>407</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E123" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F123">
-        <v>23</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="H123">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
+      </c>
+      <c r="H123" s="2">
+        <v>1</v>
       </c>
       <c r="I123" s="2">
         <f>H123*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="J123" s="2">
         <f>H123*1.75</f>
-        <v>10.5</v>
+        <v>1.75</v>
       </c>
       <c r="K123" t="s">
         <v>15</v>
@@ -6845,10 +6841,10 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>7277</v>
+        <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>407</v>
+        <v>183</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -6857,61 +6853,61 @@
         <v>72</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F124">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G124" t="s">
-        <v>11</v>
+        <v>465</v>
       </c>
       <c r="H124" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I124" s="2">
         <f>H124*0.2</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J124" s="2">
         <f>H124*1.75</f>
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="K124" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>256</v>
+        <v>536</v>
       </c>
       <c r="B125" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E125" t="s">
         <v>32</v>
       </c>
       <c r="F125">
-        <v>35</v>
-      </c>
-      <c r="G125" t="s">
-        <v>465</v>
-      </c>
-      <c r="H125" s="2">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H125">
+        <v>9</v>
       </c>
       <c r="I125" s="2">
         <f>H125*0.2</f>
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J125" s="2">
         <f>H125*1.75</f>
-        <v>7</v>
+        <v>15.75</v>
       </c>
       <c r="K125" t="s">
         <v>25</v>
@@ -6919,10 +6915,10 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>536</v>
+        <v>572</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -6934,21 +6930,21 @@
         <v>32</v>
       </c>
       <c r="F126">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="H126">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I126" s="2">
         <f>H126*0.2</f>
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J126" s="2">
         <f>H126*1.75</f>
-        <v>15.75</v>
+        <v>19.25</v>
       </c>
       <c r="K126" t="s">
         <v>25</v>
@@ -6956,36 +6952,36 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>572</v>
+        <v>2012</v>
       </c>
       <c r="B127" t="s">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127">
         <v>32</v>
       </c>
-      <c r="F127">
-        <v>29</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H127">
+      <c r="G127" t="s">
         <v>11</v>
+      </c>
+      <c r="H127" s="2">
+        <v>1</v>
       </c>
       <c r="I127" s="2">
         <f>H127*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="J127" s="2">
         <f>H127*1.75</f>
-        <v>19.25</v>
+        <v>1.75</v>
       </c>
       <c r="K127" t="s">
         <v>25</v>
@@ -6993,36 +6989,36 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>788</v>
+        <v>2170</v>
       </c>
       <c r="B128" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E128" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F128">
-        <v>34</v>
-      </c>
-      <c r="G128" t="s">
-        <v>459</v>
-      </c>
-      <c r="H128" s="2">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H128">
+        <v>5</v>
       </c>
       <c r="I128" s="2">
         <f>H128*0.2</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J128" s="2">
         <f>H128*1.75</f>
-        <v>14</v>
+        <v>8.75</v>
       </c>
       <c r="K128" t="s">
         <v>25</v>
@@ -7030,36 +7026,36 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>2012</v>
+        <v>2188</v>
       </c>
       <c r="B129" t="s">
-        <v>398</v>
+        <v>227</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E129" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F129">
-        <v>32</v>
-      </c>
-      <c r="G129" t="s">
-        <v>11</v>
-      </c>
-      <c r="H129" s="2">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H129">
+        <v>6</v>
       </c>
       <c r="I129" s="2">
         <f>H129*0.2</f>
-        <v>0.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J129" s="2">
         <f>H129*1.75</f>
-        <v>1.75</v>
+        <v>10.5</v>
       </c>
       <c r="K129" t="s">
         <v>25</v>
@@ -7067,10 +7063,10 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>2170</v>
+        <v>2194</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7079,24 +7075,24 @@
         <v>590</v>
       </c>
       <c r="E130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130">
         <v>32</v>
       </c>
-      <c r="F130">
-        <v>29</v>
-      </c>
       <c r="G130" s="3" t="s">
-        <v>47</v>
+        <v>459</v>
       </c>
       <c r="H130">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I130" s="2">
         <f>H130*0.2</f>
-        <v>1</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="J130" s="2">
         <f>H130*1.75</f>
-        <v>8.75</v>
+        <v>49</v>
       </c>
       <c r="K130" t="s">
         <v>25</v>
@@ -7104,10 +7100,10 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>2188</v>
+        <v>2517</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>57</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -7116,24 +7112,24 @@
         <v>590</v>
       </c>
       <c r="E131" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="F131">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="H131">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I131" s="2">
         <f>H131*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J131" s="2">
         <f>H131*1.75</f>
-        <v>10.5</v>
+        <v>24.5</v>
       </c>
       <c r="K131" t="s">
         <v>25</v>
@@ -7141,10 +7137,10 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>2194</v>
+        <v>2724</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="C132">
         <v>2</v>
@@ -7153,24 +7149,24 @@
         <v>590</v>
       </c>
       <c r="E132" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F132">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H132">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I132" s="2">
         <f>H132*0.2</f>
-        <v>5.6000000000000005</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J132" s="2">
         <f>H132*1.75</f>
-        <v>49</v>
+        <v>12.25</v>
       </c>
       <c r="K132" t="s">
         <v>25</v>
@@ -7178,36 +7174,36 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>2517</v>
+        <v>2841</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="C133">
         <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E133" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F133">
-        <v>35</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H133">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="2">
+        <v>16</v>
       </c>
       <c r="I133" s="2">
         <f>H133*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>3.2</v>
       </c>
       <c r="J133" s="2">
         <f>H133*1.75</f>
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="K133" t="s">
         <v>25</v>
@@ -7215,10 +7211,10 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>2724</v>
+        <v>4657</v>
       </c>
       <c r="B134" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -7227,24 +7223,24 @@
         <v>590</v>
       </c>
       <c r="E134" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F134">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>67</v>
+        <v>469</v>
       </c>
       <c r="H134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I134" s="2">
         <f>H134*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J134" s="2">
         <f>H134*1.75</f>
-        <v>12.25</v>
+        <v>15.75</v>
       </c>
       <c r="K134" t="s">
         <v>25</v>
@@ -7252,36 +7248,36 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>2841</v>
+        <v>5010</v>
       </c>
       <c r="B135" t="s">
-        <v>160</v>
+        <v>291</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E135" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="F135">
-        <v>26</v>
-      </c>
-      <c r="G135" t="s">
-        <v>11</v>
-      </c>
-      <c r="H135" s="2">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H135">
+        <v>7</v>
       </c>
       <c r="I135" s="2">
         <f>H135*0.2</f>
-        <v>3.2</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J135" s="2">
         <f>H135*1.75</f>
-        <v>28</v>
+        <v>12.25</v>
       </c>
       <c r="K135" t="s">
         <v>25</v>
@@ -7289,10 +7285,10 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>4657</v>
+        <v>5514</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -7301,24 +7297,24 @@
         <v>590</v>
       </c>
       <c r="E136" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="F136">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H136">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I136" s="2">
         <f>H136*0.2</f>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J136" s="2">
         <f>H136*1.75</f>
-        <v>15.75</v>
+        <v>17.5</v>
       </c>
       <c r="K136" t="s">
         <v>25</v>
@@ -7326,10 +7322,10 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>5010</v>
+        <v>5800</v>
       </c>
       <c r="B137" t="s">
-        <v>291</v>
+        <v>69</v>
       </c>
       <c r="C137">
         <v>2</v>
@@ -7338,24 +7334,24 @@
         <v>590</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="F137">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="H137">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I137" s="2">
         <f>H137*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J137" s="2">
         <f>H137*1.75</f>
-        <v>12.25</v>
+        <v>21</v>
       </c>
       <c r="K137" t="s">
         <v>25</v>
@@ -7363,10 +7359,10 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>5514</v>
+        <v>5833</v>
       </c>
       <c r="B138" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -7375,24 +7371,24 @@
         <v>590</v>
       </c>
       <c r="E138" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="F138">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>465</v>
+        <v>67</v>
       </c>
       <c r="H138">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I138" s="2">
         <f>H138*0.2</f>
-        <v>2</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J138" s="2">
         <f>H138*1.75</f>
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="K138" t="s">
         <v>25</v>
@@ -7400,10 +7396,10 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>5800</v>
+        <v>6046</v>
       </c>
       <c r="B139" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="C139">
         <v>2</v>
@@ -7412,24 +7408,24 @@
         <v>590</v>
       </c>
       <c r="E139" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F139">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>467</v>
+        <v>67</v>
       </c>
       <c r="H139">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I139" s="2">
         <f>H139*0.2</f>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="J139" s="2">
         <f>H139*1.75</f>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K139" t="s">
         <v>25</v>
@@ -7437,10 +7433,10 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>5833</v>
+        <v>6052</v>
       </c>
       <c r="B140" t="s">
-        <v>199</v>
+        <v>33</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -7449,24 +7445,24 @@
         <v>590</v>
       </c>
       <c r="E140" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F140">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H140">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I140" s="2">
         <f>H140*0.2</f>
-        <v>2.4000000000000004</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="J140" s="2">
         <f>H140*1.75</f>
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K140" t="s">
         <v>25</v>
@@ -7474,10 +7470,10 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>6046</v>
+        <v>6884</v>
       </c>
       <c r="B141" t="s">
-        <v>285</v>
+        <v>101</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -7486,24 +7482,24 @@
         <v>590</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F141">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>67</v>
+        <v>463</v>
       </c>
       <c r="H141">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I141" s="2">
         <f>H141*0.2</f>
-        <v>1.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J141" s="2">
         <f>H141*1.75</f>
-        <v>14</v>
+        <v>19.25</v>
       </c>
       <c r="K141" t="s">
         <v>25</v>
@@ -7511,36 +7507,36 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>6052</v>
+        <v>6908</v>
       </c>
       <c r="B142" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="s">
         <v>590</v>
       </c>
       <c r="E142" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F142">
         <v>23</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>11</v>
+        <v>462</v>
       </c>
       <c r="H142">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I142" s="2">
         <f>H142*0.2</f>
-        <v>5.6000000000000005</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J142" s="2">
         <f>H142*1.75</f>
-        <v>49</v>
+        <v>29.75</v>
       </c>
       <c r="K142" t="s">
         <v>25</v>
@@ -7548,36 +7544,36 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>6832</v>
+        <v>7023</v>
       </c>
       <c r="B143" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C143">
         <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E143" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F143">
-        <v>21</v>
-      </c>
-      <c r="G143" t="s">
-        <v>14</v>
-      </c>
-      <c r="H143" s="2">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143">
+        <v>15</v>
       </c>
       <c r="I143" s="2">
         <f>H143*0.2</f>
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="2">
         <f>H143*1.75</f>
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="K143" t="s">
         <v>25</v>
@@ -7585,10 +7581,10 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>6884</v>
+        <v>7070</v>
       </c>
       <c r="B144" t="s">
-        <v>101</v>
+        <v>232</v>
       </c>
       <c r="C144">
         <v>2</v>
@@ -7597,24 +7593,24 @@
         <v>590</v>
       </c>
       <c r="E144" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144">
         <v>23</v>
       </c>
-      <c r="F144">
-        <v>24</v>
-      </c>
       <c r="G144" s="3" t="s">
-        <v>463</v>
+        <v>21</v>
       </c>
       <c r="H144">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I144" s="2">
         <f>H144*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J144" s="2">
         <f>H144*1.75</f>
-        <v>19.25</v>
+        <v>14</v>
       </c>
       <c r="K144" t="s">
         <v>25</v>
@@ -7622,36 +7618,36 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>6908</v>
+        <v>7129</v>
       </c>
       <c r="B145" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="s">
         <v>590</v>
       </c>
       <c r="E145" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F145">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H145">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I145" s="2">
         <f>H145*0.2</f>
-        <v>3.4000000000000004</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J145" s="2">
         <f>H145*1.75</f>
-        <v>29.75</v>
+        <v>19.25</v>
       </c>
       <c r="K145" t="s">
         <v>25</v>
@@ -7659,10 +7655,10 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>7023</v>
+        <v>7223</v>
       </c>
       <c r="B146" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="C146">
         <v>2</v>
@@ -7671,24 +7667,24 @@
         <v>590</v>
       </c>
       <c r="E146" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="F146">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>11</v>
+        <v>470</v>
       </c>
       <c r="H146">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2">
         <f>H146*0.2</f>
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J146" s="2">
         <f>H146*1.75</f>
-        <v>26.25</v>
+        <v>14</v>
       </c>
       <c r="K146" t="s">
         <v>25</v>
@@ -7696,10 +7692,10 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>7070</v>
+        <v>7314</v>
       </c>
       <c r="B147" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="C147">
         <v>2</v>
@@ -7708,24 +7704,24 @@
         <v>590</v>
       </c>
       <c r="E147" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="F147">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>21</v>
+        <v>462</v>
       </c>
       <c r="H147">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I147" s="2">
         <f>H147*0.2</f>
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J147" s="2">
         <f>H147*1.75</f>
-        <v>14</v>
+        <v>22.75</v>
       </c>
       <c r="K147" t="s">
         <v>25</v>
@@ -7733,84 +7729,84 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>7129</v>
+        <v>513</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>355</v>
       </c>
       <c r="C148">
         <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E148" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F148">
-        <v>21</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="H148">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="G148" t="s">
+        <v>67</v>
+      </c>
+      <c r="H148" s="2">
+        <v>5</v>
       </c>
       <c r="I148" s="2">
         <f>H148*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J148" s="2">
         <f>H148*1.75</f>
-        <v>19.25</v>
+        <v>8.75</v>
       </c>
       <c r="K148" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>7199</v>
+        <v>531</v>
       </c>
       <c r="B149" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="C149">
         <v>2</v>
       </c>
       <c r="D149" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E149" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F149">
-        <v>21</v>
-      </c>
-      <c r="G149" t="s">
+        <v>32</v>
+      </c>
+      <c r="G149" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H149" s="2">
-        <v>13</v>
+      <c r="H149">
+        <v>19</v>
       </c>
       <c r="I149" s="2">
         <f>H149*0.2</f>
-        <v>2.6</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J149" s="2">
         <f>H149*1.75</f>
-        <v>22.75</v>
+        <v>33.25</v>
       </c>
       <c r="K149" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>7223</v>
+        <v>2529</v>
       </c>
       <c r="B150" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -7819,35 +7815,35 @@
         <v>590</v>
       </c>
       <c r="E150" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F150">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="H150">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I150" s="2">
         <f>H150*0.2</f>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J150" s="2">
         <f>H150*1.75</f>
-        <v>14</v>
+        <v>8.75</v>
       </c>
       <c r="K150" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>7314</v>
+        <v>2764</v>
       </c>
       <c r="B151" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -7856,61 +7852,61 @@
         <v>590</v>
       </c>
       <c r="E151" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="F151">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="H151">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I151" s="2">
         <f>H151*0.2</f>
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J151" s="2">
         <f>H151*1.75</f>
-        <v>22.75</v>
+        <v>61.25</v>
       </c>
       <c r="K151" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>513</v>
+        <v>2765</v>
       </c>
       <c r="B152" t="s">
-        <v>355</v>
+        <v>151</v>
       </c>
       <c r="C152">
         <v>2</v>
       </c>
       <c r="D152" t="s">
-        <v>72</v>
+        <v>590</v>
       </c>
       <c r="E152" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F152">
-        <v>38</v>
-      </c>
-      <c r="G152" t="s">
-        <v>67</v>
-      </c>
-      <c r="H152" s="2">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H152">
+        <v>7</v>
       </c>
       <c r="I152" s="2">
         <f>H152*0.2</f>
-        <v>1</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J152" s="2">
         <f>H152*1.75</f>
-        <v>8.75</v>
+        <v>12.25</v>
       </c>
       <c r="K152" t="s">
         <v>12</v>
@@ -7918,10 +7914,10 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>531</v>
+        <v>4465</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="C153">
         <v>2</v>
@@ -7930,24 +7926,24 @@
         <v>590</v>
       </c>
       <c r="E153" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F153">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>10</v>
+        <v>459</v>
       </c>
       <c r="H153">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I153" s="2">
         <f>H153*0.2</f>
-        <v>3.8000000000000003</v>
+        <v>1.8</v>
       </c>
       <c r="J153" s="2">
         <f>H153*1.75</f>
-        <v>33.25</v>
+        <v>15.75</v>
       </c>
       <c r="K153" t="s">
         <v>12</v>
@@ -7955,10 +7951,10 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>2529</v>
+        <v>4502</v>
       </c>
       <c r="B154" t="s">
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -7967,24 +7963,24 @@
         <v>590</v>
       </c>
       <c r="E154" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="F154">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="H154">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I154" s="2">
         <f>H154*0.2</f>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J154" s="2">
         <f>H154*1.75</f>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K154" t="s">
         <v>12</v>
@@ -7992,10 +7988,10 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>2764</v>
+        <v>4686</v>
       </c>
       <c r="B155" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -8004,24 +8000,24 @@
         <v>590</v>
       </c>
       <c r="E155" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F155">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>11</v>
+        <v>459</v>
       </c>
       <c r="H155">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="I155" s="2">
         <f>H155*0.2</f>
-        <v>7</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J155" s="2">
         <f>H155*1.75</f>
-        <v>61.25</v>
+        <v>10.5</v>
       </c>
       <c r="K155" t="s">
         <v>12</v>
@@ -8029,10 +8025,10 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>2765</v>
+        <v>4751</v>
       </c>
       <c r="B156" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -8041,13 +8037,13 @@
         <v>590</v>
       </c>
       <c r="E156" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F156">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H156">
         <v>7</v>
@@ -8066,10 +8062,10 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>4465</v>
+        <v>4892</v>
       </c>
       <c r="B157" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="C157">
         <v>2</v>
@@ -8078,24 +8074,24 @@
         <v>590</v>
       </c>
       <c r="E157" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F157">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="H157">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I157" s="2">
         <f>H157*0.2</f>
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J157" s="2">
         <f>H157*1.75</f>
-        <v>15.75</v>
+        <v>19.25</v>
       </c>
       <c r="K157" t="s">
         <v>12</v>
@@ -8103,10 +8099,10 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>4502</v>
+        <v>5116</v>
       </c>
       <c r="B158" t="s">
-        <v>244</v>
+        <v>426</v>
       </c>
       <c r="C158">
         <v>2</v>
@@ -8115,24 +8111,24 @@
         <v>590</v>
       </c>
       <c r="E158" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="F158">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>464</v>
+        <v>47</v>
       </c>
       <c r="H158">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I158" s="2">
         <f>H158*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="J158" s="2">
         <f>H158*1.75</f>
-        <v>10.5</v>
+        <v>29.75</v>
       </c>
       <c r="K158" t="s">
         <v>12</v>
@@ -8140,10 +8136,10 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>4686</v>
+        <v>5520</v>
       </c>
       <c r="B159" t="s">
-        <v>121</v>
+        <v>226</v>
       </c>
       <c r="C159">
         <v>2</v>
@@ -8152,24 +8148,24 @@
         <v>590</v>
       </c>
       <c r="E159" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F159">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H159">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I159" s="2">
         <f>H159*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="J159" s="2">
         <f>H159*1.75</f>
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="K159" t="s">
         <v>12</v>
@@ -8177,36 +8173,36 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>4751</v>
+        <v>5562</v>
       </c>
       <c r="B160" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="C160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>590</v>
       </c>
       <c r="E160" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F160">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="H160">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I160" s="2">
         <f>H160*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>2</v>
       </c>
       <c r="J160" s="2">
         <f>H160*1.75</f>
-        <v>12.25</v>
+        <v>17.5</v>
       </c>
       <c r="K160" t="s">
         <v>12</v>
@@ -8214,36 +8210,36 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>4892</v>
+        <v>5585</v>
       </c>
       <c r="B161" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" t="s">
         <v>590</v>
       </c>
       <c r="E161" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F161">
         <v>27</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>471</v>
+        <v>11</v>
       </c>
       <c r="H161">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I161" s="2">
         <f>H161*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="J161" s="2">
         <f>H161*1.75</f>
-        <v>19.25</v>
+        <v>59.5</v>
       </c>
       <c r="K161" t="s">
         <v>12</v>
@@ -8251,10 +8247,10 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>5116</v>
+        <v>5603</v>
       </c>
       <c r="B162" t="s">
-        <v>426</v>
+        <v>287</v>
       </c>
       <c r="C162">
         <v>2</v>
@@ -8263,24 +8259,24 @@
         <v>590</v>
       </c>
       <c r="E162" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F162">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="H162">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I162" s="2">
         <f>H162*0.2</f>
-        <v>3.4000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="J162" s="2">
         <f>H162*1.75</f>
-        <v>29.75</v>
+        <v>7</v>
       </c>
       <c r="K162" t="s">
         <v>12</v>
@@ -8288,10 +8284,10 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>5520</v>
+        <v>5739</v>
       </c>
       <c r="B163" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="C163">
         <v>2</v>
@@ -8300,24 +8296,24 @@
         <v>590</v>
       </c>
       <c r="E163" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F163">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="H163">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I163" s="2">
         <f>H163*0.2</f>
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J163" s="2">
         <f>H163*1.75</f>
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="K163" t="s">
         <v>12</v>
@@ -8325,25 +8321,25 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>5562</v>
+        <v>5844</v>
       </c>
       <c r="B164" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="s">
         <v>590</v>
       </c>
       <c r="E164" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F164">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>21</v>
+        <v>462</v>
       </c>
       <c r="H164">
         <v>10</v>
@@ -8362,36 +8358,36 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>5585</v>
+        <v>5885</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
         <v>590</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F165">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>11</v>
+        <v>468</v>
       </c>
       <c r="H165">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I165" s="2">
         <f>H165*0.2</f>
-        <v>6.8000000000000007</v>
+        <v>2</v>
       </c>
       <c r="J165" s="2">
         <f>H165*1.75</f>
-        <v>59.5</v>
+        <v>17.5</v>
       </c>
       <c r="K165" t="s">
         <v>12</v>
@@ -8399,10 +8395,10 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>5603</v>
+        <v>6042</v>
       </c>
       <c r="B166" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C166">
         <v>2</v>
@@ -8411,24 +8407,24 @@
         <v>590</v>
       </c>
       <c r="E166" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F166">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H166">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I166" s="2">
         <f>H166*0.2</f>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J166" s="2">
         <f>H166*1.75</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K166" t="s">
         <v>12</v>
@@ -8436,10 +8432,10 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>5739</v>
+        <v>6642</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="C167">
         <v>2</v>
@@ -8448,24 +8444,24 @@
         <v>590</v>
       </c>
       <c r="E167" t="s">
+        <v>60</v>
+      </c>
+      <c r="F167">
         <v>27</v>
       </c>
-      <c r="F167">
-        <v>24</v>
-      </c>
       <c r="G167" s="3" t="s">
-        <v>466</v>
+        <v>67</v>
       </c>
       <c r="H167">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I167" s="2">
         <f>H167*0.2</f>
-        <v>0.8</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J167" s="2">
         <f>H167*1.75</f>
-        <v>7</v>
+        <v>12.25</v>
       </c>
       <c r="K167" t="s">
         <v>12</v>
@@ -8473,10 +8469,10 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>5844</v>
+        <v>6669</v>
       </c>
       <c r="B168" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -8485,24 +8481,24 @@
         <v>590</v>
       </c>
       <c r="E168" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F168">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="H168">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I168" s="2">
         <f>H168*0.2</f>
-        <v>2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J168" s="2">
         <f>H168*1.75</f>
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="K168" t="s">
         <v>12</v>
@@ -8510,10 +8506,10 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>5885</v>
+        <v>6684</v>
       </c>
       <c r="B169" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C169">
         <v>2</v>
@@ -8522,13 +8518,13 @@
         <v>590</v>
       </c>
       <c r="E169" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F169">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="H169">
         <v>10</v>
@@ -8547,36 +8543,36 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>6042</v>
+        <v>6831</v>
       </c>
       <c r="B170" t="s">
-        <v>286</v>
+        <v>115</v>
       </c>
       <c r="C170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="s">
         <v>590</v>
       </c>
       <c r="E170" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F170">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>67</v>
+        <v>463</v>
       </c>
       <c r="H170">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I170" s="2">
         <f>H170*0.2</f>
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J170" s="2">
         <f>H170*1.75</f>
-        <v>14</v>
+        <v>12.25</v>
       </c>
       <c r="K170" t="s">
         <v>12</v>
@@ -8584,10 +8580,10 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>6642</v>
+        <v>7068</v>
       </c>
       <c r="B171" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -8596,24 +8592,24 @@
         <v>590</v>
       </c>
       <c r="E171" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F171">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I171" s="2">
         <f>H171*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J171" s="2">
         <f>H171*1.75</f>
-        <v>12.25</v>
+        <v>8.75</v>
       </c>
       <c r="K171" t="s">
         <v>12</v>
@@ -8621,10 +8617,10 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>6669</v>
+        <v>7127</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C172">
         <v>2</v>
@@ -8633,24 +8629,24 @@
         <v>590</v>
       </c>
       <c r="E172" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F172">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>11</v>
+        <v>463</v>
       </c>
       <c r="H172">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I172" s="2">
         <f>H172*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="J172" s="2">
         <f>H172*1.75</f>
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="K172" t="s">
         <v>12</v>
@@ -8658,10 +8654,10 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>6684</v>
+        <v>7351</v>
       </c>
       <c r="B173" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="C173">
         <v>2</v>
@@ -8670,24 +8666,24 @@
         <v>590</v>
       </c>
       <c r="E173" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F173">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H173">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I173" s="2">
         <f>H173*0.2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J173" s="2">
         <f>H173*1.75</f>
-        <v>17.5</v>
+        <v>26.25</v>
       </c>
       <c r="K173" t="s">
         <v>12</v>
@@ -8695,47 +8691,47 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>6831</v>
+        <v>22</v>
       </c>
       <c r="B174" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
         <v>590</v>
       </c>
       <c r="E174" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F174">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H174">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I174" s="2">
         <f>H174*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J174" s="2">
         <f>H174*1.75</f>
-        <v>12.25</v>
+        <v>8.75</v>
       </c>
       <c r="K174" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>7068</v>
+        <v>610</v>
       </c>
       <c r="B175" t="s">
-        <v>335</v>
+        <v>437</v>
       </c>
       <c r="C175">
         <v>2</v>
@@ -8744,35 +8740,35 @@
         <v>590</v>
       </c>
       <c r="E175" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F175">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="H175">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I175" s="2">
         <f>H175*0.2</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J175" s="2">
         <f>H175*1.75</f>
-        <v>8.75</v>
+        <v>1.75</v>
       </c>
       <c r="K175" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>7127</v>
+        <v>1852</v>
       </c>
       <c r="B176" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="C176">
         <v>2</v>
@@ -8781,72 +8777,72 @@
         <v>590</v>
       </c>
       <c r="E176" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F176">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H176">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I176" s="2">
         <f>H176*0.2</f>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J176" s="2">
         <f>H176*1.75</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K176" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>7351</v>
+        <v>2038</v>
       </c>
       <c r="B177" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D177" t="s">
         <v>590</v>
       </c>
       <c r="E177" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F177">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c r="H177">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I177" s="2">
         <f>H177*0.2</f>
-        <v>3</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J177" s="2">
         <f>H177*1.75</f>
-        <v>26.25</v>
+        <v>21</v>
       </c>
       <c r="K177" t="s">
-        <v>12</v>
+        <v>473</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>22</v>
+        <v>2296</v>
       </c>
       <c r="B178" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C178">
         <v>2</v>
@@ -8855,24 +8851,24 @@
         <v>590</v>
       </c>
       <c r="E178" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F178">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H178">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I178" s="2">
         <f>H178*0.2</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J178" s="2">
         <f>H178*1.75</f>
-        <v>8.75</v>
+        <v>26.25</v>
       </c>
       <c r="K178" t="s">
         <v>473</v>
@@ -8880,10 +8876,10 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>610</v>
+        <v>2379</v>
       </c>
       <c r="B179" t="s">
-        <v>437</v>
+        <v>40</v>
       </c>
       <c r="C179">
         <v>2</v>
@@ -8892,24 +8888,24 @@
         <v>590</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F179">
         <v>31</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>47</v>
+        <v>462</v>
       </c>
       <c r="H179">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I179" s="2">
         <f>H179*0.2</f>
-        <v>0.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J179" s="2">
         <f>H179*1.75</f>
-        <v>1.75</v>
+        <v>38.5</v>
       </c>
       <c r="K179" t="s">
         <v>473</v>
@@ -8917,10 +8913,10 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180">
-        <v>1852</v>
+        <v>4199</v>
       </c>
       <c r="B180" t="s">
-        <v>86</v>
+        <v>163</v>
       </c>
       <c r="C180">
         <v>2</v>
@@ -8929,24 +8925,24 @@
         <v>590</v>
       </c>
       <c r="E180" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F180">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H180">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I180" s="2">
         <f>H180*0.2</f>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J180" s="2">
         <f>H180*1.75</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K180" t="s">
         <v>473</v>
@@ -8954,36 +8950,36 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181">
-        <v>2038</v>
+        <v>4210</v>
       </c>
       <c r="B181" t="s">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" t="s">
         <v>590</v>
       </c>
       <c r="E181" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F181">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H181">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I181" s="2">
         <f>H181*0.2</f>
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="J181" s="2">
         <f>H181*1.75</f>
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K181" t="s">
         <v>473</v>
@@ -8991,36 +8987,36 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>2296</v>
+        <v>4371</v>
       </c>
       <c r="B182" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="s">
         <v>590</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F182">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H182">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I182" s="2">
         <f>H182*0.2</f>
-        <v>3</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="J182" s="2">
         <f>H182*1.75</f>
-        <v>26.25</v>
+        <v>24.5</v>
       </c>
       <c r="K182" t="s">
         <v>473</v>
@@ -9028,10 +9024,10 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>2379</v>
+        <v>4378</v>
       </c>
       <c r="B183" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="C183">
         <v>2</v>
@@ -9040,24 +9036,24 @@
         <v>590</v>
       </c>
       <c r="E183" t="s">
+        <v>39</v>
+      </c>
+      <c r="F183">
         <v>27</v>
       </c>
-      <c r="F183">
-        <v>31</v>
-      </c>
       <c r="G183" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="H183">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I183" s="2">
         <f>H183*0.2</f>
-        <v>4.4000000000000004</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J183" s="2">
         <f>H183*1.75</f>
-        <v>38.5</v>
+        <v>5.25</v>
       </c>
       <c r="K183" t="s">
         <v>473</v>
@@ -9065,10 +9061,10 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184">
-        <v>4199</v>
+        <v>4433</v>
       </c>
       <c r="B184" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="C184">
         <v>2</v>
@@ -9077,24 +9073,24 @@
         <v>590</v>
       </c>
       <c r="E184" t="s">
+        <v>36</v>
+      </c>
+      <c r="F184">
         <v>27</v>
       </c>
-      <c r="F184">
-        <v>30</v>
-      </c>
       <c r="G184" s="3" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="H184">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I184" s="2">
         <f>H184*0.2</f>
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J184" s="2">
         <f>H184*1.75</f>
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="K184" t="s">
         <v>473</v>
@@ -9102,10 +9098,10 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>4210</v>
+        <v>4510</v>
       </c>
       <c r="B185" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="C185">
         <v>2</v>
@@ -9114,24 +9110,24 @@
         <v>590</v>
       </c>
       <c r="E185" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F185">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H185">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I185" s="2">
         <f>H185*0.2</f>
-        <v>1.6</v>
+        <v>3.8000000000000003</v>
       </c>
       <c r="J185" s="2">
         <f>H185*1.75</f>
-        <v>14</v>
+        <v>33.25</v>
       </c>
       <c r="K185" t="s">
         <v>473</v>
@@ -9139,10 +9135,10 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>4371</v>
+        <v>5544</v>
       </c>
       <c r="B186" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -9151,24 +9147,24 @@
         <v>590</v>
       </c>
       <c r="E186" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F186">
         <v>26</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H186">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I186" s="2">
         <f>H186*0.2</f>
-        <v>2.8000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J186" s="2">
         <f>H186*1.75</f>
-        <v>24.5</v>
+        <v>14</v>
       </c>
       <c r="K186" t="s">
         <v>473</v>
@@ -9176,10 +9172,10 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>4378</v>
+        <v>5555</v>
       </c>
       <c r="B187" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="C187">
         <v>2</v>
@@ -9188,24 +9184,24 @@
         <v>590</v>
       </c>
       <c r="E187" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F187">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H187">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I187" s="2">
         <f>H187*0.2</f>
-        <v>0.60000000000000009</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J187" s="2">
         <f>H187*1.75</f>
-        <v>5.25</v>
+        <v>10.5</v>
       </c>
       <c r="K187" t="s">
         <v>473</v>
@@ -9213,10 +9209,10 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188">
-        <v>4433</v>
+        <v>5734</v>
       </c>
       <c r="B188" t="s">
-        <v>313</v>
+        <v>41</v>
       </c>
       <c r="C188">
         <v>2</v>
@@ -9225,24 +9221,24 @@
         <v>590</v>
       </c>
       <c r="E188" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F188">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>468</v>
+        <v>10</v>
       </c>
       <c r="H188">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I188" s="2">
         <f>H188*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="J188" s="2">
         <f>H188*1.75</f>
-        <v>10.5</v>
+        <v>22.75</v>
       </c>
       <c r="K188" t="s">
         <v>473</v>
@@ -9250,10 +9246,10 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>4510</v>
+        <v>5841</v>
       </c>
       <c r="B189" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C189">
         <v>2</v>
@@ -9262,24 +9258,24 @@
         <v>590</v>
       </c>
       <c r="E189" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F189">
         <v>27</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I189" s="2">
         <f>H189*0.2</f>
-        <v>3.8000000000000003</v>
+        <v>3.6</v>
       </c>
       <c r="J189" s="2">
         <f>H189*1.75</f>
-        <v>33.25</v>
+        <v>31.5</v>
       </c>
       <c r="K189" t="s">
         <v>473</v>
@@ -9287,25 +9283,25 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>5544</v>
+        <v>5862</v>
       </c>
       <c r="B190" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="C190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" t="s">
         <v>590</v>
       </c>
       <c r="E190" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F190">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>11</v>
+        <v>464</v>
       </c>
       <c r="H190">
         <v>8</v>
@@ -9324,10 +9320,10 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>5555</v>
+        <v>6190</v>
       </c>
       <c r="B191" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="C191">
         <v>2</v>
@@ -9336,24 +9332,24 @@
         <v>590</v>
       </c>
       <c r="E191" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F191">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="H191">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I191" s="2">
         <f>H191*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J191" s="2">
         <f>H191*1.75</f>
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="K191" t="s">
         <v>473</v>
@@ -9361,10 +9357,10 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>5734</v>
+        <v>6666</v>
       </c>
       <c r="B192" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="C192">
         <v>2</v>
@@ -9373,24 +9369,24 @@
         <v>590</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="F192">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H192">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I192" s="2">
         <f>H192*0.2</f>
-        <v>2.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="J192" s="2">
         <f>H192*1.75</f>
-        <v>22.75</v>
+        <v>12.25</v>
       </c>
       <c r="K192" t="s">
         <v>473</v>
@@ -9398,10 +9394,10 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>5841</v>
+        <v>6766</v>
       </c>
       <c r="B193" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C193">
         <v>2</v>
@@ -9410,24 +9406,24 @@
         <v>590</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F193">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>47</v>
+        <v>465</v>
       </c>
       <c r="H193">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I193" s="2">
         <f>H193*0.2</f>
-        <v>3.6</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J193" s="2">
         <f>H193*1.75</f>
-        <v>31.5</v>
+        <v>10.5</v>
       </c>
       <c r="K193" t="s">
         <v>473</v>
@@ -9435,10 +9431,10 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>5862</v>
+        <v>6844</v>
       </c>
       <c r="B194" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C194">
         <v>2</v>
@@ -9447,24 +9443,24 @@
         <v>590</v>
       </c>
       <c r="E194" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F194">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H194">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I194" s="2">
         <f>H194*0.2</f>
-        <v>1.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J194" s="2">
         <f>H194*1.75</f>
-        <v>14</v>
+        <v>19.25</v>
       </c>
       <c r="K194" t="s">
         <v>473</v>
@@ -9472,10 +9468,10 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>6190</v>
+        <v>6986</v>
       </c>
       <c r="B195" t="s">
-        <v>206</v>
+        <v>278</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -9487,21 +9483,21 @@
         <v>17</v>
       </c>
       <c r="F195">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>21</v>
+        <v>469</v>
       </c>
       <c r="H195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I195" s="2">
         <f>H195*0.2</f>
-        <v>1</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J195" s="2">
         <f>H195*1.75</f>
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="K195" t="s">
         <v>473</v>
@@ -9509,10 +9505,10 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>6666</v>
+        <v>7175</v>
       </c>
       <c r="B196" t="s">
-        <v>119</v>
+        <v>310</v>
       </c>
       <c r="C196">
         <v>2</v>
@@ -9521,24 +9517,24 @@
         <v>590</v>
       </c>
       <c r="E196" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F196">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>21</v>
+        <v>468</v>
       </c>
       <c r="H196">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I196" s="2">
         <f>H196*0.2</f>
-        <v>1.4000000000000001</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="J196" s="2">
         <f>H196*1.75</f>
-        <v>12.25</v>
+        <v>5.25</v>
       </c>
       <c r="K196" t="s">
         <v>473</v>
@@ -9546,150 +9542,138 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>6766</v>
+        <v>530</v>
       </c>
       <c r="B197" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C197">
         <v>2</v>
       </c>
       <c r="D197" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E197" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F197">
-        <v>28</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="H197">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="G197" t="s">
+        <v>462</v>
+      </c>
+      <c r="H197" s="2">
+        <v>13</v>
       </c>
       <c r="I197" s="2">
         <f>H197*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="J197" s="2">
         <f>H197*1.75</f>
-        <v>10.5</v>
-      </c>
-      <c r="K197" t="s">
-        <v>473</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>6844</v>
+        <v>788</v>
       </c>
       <c r="B198" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C198">
         <v>2</v>
       </c>
       <c r="D198" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E198" t="s">
         <v>36</v>
       </c>
       <c r="F198">
-        <v>23</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H198">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="G198" t="s">
+        <v>459</v>
+      </c>
+      <c r="H198" s="2">
+        <v>8</v>
       </c>
       <c r="I198" s="2">
         <f>H198*0.2</f>
-        <v>2.2000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J198" s="2">
         <f>H198*1.75</f>
-        <v>19.25</v>
-      </c>
-      <c r="K198" t="s">
-        <v>473</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>6986</v>
+        <v>6832</v>
       </c>
       <c r="B199" t="s">
-        <v>278</v>
+        <v>52</v>
       </c>
       <c r="C199">
         <v>2</v>
       </c>
       <c r="D199" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F199">
-        <v>23</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="H199">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="G199" t="s">
+        <v>14</v>
+      </c>
+      <c r="H199" s="2">
+        <v>16</v>
       </c>
       <c r="I199" s="2">
         <f>H199*0.2</f>
-        <v>1.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="J199" s="2">
         <f>H199*1.75</f>
-        <v>10.5</v>
-      </c>
-      <c r="K199" t="s">
-        <v>473</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>7175</v>
+        <v>7199</v>
       </c>
       <c r="B200" t="s">
-        <v>310</v>
+        <v>130</v>
       </c>
       <c r="C200">
         <v>2</v>
       </c>
       <c r="D200" t="s">
-        <v>590</v>
+        <v>72</v>
       </c>
       <c r="E200" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F200">
-        <v>26</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="H200">
-        <v>3</v>
+        <v>21</v>
+      </c>
+      <c r="G200" t="s">
+        <v>10</v>
+      </c>
+      <c r="H200" s="2">
+        <v>13</v>
       </c>
       <c r="I200" s="2">
         <f>H200*0.2</f>
-        <v>0.60000000000000009</v>
+        <v>2.6</v>
       </c>
       <c r="J200" s="2">
         <f>H200*1.75</f>
-        <v>5.25</v>
-      </c>
-      <c r="K200" t="s">
-        <v>473</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.2">
@@ -19387,11 +19371,11 @@
         <v>4</v>
       </c>
       <c r="I513" s="2">
-        <f t="shared" ref="I513:I517" si="0">H513*0.2</f>
+        <f>H513*0.2</f>
         <v>0.8</v>
       </c>
       <c r="J513" s="2">
-        <f t="shared" ref="J513:J517" si="1">H513*1.75</f>
+        <f>H513*1.75</f>
         <v>7</v>
       </c>
     </row>
@@ -19418,11 +19402,11 @@
         <v>4</v>
       </c>
       <c r="I514" s="2">
-        <f t="shared" si="0"/>
+        <f>H514*0.2</f>
         <v>0.8</v>
       </c>
       <c r="J514" s="2">
-        <f t="shared" si="1"/>
+        <f>H514*1.75</f>
         <v>7</v>
       </c>
     </row>
@@ -19449,11 +19433,11 @@
         <v>3</v>
       </c>
       <c r="I515" s="2">
-        <f t="shared" si="0"/>
+        <f>H515*0.2</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="J515" s="2">
-        <f t="shared" si="1"/>
+        <f>H515*1.75</f>
         <v>5.25</v>
       </c>
     </row>
@@ -19480,11 +19464,11 @@
         <v>1</v>
       </c>
       <c r="I516" s="2">
-        <f t="shared" si="0"/>
+        <f>H516*0.2</f>
         <v>0.2</v>
       </c>
       <c r="J516" s="2">
-        <f t="shared" si="1"/>
+        <f>H516*1.75</f>
         <v>1.75</v>
       </c>
     </row>
@@ -19511,11 +19495,11 @@
         <v>4</v>
       </c>
       <c r="I517" s="2">
-        <f t="shared" si="0"/>
+        <f>H517*0.2</f>
         <v>0.8</v>
       </c>
       <c r="J517" s="2">
-        <f t="shared" si="1"/>
+        <f>H517*1.75</f>
         <v>7</v>
       </c>
     </row>
@@ -20544,8 +20528,8 @@
       <c r="H773"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X774">
-    <sortCondition ref="K49:K774"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X773">
+    <sortCondition ref="K1:K773"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Database Fanta.xlsx
+++ b/Database Fanta.xlsx
@@ -1268,6 +1268,11 @@
           <t>Rossi F.</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Atalanta</t>
@@ -1302,6 +1307,11 @@
           <t>Fruchtl</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Lecce</t>
@@ -1336,6 +1346,11 @@
           <t>Angelino</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Roma</t>
@@ -1370,6 +1385,11 @@
           <t>Gutierrez</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Napoli</t>
@@ -1404,6 +1424,11 @@
           <t>Bjarkason</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Venezia</t>
@@ -6767,6 +6792,11 @@
       <c r="C149" t="n">
         <v>2</v>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>Parma</t>
@@ -15140,6 +15170,11 @@
           <t>Dallinga</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>Bologna</t>
@@ -16947,6 +16982,11 @@
           <t>Perez M.</t>
         </is>
       </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>Lecce</t>
@@ -17253,6 +17293,11 @@
           <t>Athekame</t>
         </is>
       </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>Milan</t>
@@ -20109,6 +20154,11 @@
           <t>Lukaku</t>
         </is>
       </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>Napoli</t>
@@ -20211,6 +20261,11 @@
           <t>Djimsiti</t>
         </is>
       </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>Atalanta</t>
@@ -20381,6 +20436,11 @@
           <t>Vogliacco</t>
         </is>
       </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>Genoa</t>
@@ -20449,6 +20509,11 @@
           <t>Raterink</t>
         </is>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>Cagliari</t>
@@ -20517,6 +20582,11 @@
           <t>Samooja</t>
         </is>
       </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>Lecce</t>
@@ -20549,6 +20619,11 @@
       <c r="B536" t="inlineStr">
         <is>
           <t>Ciocci</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>*</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
